--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_7.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_7.xlsx
@@ -618,83 +618,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 7.12</t>
+          <t>X ≈ 7.123</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.342827102113169</v>
+        <v>6.177409896605582</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.11448909532268</v>
+        <v>9.806864913669529</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.57432961014802</v>
+        <v>2.364205093049044</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1785678128125454</v>
+        <v>-0.3621525103428809</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.579656197635224</v>
+        <v>-4.690404480820135</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.793119699715206</v>
+        <v>8.559022720679522</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.918898493204338</v>
+        <v>2.935866228777101</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.635799791441954</v>
+        <v>2.660296267030773</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.679358747348672</v>
+        <v>2.702335047878293</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1405609590167387</v>
+        <v>-0.05763351182547183</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.894329654228571</v>
+        <v>-1.776894320021718</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.278909884695331</v>
+        <v>-8.033754031421445</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.358324516376733</v>
+        <v>-5.1684195102793</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.655802896928236</v>
+        <v>-9.378213489265917</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-12.36628118823579</v>
+        <v>-12.03176638494576</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.727146557816482</v>
+        <v>-9.447272324795414</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-7.829055580532994</v>
+        <v>-7.587995807165193</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.976689752909884</v>
+        <v>-9.691182961335272</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.683697753578492</v>
+        <v>-5.484464979725423</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.492811433735021</v>
+        <v>-5.299576841395535</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-10.12673945020131</v>
+        <v>-9.839571595056675</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-8.168274363370422</v>
+        <v>-7.919442177743271</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.890708915144486</v>
+        <v>-7.647376599920719</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.6291372939933524</v>
+        <v>-1.72546728971917</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>62</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.305528356500005</v>
+        <v>-9.285443041731959</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-12.879402618719</v>
+        <v>-12.83353575893236</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.05109945955554</v>
+        <v>-15.89353468842279</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.7477583507183</v>
+        <v>-8.597255457159939</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-14.52890222940998</v>
+        <v>-15.36038189180448</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-14.34855492550358</v>
+        <v>-15.16804393983075</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-15.12183681031282</v>
+        <v>-15.94905747863713</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.58705127596691</v>
+        <v>-10.50092494429479</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10.54901624959924</v>
+        <v>-10.46291552122366</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.109767388172514</v>
+        <v>-8.023193464349362</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.838824287955092</v>
+        <v>-7.752678172328622</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.512042901360907</v>
+        <v>-6.42584616563515</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.419251963829119</v>
+        <v>-4.331984018024876</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.641185897312305</v>
+        <v>-4.553453799843595</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.082037917612141</v>
+        <v>-1.994048741094396</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.1205663243873403</v>
+        <v>0.2070558479803708</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-3.233199354500186</v>
+        <v>-3.145452296716122</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.728507983224205</v>
+        <v>-1.640995225168396</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.12403239500938</v>
+        <v>-3.036354402367181</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.326743689725326</v>
+        <v>-1.239866359695185</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2582150988623795</v>
+        <v>-0.1708150165389526</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.946605855349674</v>
+        <v>-1.858510441632866</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.553480475382003</v>
+        <v>1.640154081532522</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>3.090415043070507</v>
+        <v>3.177758516731622</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>79</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.782207432180222</v>
+        <v>-6.762667937049414</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.69246057836579</v>
+        <v>6.743670909236229</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.286005281282563</v>
+        <v>-2.236188915645947</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.552496700283982</v>
+        <v>4.607786743213786</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.933179160559988</v>
+        <v>3.016904085196792</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.377764028367537</v>
+        <v>4.460829128188315</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1679121876565617</v>
+        <v>-0.08525238334040353</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.4453307792595567</v>
+        <v>-0.3622233492532345</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.664475849221212</v>
+        <v>-1.581009069324367</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08571234292089969</v>
+        <v>0.169832259913008</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3590893211932951</v>
+        <v>0.4427744517305072</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.08085656936501096</v>
+        <v>0.1650711453117921</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.745221289788319</v>
+        <v>2.83029984881437</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.263310655164638</v>
+        <v>1.349248328619979</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.918890131267354</v>
+        <v>-1.830935279825823</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.200226254022951</v>
+        <v>1.286365368998723</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.120431945026169</v>
+        <v>6.205278773427821</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>8.545230368399309</v>
+        <v>8.629530957836081</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>7.499654399571263</v>
+        <v>7.584025197636755</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.159579202477694</v>
+        <v>5.24442340557512</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.353217378853749</v>
+        <v>3.439475434960066</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.7475427275344657</v>
+        <v>0.8348092252787467</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.288474350433042</v>
+        <v>2.374891397969364</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.584962662115288</v>
+        <v>-1.497619188453513</v>
       </c>
     </row>
     <row r="9">
@@ -871,76 +871,76 @@
         <v>85</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.713734592585908</v>
+        <v>-0.6941615231786287</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.09139839426666185</v>
+        <v>0.1405180772613974</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.507166060384719</v>
+        <v>-2.457583656118523</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.557640073837348</v>
+        <v>-5.508828266435906</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.266096770134439</v>
+        <v>2.34947117646341</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1111934445157985</v>
+        <v>0.1929115778636756</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.997509866513674</v>
+        <v>-2.914888030462791</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.617274459214478</v>
+        <v>-5.532542887433856</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.748877049872618</v>
+        <v>-6.663790606493201</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.693202655470671</v>
+        <v>-8.606309401372364</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.907071462130929</v>
+        <v>-4.82173235131841</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.014696555937682</v>
+        <v>-3.929194185568974</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.964586078569411</v>
+        <v>-3.877422545598527</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.840213466973118</v>
+        <v>-1.753316833543302</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.324493944643109</v>
+        <v>-1.236711888205427</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-5.426650255899311</v>
+        <v>-5.338412400720777</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-4.388311749035061</v>
+        <v>-4.300191769433106</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.843669743327077</v>
+        <v>-6.754553813186426</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-6.629863496313668</v>
+        <v>-6.541057520823877</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.795770738067745</v>
+        <v>-8.706502199841914</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.51723337011193</v>
+        <v>-10.42653958075157</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-7.068240771084092</v>
+        <v>-6.978451896894541</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-4.442724458204331</v>
+        <v>-4.354159140142016</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-2.165751939851702</v>
+        <v>-2.078408466190218</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>87</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.01180069321213</v>
+        <v>-3.223378353074501</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.192883495846175</v>
+        <v>1.628871782467066</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.866914513796729</v>
+        <v>1.920185539087321</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6427452827240074</v>
+        <v>0.05456308716946268</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.153474218413102</v>
+        <v>-3.720788100079751</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.03683308694656517</v>
+        <v>-1.236855913224815</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8042114006575858</v>
+        <v>-2.027678138609353</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.225075220434711</v>
+        <v>-3.455847079169658</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1037228152245149</v>
+        <v>-0.4696469028109007</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.200011888359512</v>
+        <v>5.617778077501512</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7507558054810701</v>
+        <v>0.8343029992995028</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.817805126919559</v>
+        <v>-1.732975022913145</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4971613187900346</v>
+        <v>0.5829056350658917</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.422722034119005</v>
+        <v>1.508557679690171</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3802308248457678</v>
+        <v>-0.2927510548397123</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.080189157782542</v>
+        <v>-1.992975274396052</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.520514446946322</v>
+        <v>3.60607687427207</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.416956209860423</v>
+        <v>3.502775978058892</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.338292967190327</v>
+        <v>1.42455869484963</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>3.822167610865748</v>
+        <v>3.907382972587968</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.429177508838173</v>
+        <v>4.515068994075598</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.205658381155303</v>
+        <v>3.292139192705058</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.332123411978223</v>
+        <v>2.418498097425051</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.640396970277664</v>
+        <v>-4.55305349661618</v>
       </c>
     </row>
     <row r="11">
@@ -1032,243 +1032,243 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.308196042673821</v>
+        <v>-3.749062480578061</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-5.752049510811986</v>
+        <v>-6.221990219342509</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.831845585892431</v>
+        <v>-2.354694627727739</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.479970039389777</v>
+        <v>-2.014049215215003</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.466677645445095</v>
+        <v>2.525227335230603</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.832987853712041</v>
+        <v>4.863642327672991</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.7849923301266415</v>
+        <v>0.8607742582610243</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.660588927839314</v>
+        <v>2.71787424629786</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.626028286102468</v>
+        <v>-1.522211797995155</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2542341930761793</v>
+        <v>-0.1653998778789472</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.110978044103639</v>
+        <v>1.184559915645629</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2603178259856733</v>
+        <v>-0.1705003139096704</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3317062599635108</v>
+        <v>-0.2405147691681506</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5237408240762775</v>
+        <v>0.6059145371288253</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-3.415796586247922</v>
+        <v>-3.285662263716013</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-3.88805126643971</v>
+        <v>-3.753574709103432</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-7.712614703804775</v>
+        <v>-8.17890895017981</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-9.344250077446759</v>
+        <v>-10.43715430528511</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.958470133484717</v>
+        <v>-8.074174538415221</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-5.684697861023999</v>
+        <v>-6.809722633178509</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-7.323116814324003</v>
+        <v>-8.442627117065705</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-6.748481760398818</v>
+        <v>-7.877582338242291</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-7.562929061784899</v>
+        <v>-8.034001721389259</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.378028154685452</v>
+        <v>-4.886757612300272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 26.43</t>
+          <t>X ≈ 26.44</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>116</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.137293873384095</v>
+        <v>-1.583122440450062</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.791425890761232</v>
+        <v>-6.212009113951481</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.535248599058342</v>
+        <v>-5.967200110917673</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.681999143091318</v>
+        <v>-3.633441241049603</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.425072814779732</v>
+        <v>-4.833354161933833</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.951389433676738</v>
+        <v>-6.355445722330636</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.298280809684321</v>
+        <v>-3.707874975414605</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.155624858252949</v>
+        <v>-6.567222262633685</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.398661424632778</v>
+        <v>-4.808253707316794</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.45923477472828</v>
+        <v>-3.373041421537245</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.04397798595118</v>
+        <v>-3.956406220031241</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.466725285470247</v>
+        <v>-3.379057106508967</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.87898137840083</v>
+        <v>-2.790097375824473</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.684527318484911</v>
+        <v>-5.593239221747744</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.770039442413292</v>
+        <v>-3.678876773090686</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.449455734949289</v>
+        <v>-1.360771774412314</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.444210360974729</v>
+        <v>-2.355741282607539</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.134203361047064</v>
+        <v>-5.046576240914625</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.9575280398632202</v>
+        <v>-1.385295484296364</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.493971286593911</v>
+        <v>-2.919853367617797</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.038002202876598</v>
+        <v>-3.46931102406181</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.5286600904226617</v>
+        <v>-0.9601420266523419</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.840290381125222</v>
+        <v>-3.26829839752213</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.916259039243172</v>
+        <v>-2.828915565581688</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 29.65</t>
+          <t>X ≈ 29.66</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.294279001924259</v>
+        <v>-3.245929615193297</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.871388441236348</v>
+        <v>3.893257707069473</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.283590674022548</v>
+        <v>-4.196696978331609</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8191422891534188</v>
+        <v>-0.7593551605073188</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.537424734086478</v>
+        <v>-4.419344578285298</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.668780884086701</v>
+        <v>-2.568333159323188</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.976883680400377</v>
+        <v>-3.345765349371128</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.421598351909459</v>
+        <v>-2.795580367247751</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.218522412813122</v>
+        <v>-3.584435372459168</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.997126401059724</v>
+        <v>-4.360181245221689</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.884595783531751</v>
+        <v>-3.254187430275394</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.00525637842501</v>
+        <v>-3.881274946357884</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.783096467123102</v>
+        <v>-1.679662552930878</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.168525215443104</v>
+        <v>-1.069340776856372</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.522949320695687</v>
+        <v>1.599863242299932</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.07458213309517</v>
+        <v>-1.96544541897034</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5290379748991256</v>
+        <v>-0.4360729516286099</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.042871324847376</v>
+        <v>1.124043876919181</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.261806120504666</v>
+        <v>1.339958681978082</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.6114128840185842</v>
+        <v>0.6940899290694844</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.9026266656256752</v>
+        <v>0.9850695457640271</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.666677490551614</v>
+        <v>1.742556917688269</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.288367978770268</v>
+        <v>2.850364963503651</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.6913909172911588</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="14">
@@ -1278,79 +1278,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.178916294419345</v>
+        <v>-7.10159173552227</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.795505875216143</v>
+        <v>1.832278228288196</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.099292906738526</v>
+        <v>-5.005915160319155</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.923603922366603</v>
+        <v>-1.855590263371425</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.069458589519158</v>
+        <v>-2.96169278306818</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.323168957667178</v>
+        <v>-1.232371333940101</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.435237894976019</v>
+        <v>-4.317519995312765</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.939102113688072</v>
+        <v>-3.821823888628273</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.899406099626624</v>
+        <v>-3.78033670671357</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.794703453503168</v>
+        <v>-7.64089257897173</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.521769833022631</v>
+        <v>-7.368031438239058</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.026433324196461</v>
+        <v>-6.873139623900457</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.039644812458519</v>
+        <v>-4.905372375511625</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.825909147460706</v>
+        <v>-6.673649548941128</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.809484048610308</v>
+        <v>-2.692538616300141</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.773376431560671</v>
+        <v>-3.647744352127198</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-7.030440303759896</v>
+        <v>-6.879276179077053</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-7.137413364634426</v>
+        <v>-6.986564664495539</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-6.137500044053809</v>
+        <v>-5.999273840160413</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.2989794341534022</v>
+        <v>0.3841161110896678</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.5607101110461699</v>
+        <v>-0.9335351053989314</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.144557512423269</v>
+        <v>-0.2341872683582551</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.92434210526298</v>
+        <v>-2.285293951225029</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.000310763381108</v>
+        <v>-2.361126204448126</v>
       </c>
     </row>
     <row r="15">
@@ -1360,79 +1360,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.41858435515563</v>
+        <v>4.411086601022227</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.612639252408471</v>
+        <v>-1.550288747772825</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9869467113563104</v>
+        <v>1.037585492929516</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.892373421208404</v>
+        <v>1.931957808637343</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.763962366655683</v>
+        <v>4.812438491253246</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.334844983795435</v>
+        <v>3.389429912424774</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.175841494083208</v>
+        <v>4.229368748298292</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.086410607725455</v>
+        <v>3.149186188326567</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.939469014273257</v>
+        <v>3.994115835334995</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.784139502569147</v>
+        <v>4.831027789236636</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.439609912077223</v>
+        <v>3.496878286323202</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.782691141799774</v>
+        <v>4.826190892963034</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.466210533234154</v>
+        <v>4.511066709726634</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.868078337632703</v>
+        <v>5.90113442381822</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8.457363197160007</v>
+        <v>8.464408343321615</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>9.059878502613223</v>
+        <v>9.061087766094317</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.67338634845693</v>
+        <v>5.710344608466087</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>6.37912322479513</v>
+        <v>6.413477385661778</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>9.037867815075309</v>
+        <v>9.048734550941667</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>8.087328901334594</v>
+        <v>7.626654200637731</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>6.730956555620487</v>
+        <v>6.280768470495396</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>8.280990439252541</v>
+        <v>7.817825734892558</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.116816431322214</v>
+        <v>5.672945608664932</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>6.040847773204263</v>
+        <v>5.597113355441486</v>
       </c>
     </row>
     <row r="16">
@@ -1445,76 +1445,76 @@
         <v>121</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.906380577923521</v>
+        <v>2.926195870069705</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.220897616052099</v>
+        <v>-3.171528793163731</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.505308223341551</v>
+        <v>8.556781541598546</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.79110605846769</v>
+        <v>7.843630915955707</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.599610265399328</v>
+        <v>6.681725430397591</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.143441803326915</v>
+        <v>5.22530886946992</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.30540936461157</v>
+        <v>9.388423581652596</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>10.32524424294559</v>
+        <v>9.931608601112359</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.899235032854115</v>
+        <v>7.50261499199145</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>7.130400502729557</v>
+        <v>6.726160404356236</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.108569867684054</v>
+        <v>3.707359760270158</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.956420209003113</v>
+        <v>7.545226381681914</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.010487294246232</v>
+        <v>6.083656347550296</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>8.269083349747682</v>
+        <v>8.338009029914787</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.613620546622911</v>
+        <v>7.68453084695556</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>7.385685381281853</v>
+        <v>7.456475408330761</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>7.251547476033835</v>
+        <v>7.326154786052257</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.320082041382641</v>
+        <v>6.399403831955468</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>5.709816946010669</v>
+        <v>5.791697097484878</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.070464021941994</v>
+        <v>5.15472935851291</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.17999236829268</v>
+        <v>6.267438691769549</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>6.104009991762119</v>
+        <v>6.191592730360448</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>6.378860374075693</v>
+        <v>6.466067442842501</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>6.302891715957742</v>
+        <v>6.390235189619226</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>96</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.018499191696968</v>
+        <v>2.038314483843152</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.655110972971933</v>
+        <v>1.704479795860301</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.241395723856002</v>
+        <v>1.292869042112997</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.565417821659665</v>
+        <v>1.617942679147681</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.349007299621732</v>
+        <v>5.431122464619996</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.426535130188398</v>
+        <v>2.508402196331403</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.875324498484353</v>
+        <v>7.958338715525379</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.478518473162012</v>
+        <v>4.561961823082463</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.560033198763414</v>
+        <v>5.64116262468584</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.781843396035072</v>
+        <v>4.862594286446857</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9002162852132045</v>
+        <v>0.9842292659098604</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.45982734752819</v>
+        <v>-1.371517560859715</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5286136528179242</v>
+        <v>0.6143787530923959</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.818532307521593</v>
+        <v>-2.724668179124322</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-5.56708105655693</v>
+        <v>-5.466333316203674</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-4.348130045715159</v>
+        <v>-4.870024011763348</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-4.482267950962978</v>
+        <v>-5.008274174957883</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-4.587287104622874</v>
+        <v>-5.118508421665688</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-4.371105919003114</v>
+        <v>-4.899605512878956</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.142345895413378</v>
+        <v>-3.66803328612415</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.5607101110461699</v>
+        <v>-0.4732637875693015</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.720025820909825</v>
+        <v>-2.632443082311497</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.445175438596493</v>
+        <v>-2.357968369829685</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.521144096714444</v>
+        <v>-2.43380062305296</v>
       </c>
     </row>
     <row r="18">
@@ -1609,76 +1609,76 @@
         <v>131</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.743960620261099</v>
+        <v>-1.724145328114915</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.347987992157641</v>
+        <v>-1.298619169269273</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.782383939312822</v>
+        <v>-2.730910621055827</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.539458925874627</v>
+        <v>-6.48693406838661</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.860222278789045</v>
+        <v>-3.778107113790782</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.914407835821564</v>
+        <v>-2.832540769678559</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.162872958155539</v>
+        <v>-2.079858741114514</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.72180320767238</v>
+        <v>-4.638359857751929</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.8765916617110463</v>
+        <v>-0.7928810910514841</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8874862783604271</v>
+        <v>-0.8022430114564898</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.375221173117325</v>
+        <v>-1.288795926340974</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.655002078189156</v>
+        <v>-1.567080930012644</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.305241828793832</v>
+        <v>-4.209300912004643</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.291495237401129</v>
+        <v>-5.192330959545465</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.663142330337493</v>
+        <v>-3.567077803353619</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-5.357990096606159</v>
+        <v>-5.26101760369508</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.728769223228198</v>
+        <v>-4.634863974187077</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.833788376887505</v>
+        <v>-4.741670865570796</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.617607191267744</v>
+        <v>-4.528529981886109</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.957231391596409</v>
+        <v>-5.870603115786302</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-4.210519271351686</v>
+        <v>-4.123072947874817</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.523142869256112</v>
+        <v>-3.435560130657784</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.9582161510646827</v>
+        <v>-0.8710090822978742</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2708260305566839</v>
+        <v>-0.1834825568951999</v>
       </c>
     </row>
     <row r="19">
@@ -1691,76 +1691,76 @@
         <v>125</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.46557864385337</v>
+        <v>1.485393935999554</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.10384282048458</v>
+        <v>1.153211643372948</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.22524981390842</v>
+        <v>5.276723132165415</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.30658256604891</v>
+        <v>5.359107423536926</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.937310027406852</v>
+        <v>5.019425192405116</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.932186525358581</v>
+        <v>6.014053591501586</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.753616965203818</v>
+        <v>2.836631182244844</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.666665548141559</v>
+        <v>1.75010889806201</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.6837318177914753</v>
+        <v>-0.5996078639126594</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.866721964915904</v>
+        <v>-3.777348638885059</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.596195901008585</v>
+        <v>-3.504586249584463</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.479343392152259</v>
+        <v>-5.381147165399767</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.621647478353637</v>
+        <v>-6.51598450800951</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.171551756419532</v>
+        <v>-3.553560222285711</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.751691948657928</v>
+        <v>-2.622911409608491</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3564633790485416</v>
+        <v>-1.224680644861451</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3093987157036366</v>
+        <v>-0.5632673324687687</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.004379562043979</v>
+        <v>0.125478101512293</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3794392523364536</v>
+        <v>-0.7707735463027916</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.6076541045864445</v>
+        <v>0.694282380396551</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.8642898889540191</v>
+        <v>0.9517362124308875</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.01169248757690866</v>
+        <v>0.07589025102141989</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.06315789473684</v>
+        <v>1.150364963503648</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.1871892366188916</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="20">
@@ -1773,76 +1773,76 @@
         <v>139</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.572084881002397</v>
+        <v>-2.552269588856213</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.06730427312261611</v>
+        <v>-0.0179354502342477</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.801418056521769</v>
+        <v>2.852891374778764</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.06442070488080986</v>
+        <v>-0.01189584739279326</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.016046282025535</v>
+        <v>-3.933931117027271</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.265977199851889</v>
+        <v>-5.184110133708884</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.188316503075683</v>
+        <v>-8.105302286034657</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.464511220542335</v>
+        <v>-8.381067870621884</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.145577786562534</v>
+        <v>-9.057146171204899</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.050090622030865</v>
+        <v>-6.957497931211954</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.342371854736719</v>
+        <v>-5.248307324054736</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.781845387136926</v>
+        <v>-7.678602181976714</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.753151414728109</v>
+        <v>-6.646909689428568</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.25515335762902</v>
+        <v>-6.153506773025462</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-7.63370633714748</v>
+        <v>-7.532963677450354</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-7.757902227969915</v>
+        <v>-7.662114550114318</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-9.330889054080721</v>
+        <v>-9.238481793275248</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-5.119361445150616</v>
+        <v>-5.032195817690031</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-7.061453640825498</v>
+        <v>-6.974577818060347</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.593784744334243</v>
+        <v>-7.507156468524137</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.417724499535218</v>
+        <v>-7.33027817605835</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-10.37140471779256</v>
+        <v>-10.28382197919423</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-12.97425217720544</v>
+        <v>-12.88704510843863</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-12.33079637489173</v>
+        <v>-12.24345290123025</v>
       </c>
     </row>
     <row r="21">
@@ -1855,158 +1855,158 @@
         <v>118</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.189321634572806</v>
+        <v>2.20913692671899</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9857895105538574</v>
+        <v>1.035158333442226</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.063271350934507</v>
+        <v>2.114744669191502</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.26579650215465</v>
+        <v>7.318321359642667</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.199268333724113</v>
+        <v>5.281383498722377</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5233091879520728</v>
+        <v>-0.4414421218090681</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.316621732536063</v>
+        <v>-1.233607515495038</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9282396149684686</v>
+        <v>1.011682964888919</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6148737735393794</v>
+        <v>0.2072294486118835</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.705322539256478</v>
+        <v>-3.116986128530073</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9545112180901896</v>
+        <v>0.5408363063989938</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.060954677539456</v>
+        <v>3.639110792453344</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.440727380540309</v>
+        <v>2.503313281974705</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.761673858564386</v>
+        <v>5.327983311489604</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.407630085240193</v>
+        <v>2.975988125125568</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>4.002858654849774</v>
+        <v>3.57528875085999</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>5.563636003839051</v>
+        <v>5.135149513180352</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4735865396511301</v>
+        <v>-0.3864209121905446</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.437509900205725</v>
+        <v>1.524385722970877</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.9177696242269349</v>
+        <v>-0.8311413484168284</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.928696668614563</v>
+        <v>2.016142992091432</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.005256664965643</v>
+        <v>1.092839403563971</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.957181088314201</v>
+        <v>-2.869974019547392</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.3566807620424299</v>
+        <v>0.4440242357039139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 58.63</t>
+          <t>X ≈ 58.62</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>159</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.194629313019753</v>
+        <v>4.214444605165937</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.0633507107152198</v>
+        <v>0.1127195336035882</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.001982001766784</v>
+        <v>-1.950508683509788</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.050016756999504</v>
+        <v>1.102541614487521</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.05848285308703538</v>
+        <v>0.1405980180852993</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.893564083187719</v>
+        <v>-2.811697017044715</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5253927907321057</v>
+        <v>-0.4423785736910801</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.057755549733081</v>
+        <v>-1.97431219981263</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.782236577931876</v>
+        <v>-5.698829335338047</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.418561470843883</v>
+        <v>-3.331067856488566</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.518756141315272</v>
+        <v>-2.429793140227524</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.859976279904451</v>
+        <v>2.941112902077904</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.993013917157306</v>
+        <v>3.07509485626607</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.771587513824926</v>
+        <v>2.854133974290889</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2256665419079269</v>
+        <v>0.3138794305949375</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.336618381957493</v>
+        <v>3.42169597699597</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.460342111929862</v>
+        <v>4.547329289551968</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>4.3553229582702</v>
+        <v>4.442488585730786</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.942573326279977</v>
+        <v>4.029449149045128</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.500735865592908</v>
+        <v>3.587364141403015</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.957371649960194</v>
+        <v>3.044817973437063</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>4.139250908649608</v>
+        <v>4.226833647247936</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>6.300893743793445</v>
+        <v>6.388100812560253</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>5.595994268065425</v>
+        <v>5.683337741726909</v>
       </c>
     </row>
     <row r="23">
@@ -2019,76 +2019,76 @@
         <v>154</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4115519047095191</v>
+        <v>-0.391736612563335</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.015634379303165</v>
+        <v>-3.966265556414797</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.508801693690899</v>
+        <v>-3.457328375433903</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9842158331101132</v>
+        <v>-0.9316909756220966</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.596198890597158</v>
+        <v>0.6783140555954219</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.022730048708908</v>
+        <v>4.104597114851913</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.604469527813237</v>
+        <v>2.687483744854262</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2635352411017919</v>
+        <v>-0.1800918911813412</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2209963163941637</v>
+        <v>-0.1375890738003349</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.291657440521028</v>
+        <v>-2.204316300792826</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.669185025744397</v>
+        <v>-2.578903523479596</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.00345588541451</v>
+        <v>-0.9146141479994796</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.478929234031341</v>
+        <v>-1.387968623760024</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.648407585415377</v>
+        <v>-3.552666642258274</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-4.956886753852991</v>
+        <v>-4.860924658922393</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.8331470105617313</v>
+        <v>0.9196756507812296</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.04965845596318985</v>
+        <v>0.1366456335852959</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.0553606976963934</v>
+        <v>0.03180492976419202</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.137880810778078</v>
+        <v>-1.051004988012927</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.898839401906883</v>
+        <v>-2.812211126096777</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.740904916240908</v>
+        <v>-4.653458592764039</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.518185994070087</v>
+        <v>-3.430603255471759</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.243335611756663</v>
+        <v>-3.156128542989855</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-5.916706867277213</v>
+        <v>-5.829363393615729</v>
       </c>
     </row>
     <row r="24">
@@ -2098,79 +2098,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.60159076030402</v>
+        <v>3.30770821565082</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.778130365360646</v>
+        <v>1.503066578799626</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3986110290751768</v>
+        <v>-0.6770062116784032</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.349832450860518</v>
+        <v>0.08325581782563773</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.081035111415233</v>
+        <v>4.881519747392545</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1700064693766024</v>
+        <v>-0.06724407384687225</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.574819071902567</v>
+        <v>1.354713066068058</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.016616352111917</v>
+        <v>1.802218211841335</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1309703290189219</v>
+        <v>0.3725838513375095</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.190959574367021</v>
+        <v>4.731628070886863</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.10038771945802</v>
+        <v>-2.333582848123342</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.321495510023468</v>
+        <v>-6.279454124323401</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.336830456895996</v>
+        <v>-2.268980690371222</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.558256860228234</v>
+        <v>-3.225829788679597</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.757531364716421</v>
+        <v>-1.690383750790566</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-6.271791846202014</v>
+        <v>-6.234618956125608</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.756294714953484</v>
+        <v>-2.25067293020377</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.321167883211764</v>
+        <v>-3.826101869319317</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-7.024694726789001</v>
+        <v>-6.551386958983059</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-4.647820347968199</v>
+        <v>-4.158658796073858</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-3.731330549002458</v>
+        <v>-3.230616728745943</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-3.077385918233745</v>
+        <v>-2.571168572507815</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-4.262389550518634</v>
+        <v>-3.7672820953198</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.878504194038044</v>
+        <v>-2.372526113249116</v>
       </c>
     </row>
     <row r="25">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.00184885380795</v>
+        <v>-4.637964129320636</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-9.411795261146381</v>
+        <v>-8.991199857643096</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.43025662264229</v>
+        <v>-3.05734866203256</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.844068234882627</v>
+        <v>-6.452001743858652</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.534421705213191</v>
+        <v>-6.117291716298958</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.672786481215603</v>
+        <v>-5.260430906183792</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.420042423470804</v>
+        <v>-4.020120744641552</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.672539923229394</v>
+        <v>-2.285770405917532</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.742603987941358</v>
+        <v>0.4366584932689079</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.343507479524092</v>
+        <v>3.014579158522025</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.943677943677947</v>
+        <v>3.289547614817941</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.340173458214906</v>
+        <v>3.01034380430292</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.891025135923179</v>
+        <v>2.557833706576211</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.723652786644912</v>
+        <v>7.026774543365349</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.713172916206759</v>
+        <v>4.363074581838895</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.957050134464858</v>
+        <v>3.617551352450761</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>7.201290607595269</v>
+        <v>6.839338913459628</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>7.096271453935607</v>
+        <v>6.734498209638602</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.961101288204169</v>
+        <v>5.608107711368369</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>4.121167618100287</v>
+        <v>3.781530702544458</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.253479078142938</v>
+        <v>3.910125474175665</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.853172377288139</v>
+        <v>4.505420452363815</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.749644381223398</v>
+        <v>1.424190466859358</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.3533513039216487</v>
+        <v>-0.6650646051557842</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>141</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.196058905952675</v>
+        <v>5.215874198098859</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.541813790294391</v>
+        <v>5.59118261318276</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.103475832638594</v>
+        <v>4.15494915089559</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.387486288693893</v>
+        <v>3.440011146181909</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.607291842000315</v>
+        <v>1.689407006998579</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.502012159534459</v>
+        <v>2.583879225677464</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3914193892006992</v>
+        <v>-0.3084051721596737</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.456227702926327</v>
+        <v>1.539671052846778</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.498742984803158</v>
+        <v>1.582150227396987</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.817670382339116</v>
+        <v>-2.728494010074563</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.966423647274631</v>
+        <v>-3.868652838967591</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-5.664043524725628</v>
+        <v>-5.563406300214204</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.661207948224877</v>
+        <v>-4.562661479635963</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.882634351557037</v>
+        <v>-4.784137153136712</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-4.123323154331956</v>
+        <v>-4.029837241939923</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-5.65575415919065</v>
+        <v>-5.56898774983889</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.953012631814197</v>
+        <v>-2.866025454192091</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-3.05803178547378</v>
+        <v>-2.970866158013195</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.7141910253862562</v>
+        <v>-0.6273152026211051</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.8913420478490295</v>
+        <v>0.9779703236591359</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.779681742251761</v>
+        <v>-1.692235418774892</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.146444260626382</v>
+        <v>-1.058861522028053</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.5468458379991716</v>
+        <v>0.6340529067659801</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.9475625364307589</v>
+        <v>-0.860219062769275</v>
       </c>
     </row>
     <row r="27">
@@ -2347,76 +2347,76 @@
         <v>125</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.537052771421855</v>
+        <v>1.556868063568039</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.612542135536387</v>
+        <v>-3.563173312648019</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.454240184346652</v>
+        <v>-3.402766866089657</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.362988963904094</v>
+        <v>-7.310464106416077</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.727052387527131</v>
+        <v>-7.644937222528867</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-12.32852780717047</v>
+        <v>-12.24666074102746</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.308981868059377</v>
+        <v>-8.225967651018351</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-6.988143064954684</v>
+        <v>-6.904699715034234</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.34924816527159</v>
+        <v>-5.265840922677761</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.136100713445195</v>
+        <v>-2.0462497221137</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5328671328670396</v>
+        <v>0.6239990713545822</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2536869717283494</v>
+        <v>0.3449861966197219</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.528862973760852</v>
+        <v>1.616168982061588</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.107436570428611</v>
+        <v>2.192590290044826</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.9516919486580733</v>
+        <v>-0.8601913716690106</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.156463379048688</v>
+        <v>-1.069696969696928</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-4.490601284296602</v>
+        <v>-4.403614106674496</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-6.995620437956298</v>
+        <v>-6.908454810495712</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-5.179439252336358</v>
+        <v>-5.092563429571207</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-4.192345895413474</v>
+        <v>-4.105717619603368</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.135710111046222</v>
+        <v>-3.048263787569354</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.211692487576734</v>
+        <v>-3.124109748978405</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.5368421052631618</v>
+        <v>-0.4496350364963533</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.58718923661889</v>
+        <v>2.674532710280374</v>
       </c>
     </row>
     <row r="28">
@@ -2429,76 +2429,76 @@
         <v>133</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-10.02060244423258</v>
+        <v>-10.0007871520864</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-9.629087593665503</v>
+        <v>-9.579718770777134</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.568694435967494</v>
+        <v>-6.517221117710498</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.034544141306355</v>
+        <v>-7.982019283818339</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.897429800067137</v>
+        <v>-9.815314635068873</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.708760594025726</v>
+        <v>-9.626893527882721</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-11.22751716085222</v>
+        <v>-11.1445029438112</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.753847880330547</v>
+        <v>-7.670404530410096</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.21190987020853</v>
+        <v>-6.128502627614701</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.749770319018623</v>
+        <v>-7.649625147594527</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.979914822020035</v>
+        <v>-2.875776263879452</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.770373178647588</v>
+        <v>-7.652859987791913</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.1357986803744</v>
+        <v>-5.028440690032106</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.86098448220288</v>
+        <v>-6.74993428735938</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-3.760714505049009</v>
+        <v>-3.663581294811941</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-6.173004732432233</v>
+        <v>-6.086238323080472</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-9.314661434672438</v>
+        <v>-9.227674257050332</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.652763295099071</v>
+        <v>-2.565597667638485</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-4.692221207223668</v>
+        <v>-4.605345384458516</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.753248151052524</v>
+        <v>-3.666619875242418</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-3.544732667437103</v>
+        <v>-3.457286343960234</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-8.131993239456428</v>
+        <v>-8.044410500858099</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-5.601503759398497</v>
+        <v>-5.514296690631689</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-2.66995362052397</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>104</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.569920306123997</v>
+        <v>1.589735598270181</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.026498408050209</v>
+        <v>5.075867230938577</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.133806143005856</v>
+        <v>-3.08233282474886</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.882159722498614</v>
+        <v>-2.829634865010597</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.215509119832006</v>
+        <v>-4.133393954833743</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.992788495013173</v>
+        <v>-4.910921428870168</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.02062185470528277</v>
+        <v>0.06239236233574275</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.266072730566357</v>
+        <v>-1.182629380645906</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.185568144316619</v>
+        <v>-2.10216090172279</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.09560645615530206</v>
+        <v>-0.001287021163825841</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.594405594405536</v>
+        <v>5.07323285976635</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.315225433266811</v>
+        <v>4.788691861081318</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.305786050683956</v>
+        <v>0.7940568757245074</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1228211858132582</v>
+        <v>-0.3857240656187528</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.425231128264862</v>
+        <v>-0.103568041168522</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.020459697874344</v>
+        <v>1.107226107226104</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.036755130450395</v>
+        <v>-0.9497679528282887</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1802358225715963</v>
+        <v>-0.09307019511101089</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.843637670740485</v>
+        <v>4.930513493505636</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.146115643048219</v>
+        <v>2.232743918858326</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.448905273569217</v>
+        <v>5.536351597046085</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>8.257538281654043</v>
+        <v>8.345121020252371</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>5.647773279352229</v>
+        <v>5.734980348119038</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.648727698157352</v>
+        <v>3.736071171818836</v>
       </c>
     </row>
     <row r="30">
@@ -2590,243 +2590,243 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.075375038620763</v>
+        <v>-0.5090442150084797</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.435305702087405</v>
+        <v>-0.8394305713505901</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.271313965290055</v>
+        <v>2.922891736484466</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.555108573803672</v>
+        <v>2.207742496037994</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.92238717692512</v>
+        <v>-2.283052531592965</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6758156574177434</v>
+        <v>-0.01529123644793629</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.668336421694583</v>
+        <v>3.372886817087618</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.421024335948992</v>
+        <v>4.136719342611251</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.492042923066585</v>
+        <v>5.218421143966161</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.745030795703322</v>
+        <v>4.446237208264307</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.926681565856825</v>
+        <v>1.599652992105781</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.647501404718099</v>
+        <v>1.322732939494351</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.553605241802238</v>
+        <v>1.237590271074474</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.363106673521543</v>
+        <v>2.055994273733454</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.734905989486215</v>
+        <v>2.435916108360097</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.39199022919869</v>
+        <v>5.113636363636303</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.226924488899321</v>
+        <v>3.938052559992286</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.029121830085089</v>
+        <v>0.7082118561709834</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-3.909336159553</v>
+        <v>-4.284230096238026</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.753170637681421</v>
+        <v>-5.139050952936543</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-6.327462688365756</v>
+        <v>-6.723263787569245</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.372517229844775</v>
+        <v>-5.757443082311738</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.035811177428108</v>
+        <v>-3.399635036496349</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-6.204563340700695</v>
+        <v>-6.600467289719568</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 87.6</t>
+          <t>X ≈ 87.59</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.724305528348197</v>
+        <v>2.151855856413178</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.85493383771887</v>
+        <v>10.22267271225718</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.928101027904205</v>
+        <v>0.3872920877969293</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2107957200114825</v>
+        <v>-0.3289547631516001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.096194008404353</v>
+        <v>3.541344422903848</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.224013275463399</v>
+        <v>2.680081025856346</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.914251997936972</v>
+        <v>-4.390026040918691</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.189592826350406</v>
+        <v>-4.664944654165893</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.147519578905893</v>
+        <v>-4.622908667000274</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.822418206270754</v>
+        <v>-2.245098735841495</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.611813718196721</v>
+        <v>-3.022561508330291</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.763334304867449</v>
+        <v>-1.19881488772792</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7604987283666844</v>
+        <v>-0.2249689830433184</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.109584706167013</v>
+        <v>-2.546348662536502</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.550435710916389</v>
+        <v>2.041179266254751</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-2.109654868410423</v>
+        <v>-1.574960127591645</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.9476965880438826</v>
+        <v>1.449017472272871</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.906507221618206</v>
+        <v>2.396808347399173</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.058858620004067</v>
+        <v>1.560068149376157</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-4.073196959243127</v>
+        <v>-3.516243935392772</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-6.744220749344009</v>
+        <v>-6.164053261253542</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-6.820203125874635</v>
+        <v>-6.239899222662643</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-5.481522956326963</v>
+        <v>-4.912792931233163</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2383426782747478</v>
+        <v>0.2745327102802833</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 90.82</t>
+          <t>X ≈ 90.81</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>104</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1980226962799421</v>
+        <v>0.2178379884261261</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.669777747775932</v>
+        <v>3.7191465706643</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.072331169334802</v>
+        <v>6.123804487591798</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.268835060531629</v>
+        <v>7.321359918019645</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.078668760521175</v>
+        <v>3.160783925519439</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.101968426061809</v>
+        <v>7.183835492204814</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.336405831696801</v>
+        <v>6.419420048737827</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.105335494287701</v>
+        <v>5.188778844208151</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.022039508864232</v>
+        <v>8.105446751458061</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.281509780635872</v>
+        <v>6.373509730274534</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.479020979021016</v>
+        <v>8.561845442518781</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.08445620249758</v>
+        <v>11.16016007451177</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>9.959632204530152</v>
+        <v>10.03040642228526</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.776667339659433</v>
+        <v>8.85218951079753</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.117538820572719</v>
+        <v>8.20514687759087</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.712767390182044</v>
+        <v>8.799533799533805</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>9.540167946472678</v>
+        <v>9.627155124094784</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>13.28130263896686</v>
+        <v>13.36846826642744</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>13.49748382458657</v>
+        <v>13.58435964735173</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>16.56919256612506</v>
+        <v>16.65582084193517</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>15.0642898889538</v>
+        <v>15.15173621243067</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>14.9883075124233</v>
+        <v>15.07589025102163</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.34008097165989</v>
+        <v>13.4272880404267</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>14.22565077508045</v>
+        <v>14.31299424874194</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>109</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.702456165305342</v>
+        <v>8.722271457451527</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.338125836213344</v>
+        <v>8.387494659101712</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.912901614958756</v>
+        <v>6.964374933215751</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2021499816471817</v>
+        <v>-0.1496251241591651</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.754031780889214</v>
+        <v>6.836146945887478</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.205238248676643</v>
+        <v>4.287105314819648</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.009183240376991</v>
+        <v>8.092197457418017</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.48144980305471</v>
+        <v>10.56489315297516</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.606713537104305</v>
+        <v>9.690120779698134</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.913478729118651</v>
+        <v>8.005202497939891</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.187913004426775</v>
+        <v>8.270748241161847</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.908732843287993</v>
+        <v>7.991998837713851</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.031615267338921</v>
+        <v>4.117929630547444</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.562482441988344</v>
+        <v>6.637115520736103</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.73821630822259</v>
+        <v>7.825824365240742</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>8.333444877832015</v>
+        <v>8.420211287183776</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.281875779923638</v>
+        <v>7.368862957545744</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.094287818924535</v>
+        <v>8.18145344638512</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.310469004544309</v>
+        <v>8.39734482730946</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.662699976146264</v>
+        <v>6.749328251956371</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>5.201904567852914</v>
+        <v>5.289350891329782</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.208490998661809</v>
+        <v>4.296073737260137</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.318203766296485</v>
+        <v>6.405410835063293</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.324803915517975</v>
+        <v>5.412147389179459</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>99</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.35738792016447</v>
+        <v>4.377203212310654</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04734644933156318</v>
+        <v>0.002022373556805235</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.521196553396912</v>
+        <v>3.572669871653908</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.823268933878033</v>
+        <v>3.87579379136605</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.464283467908103</v>
+        <v>6.546398632906367</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.643667975800227</v>
+        <v>7.725535041943232</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.882944384153326</v>
+        <v>9.965958601194352</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.570295080204396</v>
+        <v>8.653738430124847</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.63799731870159</v>
+        <v>10.72140456129542</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.54530154442767</v>
+        <v>9.942511956205081</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.789432789432794</v>
+        <v>7.210176284279392</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.510252628294012</v>
+        <v>6.931426880831395</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.334923579821535</v>
+        <v>0.7816674796856091</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.133699196691332</v>
+        <v>2.586767552494898</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>4.494772697806539</v>
+        <v>4.58238075482469</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.090001267415921</v>
+        <v>5.176767676767682</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-1.104742698437974</v>
+        <v>-1.017755520815868</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.219862862198632</v>
+        <v>-2.132697234738046</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.02662135372416</v>
+        <v>1.113497176489311</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.233916730849252</v>
+        <v>3.320545006659358</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.720855545519491</v>
+        <v>5.808301868996359</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.64487316898893</v>
+        <v>5.732455907587259</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.889420520999451</v>
+        <v>2.97662758976626</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.803350852780504</v>
+        <v>1.890694326441988</v>
       </c>
     </row>
   </sheetData>
@@ -3180,165 +3180,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 5.511</t>
+          <t>X &gt; 5.514</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3343</v>
+        <v>3348</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0956000169863529</v>
+        <v>-0.09590495976836877</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02796450287222996</v>
+        <v>-0.02903637468979525</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2332494538616814</v>
+        <v>-0.2340644508691696</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2171830925755245</v>
+        <v>-0.2180459113719095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1792438432620855</v>
+        <v>-0.1808311712465098</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2727896717356444</v>
+        <v>-0.2742329125758829</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.314907977160594</v>
+        <v>-0.3163149728840224</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.249155736635764</v>
+        <v>-0.2506705748969935</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2799493416741825</v>
+        <v>-0.2814180314537609</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2029314558160422</v>
+        <v>-0.2045411208804921</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2390041424606295</v>
+        <v>-0.24055215150387</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3519762175413987</v>
+        <v>-0.3533663174233652</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2371477596916591</v>
+        <v>-0.2387468024594881</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2321995763055682</v>
+        <v>-0.2338143284250975</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1874914713311426</v>
+        <v>-0.1891955985211027</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2010470854050368</v>
+        <v>-0.2027124643334375</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2279147171323643</v>
+        <v>-0.2295455522780259</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1957398765946152</v>
+        <v>-0.1974232064407602</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1409685235431368</v>
+        <v>-0.1427274617812557</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.2348914586042881</v>
+        <v>-0.2365052091020772</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2823927171429972</v>
+        <v>-0.2839546261249595</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.2209600511043845</v>
+        <v>-0.2226172116649749</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.197368421052623</v>
+        <v>-0.1990527731341558</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2555268866237057</v>
+        <v>-0.2571279826706316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 8.73</t>
+          <t>X &gt; 8.732</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3294</v>
+        <v>3298</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1764995096505473</v>
+        <v>-0.1910128259959976</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.178838888516303</v>
+        <v>-0.1781555573514026</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2750136840184751</v>
+        <v>-0.2734560449249273</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2177575153770945</v>
+        <v>-0.2158611539587696</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1435364342261778</v>
+        <v>-0.1124628675840853</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4225254213413194</v>
+        <v>-0.4081512817883635</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3630125664283241</v>
+        <v>-0.3656203276696672</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2920709828032813</v>
+        <v>-0.2948028799595761</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3239706216869678</v>
+        <v>-0.326653827077358</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2038592500914405</v>
+        <v>-0.206768343576897</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2143802960499883</v>
+        <v>-0.2172601234790363</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2340588679085656</v>
+        <v>-0.2369262368594178</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1609675347136417</v>
+        <v>-0.164009496397945</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.09201847044323586</v>
+        <v>-0.09517880445844185</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.006325504079072175</v>
+        <v>-0.009653894663848916</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.0593412948318246</v>
+        <v>-0.06255843370180258</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1148437085389773</v>
+        <v>-0.1179862700632412</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05024305086921288</v>
+        <v>-0.05349113010821327</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.05851748156628389</v>
+        <v>-0.06174296332849138</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1566771056044658</v>
+        <v>-0.1597454815051478</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1359528294927728</v>
+        <v>-0.1390847509137458</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1027395285479074</v>
+        <v>-0.1059279307965895</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08292589396990024</v>
+        <v>-0.08613094434721802</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2499692333264676</v>
+        <v>-0.2348669258627396</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3232</v>
+        <v>3236</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.00137581271221876</v>
+        <v>-0.01676848935334618</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06479816323882659</v>
+        <v>0.06431464428580824</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.008438456477591672</v>
+        <v>0.02581616641526097</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.07330824192685981</v>
+        <v>-0.05527819759335273</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1324204591220308</v>
+        <v>0.1796789678614203</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1553800533778116</v>
+        <v>-0.1253597660903978</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.07989155679935322</v>
+        <v>-0.06705014739772963</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.09458064302105385</v>
+        <v>-0.09925913212620685</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1278218503594459</v>
+        <v>-0.1324485659410541</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05219888358121949</v>
+        <v>-0.05700988947062768</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.06811930363102192</v>
+        <v>-0.07288561203630195</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1136272435044603</v>
+        <v>-0.1183498970621102</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07928014776897641</v>
+        <v>-0.08415337144712254</v>
       </c>
       <c r="P8" s="4" t="n">
+        <v>-0.009760680319416792</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0.02836603131844129</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>-0.06772409670066537</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>-0.05998166757483858</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>-0.02307541506070976</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>-0.004751025992156599</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>0.0334932365270717</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>-0.06279249297278255</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>-0.05502376731075742</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>-0.01804861219161324</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0.0002888069960533812</v>
-      </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1342315213793768</v>
+        <v>-0.1390509529366071</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1336074518006569</v>
+        <v>-0.1384768162818659</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.06736833044713109</v>
+        <v>-0.07234940308588023</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1143173527879071</v>
+        <v>-0.1192056265488688</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3140483871434867</v>
+        <v>-0.3002509732795673</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3153</v>
+        <v>3157</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1685213322094299</v>
+        <v>0.1520392573580835</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1012612502705323</v>
+        <v>-0.1028279420084814</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.06592689773451355</v>
+        <v>0.08242003131321241</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1892101101268793</v>
+        <v>-0.1719656002933192</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06224604192773597</v>
+        <v>0.1086809367339328</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2689602571386303</v>
+        <v>-0.2401234413035738</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.07768615564561543</v>
+        <v>-0.06659465907353734</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.0857924220369668</v>
+        <v>-0.09267877952784431</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.08932021194838313</v>
+        <v>-0.09620014029415103</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.05565431868863158</v>
+        <v>-0.062686332233163</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.07882323048199424</v>
+        <v>-0.08578936402793857</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1185001332021187</v>
+        <v>-0.1254421562789432</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1500494511521211</v>
+        <v>-0.157083939835033</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.03652294886288132</v>
+        <v>-0.04376819115444874</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.08241118326216679</v>
+        <v>0.07489273501828819</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.094438062593035</v>
+        <v>-0.1016085020824349</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.2097529145592887</v>
+        <v>-0.2167620207073071</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2326058717750854</v>
+        <v>-0.2395961320258166</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1876115678258401</v>
+        <v>-0.1946507160988062</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2668706102422718</v>
+        <v>-0.2737657056519822</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2209716007450595</v>
+        <v>-0.2280106230123451</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.08778633665725977</v>
+        <v>-0.09504991991857281</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1745205067855196</v>
+        <v>-0.1816173037541091</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2822049911007412</v>
+        <v>-0.2702883223455359</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3068</v>
+        <v>3072</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1929645374270308</v>
+        <v>0.1754530159341314</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1065989522867241</v>
+        <v>-0.1095611489218697</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1372153271478496</v>
+        <v>0.1527000812584234</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.04047590317922811</v>
+        <v>-0.02429850178351245</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.00118759606802854</v>
+        <v>0.04667990471016736</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2794925467868197</v>
+        <v>-0.2521052045292436</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.003208569068789302</v>
+        <v>0.01221554163222294</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06745919894090235</v>
+        <v>0.05783829377033811</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.09518511113621742</v>
+        <v>0.08552029903752612</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1836519422717515</v>
+        <v>0.1737094883647643</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0549450549450512</v>
+        <v>0.04525072513862938</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.01055466516674386</v>
+        <v>-0.02019511119767259</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.0443663959596563</v>
+        <v>-0.05414488336045764</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.01344892011996279</v>
+        <v>0.003533773234565274</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.1213899759192643</v>
+        <v>0.1111838785645176</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.05329271851224604</v>
+        <v>0.0432900432900496</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.09398449834989719</v>
+        <v>-0.1037764970609274</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.04944406307824067</v>
+        <v>-0.0593320034780831</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.009126752336449329</v>
+        <v>-0.01905026740035254</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.03057448544919339</v>
+        <v>-0.04043803572810845</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.06428988895383014</v>
+        <v>0.05417523682093872</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.1056095652091926</v>
+        <v>0.09540879363707688</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.0562684416386432</v>
+        <v>-0.06616611361967983</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2300206721164386</v>
+        <v>-0.2202589563862887</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2981</v>
+        <v>2985</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2573102519743671</v>
+        <v>0.2745144327193216</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1737089734163959</v>
+        <v>-0.1602290434045699</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.08673433780251827</v>
+        <v>0.1011854297237136</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.06041560233172305</v>
+        <v>-0.02659698025550483</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09325588786938965</v>
+        <v>0.1564855048497691</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2865745236422725</v>
+        <v>-0.223403927592372</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.02677298952037432</v>
+        <v>0.07166972929754678</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1343664429817153</v>
+        <v>0.1602472141876845</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.09493593963146907</v>
+        <v>0.1017010516542243</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.008065456089390466</v>
+        <v>0.01503814255072911</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.03463793139703597</v>
+        <v>0.02225322167061705</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.04218964552514137</v>
+        <v>0.02972510733473399</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.06017079420964677</v>
+        <v>-0.07271218490253517</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.02768048642748511</v>
+        <v>-0.040331245144543</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.1360296973773529</v>
+        <v>0.1229568565230323</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1155580399606393</v>
+        <v>0.10263847968492</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.1994730619999316</v>
+        <v>-0.211902876727919</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1506103910707495</v>
+        <v>-0.1631522361057876</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.04845097762958517</v>
+        <v>-0.06112530248100256</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1430161367002469</v>
+        <v>-0.1555001555684754</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.06309864607801785</v>
+        <v>-0.07584076213422719</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.01513514488470236</v>
+        <v>0.002237756880319353</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1259732693020723</v>
+        <v>-0.1385834624842985</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.1013045574099536</v>
+        <v>-0.09397650244994082</v>
       </c>
     </row>
     <row r="12">
@@ -3676,161 +3676,161 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.4026984759645487</v>
+        <v>0.4039033168606281</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.003932885164559252</v>
+        <v>0.03470311059343345</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1478313793324304</v>
+        <v>0.1801608257620941</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.01520999201350293</v>
+        <v>0.03731486547451368</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.01767444041458077</v>
+        <v>0.08031227171512256</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4496066242710697</v>
+        <v>-0.3869915146392913</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.002627548421109793</v>
+        <v>0.04629396124996532</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.05391906720916495</v>
+        <v>0.07799987186879775</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1497399232823895</v>
+        <v>0.1539223154914851</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.01641836980459743</v>
+        <v>0.02084061001267656</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0003619568836938925</v>
+        <v>-0.01512386081197548</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.05182297448983064</v>
+        <v>0.03616389162787215</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.05152376657054702</v>
+        <v>-0.06731604370726529</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.04524045893226258</v>
+        <v>-0.06111300785250506</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.249137353346029</v>
+        <v>0.2325701269871558</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2430526942316078</v>
+        <v>0.226645335340983</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.03978240045975667</v>
+        <v>0.04429752604906412</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1421604123721707</v>
+        <v>0.1672357972391865</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1715980920618918</v>
+        <v>0.1965557414131496</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.03345832457970488</v>
+        <v>0.05848417721774268</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1680961173275293</v>
+        <v>0.1932156455451093</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.2305220452952454</v>
+        <v>0.2556344611840515</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1108560601920203</v>
+        <v>0.1153148425219754</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.03488740207406948</v>
+        <v>0.06014820129005471</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 28.04</t>
+          <t>X &gt; 28.05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2773</v>
+        <v>2776</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4671193603945625</v>
+        <v>0.4869346525407465</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2463640492494505</v>
+        <v>0.295732872137819</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.385565702265481</v>
+        <v>0.4370390205224766</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1381789519190662</v>
+        <v>0.1907038094070828</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2035232257021846</v>
+        <v>0.2856383907004485</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2194563156194036</v>
+        <v>-0.1375892494763988</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1407109849664536</v>
+        <v>0.2031684557215385</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3136764041560056</v>
+        <v>0.3556820648090948</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3400084253949629</v>
+        <v>0.361275492237084</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1618117216855239</v>
+        <v>0.1626598879881058</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1695445870203187</v>
+        <v>0.1495694942562693</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1990107127355429</v>
+        <v>0.1788748555269635</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.06675430157670093</v>
+        <v>0.04646012146765344</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.190661912401346</v>
+        <v>0.1700565313448408</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.4172673599482977</v>
+        <v>0.3960167553765714</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3138536238331184</v>
+        <v>0.2929783269589095</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.143692663830258</v>
+        <v>0.1445873321744813</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.3628810029659775</v>
+        <v>0.385104023617366</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2188316410353153</v>
+        <v>0.2626561528621068</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1391856361181567</v>
+        <v>0.1829392043074165</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.3022134650172745</v>
+        <v>0.3462607081079341</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.2622801151629943</v>
+        <v>0.3064378014538747</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.2343082733881232</v>
+        <v>0.2567050211405402</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1583396152701724</v>
+        <v>0.1808727679172648</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6357728664668798</v>
+        <v>0.6555881586130639</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.08382527658687877</v>
+        <v>0.1331940994752472</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5949212443823839</v>
+        <v>0.6463945626393794</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1811033029694187</v>
+        <v>0.2336281604574353</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4160977574334765</v>
+        <v>0.4982129224317404</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.109633548608258</v>
+        <v>-0.02776648246525326</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2804976334889204</v>
+        <v>0.3635118505299459</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4363206000760584</v>
+        <v>0.4980583795104607</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4995657613960063</v>
+        <v>0.5395455614251645</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3482901077468199</v>
+        <v>0.3670051199102389</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3064860731151597</v>
+        <v>0.3033536926537792</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3875215581945142</v>
+        <v>0.3623153586241656</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1496978740994095</v>
+        <v>0.1244475916965015</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2516051182089853</v>
+        <v>0.2260533976792374</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.367690813856008</v>
+        <v>0.341626100846895</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.4209462595054845</v>
+        <v>0.395015544395477</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1738565470287554</v>
+        <v>0.1708219835511287</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.3323916102365629</v>
+        <v>0.3517181868718069</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.172066771759944</v>
+        <v>0.2139828458237361</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.1180119200291827</v>
+        <v>0.159845045056116</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2752921496923406</v>
+        <v>0.3173988630331124</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.1993097731617794</v>
+        <v>0.2415529016240114</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.09737040415659237</v>
+        <v>0.1395215900096716</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.1344386714342676</v>
+        <v>0.1766411440153135</v>
       </c>
     </row>
     <row r="15">
@@ -3922,79 +3922,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.031766616503873</v>
+        <v>1.051581908650057</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.002910715742707737</v>
+        <v>0.04645810714566068</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8834641625706183</v>
+        <v>0.9349374808276139</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2877551338653106</v>
+        <v>0.3402799913533272</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5927213569623575</v>
+        <v>0.6748365219606214</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.0481400678641819</v>
+        <v>0.03372699827882286</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5194581036565893</v>
+        <v>0.6024723206976148</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.658036398714934</v>
+        <v>0.718582642506064</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7224748659925595</v>
+        <v>0.7600698244207678</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7609200269233867</v>
+        <v>0.7757976815072993</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7031672908450162</v>
+        <v>0.6949677337638605</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7632088998200217</v>
+        <v>0.7316757435650771</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4126574401641037</v>
+        <v>0.3812132330775313</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6102440041969928</v>
+        <v>0.5782740862878768</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.5286877981773301</v>
+        <v>0.4965161873178019</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6334851765507992</v>
+        <v>0.6013930776963932</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.5389198870528844</v>
+        <v>0.530720148560647</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.7109090436425234</v>
+        <v>0.7263277982000247</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.4917914560133738</v>
+        <v>0.5311613628367624</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1088417530426753</v>
+        <v>0.1483963044473597</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.3176548929126568</v>
+        <v>0.381257383780131</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.2020842345135279</v>
+        <v>0.2658388066211259</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.1998166437471411</v>
+        <v>0.2633052088538719</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.2426128312348865</v>
+        <v>0.3061908028802875</v>
       </c>
     </row>
     <row r="16">
@@ -4007,76 +4007,76 @@
         <v>2403</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8584089045379315</v>
+        <v>0.8782241966841156</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.07948487727014708</v>
+        <v>0.1288537001585155</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8781673030197865</v>
+        <v>0.929640621276782</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2056211141635984</v>
+        <v>0.258145971651615</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3792121417346053</v>
+        <v>0.4613273067328691</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2213015998467469</v>
+        <v>-0.1394345337037421</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3323023995273928</v>
+        <v>0.4153166165684183</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.5337375940090254</v>
+        <v>0.5931582398087087</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5578097472915502</v>
+        <v>0.593186051905839</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5549874445245422</v>
+        <v>0.5665390325857658</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5630996910066699</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.557467611528935</v>
+        <v>0.5203899014821118</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2051722006936032</v>
+        <v>0.1681038568376252</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3411164041085328</v>
+        <v>0.3036029744053295</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1228504806264183</v>
+        <v>0.08535570985443286</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2021716604851846</v>
+        <v>0.1648545253196403</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2761069970184664</v>
+        <v>0.2634403179204909</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4207757334961357</v>
+        <v>0.4328585727130232</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.05435184212880273</v>
+        <v>0.0916361546282829</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2995452295790031</v>
+        <v>-0.2374979856598429</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.0106164780873641</v>
+        <v>0.07682984538950421</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2114427996865942</v>
+        <v>-0.1238600610882656</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1030510107979055</v>
+        <v>-0.01584394203109696</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.05417572384719449</v>
+        <v>0.03316774981428949</v>
       </c>
     </row>
     <row r="17">
@@ -4089,76 +4089,76 @@
         <v>2282</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7498179437668284</v>
+        <v>0.7696332359130125</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.254483247862602</v>
+        <v>0.3038520707509704</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.4737483497511903</v>
+        <v>0.5252216680081858</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1965890866518194</v>
+        <v>-0.1440642291638028</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.04938384508103866</v>
+        <v>0.1314990100793025</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5057599485689295</v>
+        <v>-0.4238928824259247</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1434846043180045</v>
+        <v>-0.06047038727697895</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.01455604075690786</v>
+        <v>0.09799939067735863</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1685404836837066</v>
+        <v>0.2268228171335593</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.206334955461088</v>
+        <v>0.2399333419704277</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3751058735754853</v>
+        <v>0.3829886173201231</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1651480390949303</v>
+        <v>0.1479073361428718</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1026468730661918</v>
+        <v>-0.1455604075691426</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.07925344708443305</v>
+        <v>-0.122410668327646</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.2743375903576322</v>
+        <v>-0.31758039513646</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.178724553457144</v>
+        <v>-0.2217739264088152</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.09375641137805246</v>
+        <v>-0.1110506771031439</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1079729012199522</v>
+        <v>0.1164904849091926</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.2455216362102419</v>
+        <v>-0.2106019584679686</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5842827928717469</v>
+        <v>-0.5234136336199171</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3388652381276742</v>
+        <v>-0.2514189146508059</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.546311243054376</v>
+        <v>-0.4587285044560474</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.446745698602335</v>
+        <v>-0.3595386298355265</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3912507283241453</v>
+        <v>-0.3039072546626613</v>
       </c>
     </row>
     <row r="18">
@@ -4171,76 +4171,76 @@
         <v>2186</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.694102756300552</v>
+        <v>0.713918048446736</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1929735215997965</v>
+        <v>0.2423423444881649</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4400364797081622</v>
+        <v>0.4915097979651577</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2739690789655995</v>
+        <v>-0.2214442214775829</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1833535069939316</v>
+        <v>-0.1012383419956677</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6345341148821575</v>
+        <v>-0.5526670487391527</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4956372456121585</v>
+        <v>-0.412623028571133</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1814825656067214</v>
+        <v>-0.09803921568627061</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.06823138303525411</v>
+        <v>-0.01095239856864794</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.005397713789029979</v>
+        <v>0.03692535904739458</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3520452150589151</v>
+        <v>0.3565846364122365</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2365101786721624</v>
+        <v>0.2146341385729897</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1303692017418072</v>
+        <v>-0.1789337650364331</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.041044252184534</v>
+        <v>-0.008130375081307761</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.04190237866726676</v>
+        <v>-0.09146864745922301</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.004378340987862828</v>
+        <v>-0.01764217517641953</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.09896870655431655</v>
+        <v>0.1040149476882775</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3141691320346354</v>
+        <v>0.346389796451362</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.06434318646270754</v>
+        <v>-0.004680484898230475</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.4719433336567462</v>
+        <v>-0.3853150578466398</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3291227368467204</v>
+        <v>-0.2416764133698521</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.450850767540139</v>
+        <v>-0.3632680289418104</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3589830018779807</v>
+        <v>-0.2717759331111722</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2977146975073666</v>
+        <v>-0.2103712238458826</v>
       </c>
     </row>
     <row r="19">
@@ -4253,76 +4253,76 @@
         <v>2055</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8495218815217527</v>
+        <v>0.8693371736679367</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2912051314792237</v>
+        <v>0.3405739543675921</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6454559808720362</v>
+        <v>0.6969292991290317</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1254368431488047</v>
+        <v>0.1779617006368213</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.05103569451708978</v>
+        <v>0.1331508595153537</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4891990990947761</v>
+        <v>-0.4073320329517713</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3893560396057509</v>
+        <v>-0.3063418225647254</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.10794906656389</v>
+        <v>0.1913924164843408</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.01670087378632701</v>
+        <v>0.03889317744850729</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.06231635270463443</v>
+        <v>0.09041979045178294</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4621531940618837</v>
+        <v>0.4614726430889746</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3570883322725678</v>
+        <v>0.3282130553538778</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1357662309315799</v>
+        <v>0.07798988277516372</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3809774264598289</v>
+        <v>0.3223466451448687</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.1889406547482153</v>
+        <v>0.1300908656415913</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.3462130199780376</v>
+        <v>0.3166070613860796</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4067223166766922</v>
+        <v>0.4061040663090409</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.6423357664233507</v>
+        <v>0.6707381890182305</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.2259135457170771</v>
+        <v>0.283701161868386</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1222729027126519</v>
+        <v>-0.03564462690254544</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.08169551250601614</v>
+        <v>0.005750810970852172</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.2550014900098247</v>
+        <v>-0.1674187514114962</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.3207837111025711</v>
+        <v>-0.2335766423357626</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2994287682472887</v>
+        <v>-0.2120852945858047</v>
       </c>
     </row>
     <row r="20">
@@ -4335,76 +4335,76 @@
         <v>1930</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8096218321479469</v>
+        <v>0.829437124294131</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2385731568027154</v>
+        <v>0.2879419796910838</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3488372093023244</v>
+        <v>0.40031052755932</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2101295896815216</v>
+        <v>-0.157604732193505</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2654328503591898</v>
+        <v>-0.183317685360926</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9050919504194681</v>
+        <v>-0.8232248842764633</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5929164673783944</v>
+        <v>-0.5099022503373689</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.006995926565338095</v>
+        <v>0.09043927648578887</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.02650061222436761</v>
+        <v>0.08024687183718981</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3167877463329205</v>
+        <v>0.340922927066849</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7249996380431227</v>
+        <v>0.7183417423553848</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7350955683104345</v>
+        <v>0.6979902717239241</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5734225592531672</v>
+        <v>0.5050607630073358</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6110635134338835</v>
+        <v>0.5733768826727612</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.314629294865199</v>
+        <v>0.308394121810629</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3917231494486728</v>
+        <v>0.4164313946922675</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4130256587086336</v>
+        <v>0.4688871879915411</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6188873340645102</v>
+        <v>0.7060529615250957</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.2651203331557781</v>
+        <v>0.3519961559209293</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1695479679522407</v>
+        <v>-0.08291969214213424</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1429639970565333</v>
+        <v>-0.05551767357966497</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.2707598450896853</v>
+        <v>-0.1831771064913568</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4104172347968387</v>
+        <v>-0.3232101660300302</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3309454784070169</v>
+        <v>-0.243602004745533</v>
       </c>
     </row>
     <row r="21">
@@ -4417,240 +4417,240 @@
         <v>1791</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.072077015357266</v>
+        <v>1.09189230750345</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2623123878242808</v>
+        <v>0.3116812107126492</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1584917387476068</v>
+        <v>0.2099650570046023</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2214380960954188</v>
+        <v>-0.1689132386074021</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.02565328420340762</v>
+        <v>0.1077684492016715</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5666424531156764</v>
+        <v>-0.4847753869726716</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.003435392581110364</v>
+        <v>0.07957882445991515</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6644719139734789</v>
+        <v>0.7479152638939297</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7383481261447358</v>
+        <v>0.7894024458086335</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8885331920071593</v>
+        <v>0.9073553666540946</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.195889999570987</v>
+        <v>1.181415008816018</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.396097686014059</v>
+        <v>1.348099903809008</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.142039969852505</v>
+        <v>1.060127146529723</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.14395248332653</v>
+        <v>1.095452163600761</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.9315017978522206</v>
+        <v>0.916964045929717</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.024217804647535</v>
+        <v>1.043409555679489</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.169253545407528</v>
+        <v>1.222278750468419</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.064234391747867</v>
+        <v>1.151400019208452</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.8337377437551154</v>
+        <v>0.9206135665202666</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.4066490794609976</v>
+        <v>0.4932773552711041</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.421632155843831</v>
+        <v>0.5090784793206993</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5131539669179617</v>
+        <v>0.6007367055162902</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.5646654324252793</v>
+        <v>0.6518725011920878</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.6003662327104564</v>
+        <v>0.6877097063719404</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.02</t>
+          <t>X &gt; 57.01</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1673</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9932755419158852</v>
+        <v>1.013090834062069</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2112841149718605</v>
+        <v>0.2606529378602289</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.0241438641283267</v>
+        <v>0.07561718238532222</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.749527565667151</v>
+        <v>-0.6970027081791343</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3392520211423431</v>
+        <v>-0.2571368561440792</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5696988340417377</v>
+        <v>-0.4878317678987329</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.08918623809114479</v>
+        <v>0.1722004551321703</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6458678561627025</v>
+        <v>0.7293112060831533</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7470570165257442</v>
+        <v>0.830464259119573</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.142014947111228</v>
+        <v>1.191200134395721</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.21291492259234</v>
+        <v>1.226596292070781</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.208140050030799</v>
+        <v>1.186510373109648</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.9799089988655467</v>
+        <v>0.9583363730793195</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8182554586534536</v>
+        <v>0.7969233677544452</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7568555707680673</v>
+        <v>0.7717370038824285</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.8141283722961603</v>
+        <v>0.8648311067665873</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.8593090564087689</v>
+        <v>0.9462962340308749</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.172699944590114</v>
+        <v>1.2598655720507</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.7911524990084402</v>
+        <v>0.8780283217735914</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.50006295097036</v>
+        <v>0.5866912267804665</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.3153359140584371</v>
+        <v>0.4027822375353054</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.4784449900084411</v>
+        <v>0.5660277286067696</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.8130682354421594</v>
+        <v>0.900275304208968</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.617553851083926</v>
+        <v>0.70489732474541</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.24</t>
+          <t>X &gt; 60.23</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1514</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6570699609346988</v>
+        <v>0.6768852530808829</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2268200537280052</v>
+        <v>0.2761888766163736</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2369272278517798</v>
+        <v>0.2884005461087753</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9385153776248742</v>
+        <v>-0.8859905201368576</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3810220640765962</v>
+        <v>-0.2989068990783323</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3256469353533546</v>
+        <v>-0.2437798692103499</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1537292140375754</v>
+        <v>0.236743431078601</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.9298018862402699</v>
+        <v>1.013245236160721</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.432762222284502</v>
+        <v>1.516169464878331</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.620965839089344</v>
+        <v>1.666127882447633</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.60481432758661</v>
+        <v>1.61058963403606</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.034664514660982</v>
+        <v>1.002242340014568</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.7684930926512905</v>
+        <v>0.7360347886495404</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6131168874696584</v>
+        <v>0.5808754903176592</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8126409443405649</v>
+        <v>0.8198211215526499</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.5492169379922274</v>
+        <v>0.5963096309631055</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.4811292308950001</v>
+        <v>0.5681164085171062</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.8384614642894945</v>
+        <v>0.92562709175008</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.4601908665539014</v>
+        <v>0.5470666893190526</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.1849328364228171</v>
+        <v>0.2715611122329236</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.03786980969358922</v>
+        <v>0.1253161331704575</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.09398782946422557</v>
+        <v>0.1815705680625541</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.2367378154766016</v>
+        <v>0.3239448842434101</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.09471895920805906</v>
+        <v>0.182062432869543</v>
       </c>
     </row>
     <row r="24">
@@ -4663,76 +4663,76 @@
         <v>1360</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.7780756721914699</v>
+        <v>0.7978909643376539</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.707215629233005</v>
+        <v>0.7565844521213734</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6610759439676528</v>
+        <v>0.7125492622246483</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.9333404731067034</v>
+        <v>-0.8808156156186868</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4916779662970114</v>
+        <v>-0.4095628012987476</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.818036682078052</v>
+        <v>-0.7361696159350473</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1237810861987825</v>
+        <v>-0.04076686915775696</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.064929766836364</v>
+        <v>1.148373116756815</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.620026056811362</v>
+        <v>1.703433299405191</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.064012886927571</v>
+        <v>2.104398767902815</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.088781901419665</v>
+        <v>2.084988123931218</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.265451677610706</v>
+        <v>1.219298148216161</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.022980620819759</v>
+        <v>0.9765469397606239</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.095671864546347</v>
+        <v>1.048938349447575</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.465955110165424</v>
+        <v>1.463082040812317</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5170660327159737</v>
+        <v>0.5596931846013433</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.5299869509975679</v>
+        <v>0.6169741286196739</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.9396736796908414</v>
+        <v>1.026839307151427</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.6411489829576666</v>
+        <v>0.7280248057228178</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.5341246928219121</v>
+        <v>0.6207529686320186</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.5789957713067651</v>
+        <v>0.6664420947836334</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.5030133947762039</v>
+        <v>0.5905961333745324</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.6308049535603715</v>
+        <v>0.71801202232718</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.7754245307365366</v>
+        <v>0.8627680043980206</v>
       </c>
     </row>
     <row r="25">
@@ -4742,79 +4742,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4617865740136935</v>
+        <v>0.5190223808584165</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5872521632890368</v>
+        <v>0.6736419936015778</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7797816801138993</v>
+        <v>0.8669443148805414</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.077081021417008</v>
+        <v>-0.9879346637791642</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.11593118922962</v>
+        <v>-0.9974608622644539</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9287169042769818</v>
+        <v>-0.8104946761670746</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3140576370245327</v>
+        <v>-0.1958201952939689</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9583221935062269</v>
+        <v>1.075723661747418</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.816172013359797</v>
+        <v>1.851305460301589</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.8257531189969</v>
+        <v>1.81248440090458</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.55805110670196</v>
+        <v>2.575940454159493</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.115338647934401</v>
+        <v>2.052492845164998</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.399345394038946</v>
+        <v>1.337161120886378</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.504983585964268</v>
+        <v>1.523912587017271</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.827048852650151</v>
+        <v>1.813467128768202</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.277551338858053</v>
+        <v>1.314616755793224</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.8981149871670695</v>
+        <v>0.9356015796000605</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.528991172836925</v>
+        <v>1.566054993425951</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.499873912013506</v>
+        <v>1.536848335134586</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.114604227235851</v>
+        <v>1.151798720266008</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.061836904489397</v>
+        <v>1.099448630731359</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.9040883791444472</v>
+        <v>0.941903322917014</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.178938761458021</v>
+        <v>1.216378035399067</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.184736252154458</v>
+        <v>1.222245128581037</v>
       </c>
     </row>
     <row r="26">
@@ -4827,76 +4827,76 @@
         <v>1075</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.213989405006814</v>
+        <v>1.233804697152998</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.96386520404851</v>
+        <v>2.013234026936878</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.359396255749168</v>
+        <v>1.410869574006163</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2831144097026765</v>
+        <v>-0.2305895522146599</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3699436577267647</v>
+        <v>-0.2878284927285009</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2755798834519396</v>
+        <v>-0.1937128173089349</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2512314312490105</v>
+        <v>0.334245648290036</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.45819902446145</v>
+        <v>1.541642374381901</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.963974867091821</v>
+        <v>2.04738210968565</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.616797169826647</v>
+        <v>1.645868476360391</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.504960156122948</v>
+        <v>2.477031182589172</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.946710227542297</v>
+        <v>1.919730247107744</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.193979252830701</v>
+        <v>1.167970222962857</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7865063378705628</v>
+        <v>0.7611903251606549</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.4297034001791</v>
+        <v>1.46007967713328</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.9086529000210319</v>
+        <v>0.9954193093727923</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.03032894826159804</v>
+        <v>0.1173161258837041</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.7625190969275195</v>
+        <v>0.8496847243881049</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.8856770267333118</v>
+        <v>0.972552849498463</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.7006773604005687</v>
+        <v>0.7873056362106752</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.6224294238375592</v>
+        <v>0.7098757473144275</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.3604005356790836</v>
+        <v>0.4479832742774121</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.100367197062418</v>
+        <v>1.187574265829227</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.396491562200282</v>
+        <v>1.483835035861766</v>
       </c>
     </row>
     <row r="27">
@@ -4909,76 +4909,76 @@
         <v>934</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.6128418679261216</v>
+        <v>0.6326571600723057</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.423725214047799</v>
+        <v>1.473094036936168</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.9451401311866405</v>
+        <v>0.9966134494436361</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8372414958631822</v>
+        <v>-0.7847166383751656</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6684342417326761</v>
+        <v>-0.5863190767344122</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6948951704552471</v>
+        <v>-0.6130281043122423</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3482483109956931</v>
+        <v>0.4312625280367186</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.458496622252085</v>
+        <v>1.541939972172536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.034207945681445</v>
+        <v>2.117615188275273</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.286240344190006</v>
+        <v>2.306237973777236</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.481903535436722</v>
+        <v>3.434998470640025</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.095656993141624</v>
+        <v>3.04941146035442</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.077899376330528</v>
+        <v>2.033087000335911</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.642340210685653</v>
+        <v>1.598332910214111</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.268008265474656</v>
+        <v>2.288857284830627</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.899639404677181</v>
+        <v>1.986405814028942</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.4807049255535603</v>
+        <v>0.5676921031756663</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.339283202300741</v>
+        <v>1.426448829761327</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.127198863295249</v>
+        <v>1.2140746860604</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.6718939332804084</v>
+        <v>0.7585222090905148</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.9850607668981581</v>
+        <v>1.072507090375026</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.5878792468986447</v>
+        <v>0.6754619854969732</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.18392877268117</v>
+        <v>1.271135841447979</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.750358401501117</v>
+        <v>1.837701875162601</v>
       </c>
     </row>
     <row r="28">
@@ -4991,76 +4991,76 @@
         <v>809</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4700404304267778</v>
+        <v>0.4898557225729618</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.201887659904443</v>
+        <v>2.251256482792812</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.624896051386465</v>
+        <v>1.67636936964346</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1710631190998768</v>
+        <v>0.2235879765878934</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4222051503863682</v>
+        <v>0.5043203153846321</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.102637684414226</v>
+        <v>1.184504750557231</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.6858920345827</v>
+        <v>1.768906251623726</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.763601641907037</v>
+        <v>2.847044991827488</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.175038617954783</v>
+        <v>3.258445860548612</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.969543968670109</v>
+        <v>2.978748433587334</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.937564289851068</v>
+        <v>3.869330887093277</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.534774734398312</v>
+        <v>3.467276921376474</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.162731947802968</v>
+        <v>2.09750572998275</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.570477361528823</v>
+        <v>1.506513166729754</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.765489757151535</v>
+        <v>2.775422281199546</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>2.371843172249164</v>
+        <v>2.458609581600925</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.248830112489614</v>
+        <v>1.33581729011172</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.627123690597564</v>
+        <v>2.71428931805815</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.101648510333511</v>
+        <v>2.188524333098663</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.423476107058811</v>
+        <v>1.510104382868917</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.621768257309832</v>
+        <v>1.7092145807867</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.174957697837364</v>
+        <v>1.262540436435692</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.449808080150937</v>
+        <v>1.537015148917746</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.621058210660919</v>
+        <v>1.708401684322403</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>676</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.534027859908576</v>
+        <v>2.55384315205476</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.529579536716277</v>
+        <v>4.578948359604645</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.236948617685393</v>
+        <v>3.288421935942388</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.785479932167974</v>
+        <v>1.83800478965599</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.452547529691572</v>
+        <v>2.534662694689835</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.229732316119133</v>
+        <v>3.311599382262138</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.226547985755545</v>
+        <v>4.30956220279657</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.832863160335435</v>
+        <v>4.916306510255886</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.021879074945488</v>
+        <v>5.105286317539317</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.078521483851468</v>
+        <v>5.069833768346491</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.298547606239907</v>
+        <v>5.196400785139687</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.759012415515336</v>
+        <v>5.655114508535341</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.598685458968042</v>
+        <v>3.499504064098105</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.229330061552957</v>
+        <v>3.130932562282787</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.049491483294545</v>
+        <v>4.042267659320153</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.053004076572577</v>
+        <v>4.139770485924338</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.327150194993393</v>
+        <v>3.4141373726155</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.66591802358225</v>
+        <v>3.753083651042836</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.438312226953492</v>
+        <v>3.525188049718643</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.441973631213848</v>
+        <v>2.528601907023955</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.638254385995253</v>
+        <v>2.725700709472122</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.006058991713211</v>
+        <v>3.093641730311539</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.837122391778266</v>
+        <v>2.924329460545074</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.465295745494636</v>
+        <v>2.55263921915612</v>
       </c>
     </row>
     <row r="30">
@@ -5155,322 +5155,322 @@
         <v>572</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.70932014241486</v>
+        <v>2.729135434561044</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.439230651019201</v>
+        <v>4.48859947390757</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.395267665083807</v>
+        <v>4.446740983340803</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.634141687561886</v>
+        <v>2.686666545049903</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.664921465968582</v>
+        <v>3.747036630966846</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.724736099961369</v>
+        <v>4.806603166104374</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.99876068402115</v>
+        <v>5.081774901062175</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.941760595044848</v>
+        <v>6.025203944965298</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.332324023902238</v>
+        <v>6.415731266496067</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.019272018398155</v>
+        <v>5.991855730075628</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.244755244755247</v>
+        <v>5.218794953389384</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.839700957742338</v>
+        <v>5.812645898981529</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.015576260474234</v>
+        <v>3.991403552893296</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.794149857141996</v>
+        <v>3.770324676446705</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.708447911481755</v>
+        <v>4.796055968499907</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.604375781790431</v>
+        <v>4.691142191142191</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.120587526892265</v>
+        <v>4.207574704514371</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.36521872288295</v>
+        <v>4.452384350343536</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.182798509901311</v>
+        <v>3.269674332666462</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.495765992698509</v>
+        <v>2.582394268508615</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>2.12722695189089</v>
+        <v>2.214673275367758</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.051244575360329</v>
+        <v>2.138827313958657</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.326094957673902</v>
+        <v>2.413302026440711</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.250126299555951</v>
+        <v>2.337469773217435</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 85.99</t>
+          <t>X &gt; 85.98</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.482194737278988</v>
+        <v>3.382213683213728</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.638872811548339</v>
+        <v>5.563160155304175</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.829001367989051</v>
+        <v>4.754071923883252</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.854491607634621</v>
+        <v>2.783256269220381</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.01011923093845</v>
+        <v>4.963189067113362</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.827585616731419</v>
+        <v>5.779086070820803</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.474657849169937</v>
+        <v>5.426424598670486</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.456521473218103</v>
+        <v>6.406074789137541</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.708128796072891</v>
+        <v>6.657205576922266</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.27948548913794</v>
+        <v>6.303577112625817</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.922340817077661</v>
+        <v>5.948705937177678</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.695792234886241</v>
+        <v>6.718174563079785</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.518336657971467</v>
+        <v>4.546794466873564</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.086383938849757</v>
+        <v>4.116071984556946</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.111465946078738</v>
+        <v>5.272050562141551</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>4.443536620951271</v>
+        <v>4.605933282403882</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.098872399913979</v>
+        <v>4.261932111812946</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.046484825201681</v>
+        <v>5.207511576059005</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.63108706345303</v>
+        <v>4.793150856142994</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.976075157218197</v>
+        <v>4.139660531657228</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>3.853763573164358</v>
+        <v>4.017282430918087</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.567254880844324</v>
+        <v>3.731352435895545</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.421052631578945</v>
+        <v>3.585659081150709</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.976662920829419</v>
+        <v>4.140078928767764</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 89.21</t>
+          <t>X &gt; 89.2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>381</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.669180526359021</v>
+        <v>3.688995818505205</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.351970616115189</v>
+        <v>4.401339439003557</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.791428223548039</v>
+        <v>5.842901541805034</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.506742036602013</v>
+        <v>3.55926689409003</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.235602094240832</v>
+        <v>5.317717259239096</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.469936798041637</v>
+        <v>6.551803864184642</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.791081800949605</v>
+        <v>7.874096017990631</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.083121851589347</v>
+        <v>9.166565201509798</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.386425245542718</v>
+        <v>9.469832488136547</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.525099524225652</v>
+        <v>8.435136707388011</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.274599416331711</v>
+        <v>8.185636140125858</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.782820829996069</v>
+        <v>8.692227050813983</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.820726490821301</v>
+        <v>5.736604250973578</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.86176727909011</v>
+        <v>5.777305479239033</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.990040334806466</v>
+        <v>6.077648391824617</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.06033452121374</v>
+        <v>6.1471009305655</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.876327849561719</v>
+        <v>4.963315027183825</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.82117746230626</v>
+        <v>5.908343089766845</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.512424264723911</v>
+        <v>5.599300087489063</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>5.96198481324803</v>
+        <v>6.048613089058136</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.46848936401944</v>
+        <v>6.555935687496309</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.130039795887846</v>
+        <v>6.217622534486175</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>5.61748860339825</v>
+        <v>5.704695672165059</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>5.01658556207822</v>
+        <v>5.103929035739704</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 92.43</t>
+          <t>X &gt; 92.42</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>277</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.972431119601708</v>
+        <v>4.992246411747892</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.60810079050971</v>
+        <v>4.657469613398078</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.685962857620879</v>
+        <v>5.737436175877875</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.094259457220502</v>
+        <v>2.146784314708519</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.045425439752904</v>
+        <v>6.127540604751168</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.232639724705543</v>
+        <v>6.314506790848547</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.337241731643793</v>
+        <v>8.420255948684819</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.57658676552209</v>
+        <v>10.66003011544254</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.898685594331759</v>
+        <v>9.982092836925588</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.367458128317125</v>
+        <v>9.209177160889098</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.197849082325618</v>
+        <v>8.044387882187714</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.918668921186836</v>
+        <v>7.765638478739717</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.266769110945056</v>
+        <v>4.124490800372797</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.767364368262641</v>
+        <v>4.622836384357868</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.191268340150543</v>
+        <v>5.278876397168695</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.06447524911011</v>
+        <v>5.151241658461871</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.125283192237752</v>
+        <v>3.212270369859858</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.020264038578091</v>
+        <v>3.107429666038676</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.514423563548036</v>
+        <v>2.601299386313187</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.979495259821277</v>
+        <v>2.066123535631384</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.241185195813031</v>
+        <v>3.3286315192899</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.804191988957569</v>
+        <v>2.891774727555898</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.718031540946228</v>
+        <v>2.805238609713037</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.559030391853547</v>
+        <v>1.646373865515031</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>168</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.552355345901134</v>
+        <v>2.572170638047318</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.188025016809135</v>
+        <v>2.237393839697503</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.889913306729049</v>
+        <v>4.941386624986045</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.58419177172393</v>
+        <v>3.636716629211946</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.585674896991847</v>
+        <v>5.667790061990111</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.548037110938573</v>
+        <v>7.629904177081578</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.550089205144282</v>
+        <v>8.633103422185307</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.63831253283723</v>
+        <v>10.72175588275768</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.08811984574719</v>
+        <v>10.17152708834102</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.31081380993994</v>
+        <v>9.99032738863589</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.204295704295703</v>
+        <v>7.897523125472368</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.92511554315692</v>
+        <v>7.618773722024372</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.41933916423713</v>
+        <v>4.128747749842809</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.602674665666797</v>
+        <v>3.315952897064854</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.538784241818078</v>
+        <v>3.62639229883623</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.943536620951271</v>
+        <v>3.030303030303031</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.4284463347510652</v>
+        <v>0.5154335123731713</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.271810914146684</v>
+        <v>-0.1846452866860986</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-1.246105919003114</v>
+        <v>-1.159230096237962</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-1.059012562080042</v>
+        <v>-0.9723842862699357</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.969051793715735</v>
+        <v>2.056498117192604</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.893069417185174</v>
+        <v>1.980652155783503</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.3822055137844558</v>
+        <v>0.4694125825512643</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.8842393348096778</v>
+        <v>-0.7968958611481938</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03747399978104227</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.395297120402311</v>
+        <v>5.44466594329068</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.853724300640373</v>
+        <v>6.905197618897368</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.241168017328931</v>
+        <v>3.293692874816948</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.325062599590261</v>
+        <v>4.407177764588525</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.410827609180565</v>
+        <v>7.49269467532357</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.637731774392194</v>
+        <v>6.720745991433219</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.6054680083539</v>
+        <v>13.68891135827435</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.299165210638698</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.97437488654451</v>
+        <v>10.05893213951489</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.799533799533791</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>8.520353638395008</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.844805002746455</v>
+        <v>8.931080311372703</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>4.275552512457679</v>
+        <v>4.362175347969576</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.167148631052029</v>
+        <v>2.254756688070181</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.136173523976268</v>
+        <v>-0.04940711462450764</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.628239295413593</v>
+        <v>2.715226473035699</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.523220141753932</v>
+        <v>2.610385769214517</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-4.506975484220504</v>
+        <v>-4.420099661455353</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-7.21843285193512</v>
+        <v>-7.131804576125013</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-3.413970980611388</v>
+        <v>-3.32652465713452</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-3.48995335714195</v>
+        <v>-3.402370618543621</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-3.215102974828376</v>
+        <v>-3.127895906061568</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-4.740346995265163</v>
+        <v>-4.653003521603679</v>
       </c>
     </row>
   </sheetData>
@@ -5824,165 +5824,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 5.511</t>
+          <t>X &lt; 5.514</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.86107672485663</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.4018043288730411</v>
+        <v>-0.3524355059846727</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.302999662959209</v>
+        <v>8.354472981216205</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.139718741966611</v>
+        <v>6.192243599454628</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.325062599590261</v>
+        <v>4.407177764588525</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.860102971499416</v>
+        <v>8.94197003764242</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.98555786134873</v>
+        <v>11.06857207838976</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.808366559078543</v>
+        <v>7.891809908998994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.299165210638698</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.626548799587972</v>
+        <v>5.711106052558357</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.350258437214961</v>
+        <v>7.43444105703913</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.86817972535154</v>
+        <v>12.95279310286649</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.395529640427597</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.065699355689716</v>
+        <v>5.153307412707868</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.660927925299099</v>
+        <v>5.747694334650859</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>6.976065382370109</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.421770866391618</v>
+        <v>5.508936493852204</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.739401327373692</v>
+        <v>2.826277150138843</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.274320771253279</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>9.629507280258174</v>
+        <v>9.716953603735043</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.654974179089926</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.48054919908467</v>
+        <v>5.567756267851479</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.303131265604407</v>
+        <v>8.39047473926589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 8.73</t>
+          <t>X &lt; 8.732</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.839337594421842</v>
+        <v>4.210392555989515</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.958200542640782</v>
+        <v>3.8756157576397</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.879421536056284</v>
+        <v>5.74338183257565</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.484743708474959</v>
+        <v>3.377535251149446</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.438690659509881</v>
+        <v>0.5624059356269626</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.18893015454654</v>
+        <v>8.724578733294592</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.57549818530439</v>
+        <v>7.658512402345416</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.616185338764325</v>
+        <v>5.699628688684776</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.498044762459429</v>
+        <v>6.581452005053258</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.202970672685048</v>
+        <v>3.287527925655432</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.477404947993186</v>
+        <v>3.561587567817355</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.038560921308182</v>
+        <v>4.123174298823137</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.073400788886993</v>
+        <v>2.159676097513241</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1713021166471904</v>
+        <v>0.2579249521590867</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.16849867134718</v>
+        <v>-2.080890614329029</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.7329339672840192</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.813600396375719</v>
+        <v>0.9005875739978251</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.9720910261914995</v>
+        <v>-0.884925398730914</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.7559098405717393</v>
+        <v>-0.6690340178065881</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.952191919712675</v>
+        <v>2.038820195522781</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.408827704079883</v>
+        <v>1.496274027556751</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.4925091930955361</v>
+        <v>0.5800919316938646</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.07297655904466893</v>
+        <v>0.01423050972213957</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>4.593968897635833</v>
+        <v>4.140078928767764</v>
       </c>
     </row>
     <row r="8">
@@ -5992,79 +5992,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.6551979247038275</v>
+        <v>-0.3799775482145691</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.827190536867946</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.321469870229997</v>
+        <v>-1.609295134725819</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3780168653678402</v>
+        <v>-0.6918143715598575</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.058314772497184</v>
+        <v>-4.831952670194099</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.101275203063189</v>
+        <v>0.5551798261907663</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2243068195704865</v>
+        <v>-0.453963357189167</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.04953879064231614</v>
+        <v>0.1329821405627669</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.6435482677289457</v>
+        <v>0.7269555103227745</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6830036065294038</v>
+        <v>-0.5984463535590194</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.4085693312212655</v>
+        <v>-0.3243867113970964</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4172228833305525</v>
+        <v>0.5018362608455078</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1551149267915406</v>
+        <v>-0.06883961816529194</v>
       </c>
       <c r="P8" s="4" t="n">
+        <v>-1.394890870302497</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>-2.053034167883055</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>-0.3536748702494492</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>-0.4875920072269224</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>-1.144918898893422</v>
+      </c>
+      <c r="U8" s="4" t="n">
         <v>-1.481513705814393</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>-2.140642224901207</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>-0.4404412796012096</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>-0.5745791848490285</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>-1.232084526354008</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>-1.568389528579544</v>
-      </c>
       <c r="V8" s="4" t="n">
-        <v>0.8286485797247423</v>
+        <v>0.9152768555348487</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.837770551937254</v>
+        <v>0.9252168754141223</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.3431842002839076</v>
+        <v>-0.2556014616855791</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.4841523698749626</v>
+        <v>0.5713594386417711</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>4.076078125507777</v>
+        <v>3.810444312490326</v>
       </c>
     </row>
     <row r="9">
@@ -6074,79 +6074,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.515624237639223</v>
+        <v>-2.310048634344518</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7642792959811899</v>
+        <v>0.7772277992448338</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.618962432915922</v>
+        <v>-1.801475660432544</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.128570469948777</v>
+        <v>0.9076235520638747</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.929118002416438</v>
+        <v>-2.469992015540434</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.104250128690055</v>
+        <v>1.73984590886711</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.207307244559864</v>
+        <v>-0.3423891076838785</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1013324375769784</v>
+        <v>-0.01788908765652764</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05980914833565265</v>
+        <v>0.02359809425817616</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4492594501333187</v>
+        <v>-0.3647021971629343</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1748251748251803</v>
+        <v>-0.09064255500101126</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3152254332668178</v>
+        <v>0.3998388107817732</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7288629737609398</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6464095834174515</v>
+        <v>-0.5597867479055552</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-2.074768871735031</v>
+        <v>-1.98716081471688</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.05892123633588398</v>
+        <v>0.1456876456876444</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.463244869549612</v>
+        <v>1.550232047171718</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.742841100505331</v>
+        <v>1.830006727965916</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.189791516894317</v>
+        <v>1.276667339659468</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.146115643048162</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.60275142741537</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.01169248757673103</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.032388663967609</v>
+        <v>1.119595732734417</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.349351398781053</v>
+        <v>2.197609633357303</v>
       </c>
     </row>
     <row r="10">
@@ -6156,79 +6156,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.075647996356253</v>
+        <v>-1.916709182397483</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.5992847219772486</v>
+        <v>0.6220772376435093</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.84192787327266</v>
+        <v>-1.965367098743812</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5269479247000532</v>
+        <v>-0.6668268653129843</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8923287047575741</v>
+        <v>-1.289973659699342</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.613726159905212</v>
+        <v>1.361466341363759</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8985001096657683</v>
+        <v>-0.9780057887460458</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.466995759762042</v>
+        <v>-1.383552409841592</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.715327542984483</v>
+        <v>-1.631920300390654</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.489393229397528</v>
+        <v>-2.404835976427144</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.345393736698085</v>
+        <v>-1.261211116873916</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7550086804455631</v>
+        <v>-0.6703953029306078</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4305573160941378</v>
+        <v>-0.3442820074678892</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9418387918901345</v>
+        <v>-0.8552159563782382</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.890822383440721</v>
+        <v>-1.80321432642257</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.295593813831339</v>
+        <v>-1.208827404479578</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.01954364323968605</v>
+        <v>0.1065308208617921</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.3753305828837483</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.7388595421915269</v>
+        <v>-0.6519837194263758</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.5517661852684554</v>
+        <v>-0.465137909458349</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.384985473365006</v>
+        <v>-1.297539149888138</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.75082292235934</v>
+        <v>-1.663240183761012</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3165522501906963</v>
+        <v>-0.2293451814238878</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.233700864525865</v>
+        <v>1.144097927671687</v>
       </c>
     </row>
     <row r="11">
@@ -6238,79 +6238,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.055157818422188</v>
+        <v>-2.160209300220117</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9175360009620306</v>
+        <v>0.8188966361634229</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.087236094737975</v>
+        <v>-1.180233349828789</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2899763412077334</v>
+        <v>-0.5201896576010512</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.348197767916524</v>
+        <v>-1.771311937928644</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.281600556040473</v>
+        <v>0.8346704764138551</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.8803841676367838</v>
+        <v>-1.18530098507852</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.621987708232247</v>
+        <v>-1.795627478298144</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.348982937509433</v>
+        <v>-1.394948716898334</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7341597350336002</v>
+        <v>-0.7821830996322774</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.9226884226884238</v>
+        <v>-0.8385058028642547</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9703871023457182</v>
+        <v>-0.8857737248307629</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2433592484612817</v>
+        <v>-0.157083939835033</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4647856517935196</v>
+        <v>-0.3781628162816233</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.586877133843295</v>
+        <v>-1.499269076825144</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.454611527196882</v>
+        <v>-1.367845117845121</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7260653823701162</v>
+        <v>0.8130525599922223</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.3895647472289738</v>
+        <v>0.4767303746895593</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.3201799930771969</v>
+        <v>-0.2333041703120458</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3298763268088436</v>
+        <v>0.4165046026189501</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.2134878888239484</v>
+        <v>-0.1260415653470801</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.7524332283174786</v>
+        <v>-0.6648504897191501</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.216861598440552</v>
+        <v>0.3040686672073605</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.04797809972794198</v>
+        <v>-0.003245067497402943</v>
       </c>
     </row>
     <row r="12">
@@ -6320,161 +6320,161 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.436556944184552</v>
+        <v>-2.425893842403923</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2514078290097714</v>
+        <v>-0.4175714773248558</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.21180815052535</v>
+        <v>-1.379871853870931</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4973036559253501</v>
+        <v>-0.7795050477977341</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6732904965889261</v>
+        <v>-1.011259633253914</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.896981116866954</v>
+        <v>1.540021294499866</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5838946040694211</v>
+        <v>-0.8209548562561366</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8625351817019222</v>
+        <v>-0.9928781817382415</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.390271854509926</v>
+        <v>-1.412882092222006</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6463109754580856</v>
+        <v>-0.6706462531069874</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5616300208330642</v>
+        <v>-0.4774474010088952</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.8408101819718468</v>
+        <v>-0.7561968044568914</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2578542937912474</v>
+        <v>-0.1715789851649987</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2895273764403683</v>
+        <v>-0.202904540928472</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.897422498942746</v>
+        <v>-1.809814441924594</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.871453891382693</v>
+        <v>-1.784687482030932</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.7552400675665041</v>
+        <v>-0.780084694909732</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.319429961765728</v>
+        <v>-1.454185360780258</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.484201157098347</v>
+        <v>-1.617800621222152</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.7256792287467135</v>
+        <v>-0.8616948492047882</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.459519634855688</v>
+        <v>-1.593994337853935</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.805585617347717</v>
+        <v>-1.939318874453683</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.149055845721172</v>
+        <v>-1.173444560305867</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.7305927901497569</v>
+        <v>-0.8683244325767703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 28.04</t>
+          <t>X &lt; 28.05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.196871958736857</v>
+        <v>-2.264700324441137</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.247214956892371</v>
+        <v>-1.448824524339216</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.987527407354158</v>
+        <v>-2.192784065107247</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.070762704616591</v>
+        <v>-1.287887302836161</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.350704168188642</v>
+        <v>-1.693156683572013</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4750098037975548</v>
+        <v>0.1190317379170835</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.074483546518771</v>
+        <v>-1.337493407385878</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.81896263346804</v>
+        <v>-1.99327845871823</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.932718847332303</v>
+        <v>-2.020936318697281</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.153989502689456</v>
+        <v>-1.157785083269069</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.190114233592489</v>
+        <v>-1.10593161376832</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.314014891625682</v>
+        <v>-1.229401514110727</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7307643554316101</v>
+        <v>-0.6444890468053615</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.26274976497502</v>
+        <v>-1.176126929463123</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.232437290273026</v>
+        <v>-2.144829233254875</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.792488223769226</v>
+        <v>-1.705721814417466</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.059186043239009</v>
+        <v>-1.063241435866992</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.007458444186739</v>
+        <v>-2.09975915832171</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.389111639231928</v>
+        <v>-1.573308771186213</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.046012042059239</v>
+        <v>-1.231183458112582</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.745382497941648</v>
+        <v>-1.929009129184216</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.574192487576731</v>
+        <v>-1.759257493923968</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.455592105263165</v>
+        <v>-1.549946562976096</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.127364753991436</v>
+        <v>-1.223127196115882</v>
       </c>
     </row>
     <row r="14">
@@ -6484,79 +6484,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.361961106876855</v>
+        <v>-2.41504066181907</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4489199128235981</v>
+        <v>-0.6164507851667906</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.340116279069768</v>
+        <v>-2.502905574008111</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.029187026791767</v>
+        <v>-1.204317187509403</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.844763714406795</v>
+        <v>-2.117380967718482</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.01741905180266201</v>
+        <v>-0.3013952926794303</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.371221863971861</v>
+        <v>-1.650750964900048</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.911642546316401</v>
+        <v>-2.117248062015499</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.131899361787113</v>
+        <v>-2.264537498962156</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.597064524639954</v>
+        <v>-1.660143048739549</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.453520301687838</v>
+        <v>-1.443080966262947</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.732700462826621</v>
+        <v>-1.648087085311666</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8941736754537217</v>
+        <v>-0.8078983668274731</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.246490131141975</v>
+        <v>-1.159867295630079</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.643838545516751</v>
+        <v>-1.556230488498599</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.833950290043497</v>
+        <v>-1.747183880691736</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9750049540213155</v>
+        <v>-0.9648706511770655</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.527903902523143</v>
+        <v>-1.593271564422324</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.9723433259238377</v>
+        <v>-1.11560007878596</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.7852499690007662</v>
+        <v>-0.9287542688179329</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.328614184633558</v>
+        <v>-1.471300436783963</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.064324066524108</v>
+        <v>-1.20851341870317</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.7118091671867433</v>
+        <v>-0.856984117861181</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.8418345100829541</v>
+        <v>-0.986965318628954</v>
       </c>
     </row>
     <row r="15">
@@ -6566,79 +6566,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.04887152682398</v>
+        <v>-3.087749768299219</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1274426233115804</v>
+        <v>-0.2657678763443485</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.73378963469964</v>
+        <v>-2.863753825557779</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.156800409172099</v>
+        <v>-1.298628056837089</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.01936295299658</v>
+        <v>-2.240165230580558</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2051630532063484</v>
+        <v>-0.4355992422337778</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.811235231466569</v>
+        <v>-2.03623409313473</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.201857891965815</v>
+        <v>-2.364600347411262</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.384298768457974</v>
+        <v>-2.484987070576992</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.48647195767056</v>
+        <v>-2.526283632487377</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.324019765229167</v>
+        <v>-2.301965907263948</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.491217843501204</v>
+        <v>-2.406604465986248</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.488382267000539</v>
+        <v>-1.40210695837429</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.045754918932992</v>
+        <v>-1.959132083421096</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.809026775085883</v>
+        <v>-1.721418718067731</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.109654868410423</v>
+        <v>-2.022888459058663</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.843067652009552</v>
+        <v>-1.82085934743592</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.332096307765404</v>
+        <v>-2.373628382724064</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.714270713010613</v>
+        <v>-1.821790753199515</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.6283009515931539</v>
+        <v>-0.7390882802975653</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.21804981858272</v>
+        <v>-1.393616531130327</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.89007086595511</v>
+        <v>-1.067607506825937</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.8867857354773605</v>
+        <v>-1.063776450637761</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.009199025232121</v>
+        <v>-1.18614144702299</v>
       </c>
     </row>
     <row r="16">
@@ -6648,79 +6648,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.145510890426635</v>
+        <v>-2.18170314456038</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3067931260595742</v>
+        <v>-0.4215830159687357</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.281962508256839</v>
+        <v>-2.392200465686066</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7869649749984262</v>
+        <v>-0.9070847851335557</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.196121852344724</v>
+        <v>-1.384262452802787</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2242440836545327</v>
+        <v>0.02956407053800092</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.083186527518791</v>
+        <v>-1.274375821437246</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.558483938976273</v>
+        <v>-1.693847800833659</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.615289066647428</v>
+        <v>-1.695858919316478</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.602727417760569</v>
+        <v>-1.629139428234112</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.623278393189899</v>
+        <v>-1.594345139253683</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.607473303591213</v>
+        <v>-1.522859926076258</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.7657289633088737</v>
+        <v>-0.6794536546826251</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.085483783553599</v>
+        <v>-0.9988609480417026</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.5646712996905663</v>
+        <v>-0.4770632426724148</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7560700653810741</v>
+        <v>-0.6693036560293137</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.930758764611511</v>
+        <v>-0.9015492099192812</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.273452950271484</v>
+        <v>-1.301375164477925</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.4078416192003544</v>
+        <v>-0.4955132820786758</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.4299640749716147</v>
+        <v>0.281303029364274</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.251915644643006</v>
+        <v>-0.4578999724267234</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.2256962364588802</v>
+        <v>0.01683513291136762</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.03387180823345659</v>
+        <v>-0.2407680414224558</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.1497780577319503</v>
+        <v>-0.3566309978064055</v>
       </c>
     </row>
     <row r="17">
@@ -6730,79 +6730,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.608260658853268</v>
+        <v>-1.640847113431967</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6159018255792432</v>
+        <v>-0.7119163399802133</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.134407617652442</v>
+        <v>-1.232458291823228</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1256067086662824</v>
+        <v>0.01987206943934439</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3657120831823022</v>
+        <v>-0.5287050793298391</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7479748250463274</v>
+        <v>0.580473929801137</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.02501530558534171</v>
+        <v>-0.1417755450013516</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2912743059019718</v>
+        <v>-0.4576898817880277</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6012448655182894</v>
+        <v>-0.7166686442572399</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6723228542160555</v>
+        <v>-0.7388679087519492</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.013002814408793</v>
+        <v>-1.028564282396417</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5891952778322818</v>
+        <v>-0.5551149273150813</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.04442349372588694</v>
+        <v>0.04185181490036172</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.09010297262928901</v>
+        <v>-0.003480137117392701</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.3052500548568204</v>
+        <v>0.3928581118749719</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1096174645365053</v>
+        <v>0.1963838738882657</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.05999442413823886</v>
+        <v>-0.02540672530361121</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4646345224632498</v>
+        <v>-0.4817412779824508</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2443492939190577</v>
+        <v>0.1735174140139364</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.9251144220469385</v>
+        <v>0.7997305350540245</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.4349871528549798</v>
+        <v>0.2571843670879943</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.8540318940487097</v>
+        <v>0.6739553345748064</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.652194145842067</v>
+        <v>0.4736044001233637</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5411715375038497</v>
+        <v>0.3626384371526186</v>
       </c>
     </row>
     <row r="18">
@@ -6812,79 +6812,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.325718766286684</v>
+        <v>-1.355361949037416</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.439174845870788</v>
+        <v>-0.5245805730979924</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9489872468117042</v>
+        <v>-1.036132920652136</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2373430532976357</v>
+        <v>0.1434994827669982</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.07908381192430625</v>
+        <v>-0.06657087999506217</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8779582314199814</v>
+        <v>0.7294096511689858</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6366061236253486</v>
+        <v>0.4868766247467065</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.08085379724083452</v>
+        <v>-0.0675168792197951</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1205378932749213</v>
+        <v>-0.2219473207787672</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.2468303003357377</v>
+        <v>-0.3025672400360548</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8630842841369173</v>
+        <v>-0.871066657979668</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6564344857615296</v>
+        <v>-0.6183339549638163</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.000118034489688057</v>
+        <v>0.08639334311593672</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3022800287615794</v>
+        <v>-0.2156571932496831</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.1516919486581116</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.2371765070876322</v>
+        <v>-0.1984419089682206</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.4043076914336083</v>
+        <v>-0.4133307058647233</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.7858801782159475</v>
+        <v>-0.8420580493620236</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.1155887243104559</v>
+        <v>-0.2213083688425499</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.6076541045866222</v>
+        <v>0.4513674006396471</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3572109629977689</v>
+        <v>0.2003585787191966</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.5746267306643134</v>
+        <v>0.4165228544279245</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.4098571612405095</v>
+        <v>0.2529623661010518</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.3013817325405839</v>
+        <v>0.1445570807109178</v>
       </c>
     </row>
     <row r="19">
@@ -6894,79 +6894,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.366416229321771</v>
+        <v>-1.391209958134432</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5264504606176743</v>
+        <v>-0.5987175936989999</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.125218394314118</v>
+        <v>-1.198526681743012</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4126984800792997</v>
+        <v>-0.4902333438918731</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2990679939880465</v>
+        <v>-0.4216305386834236</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.51405669639135</v>
+        <v>0.3888176262297733</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3677870101247436</v>
+        <v>0.2412597870135755</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.3812062972458605</v>
+        <v>-0.5057418621613792</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1932701236707075</v>
+        <v>-0.2767949433611321</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3084778305815661</v>
+        <v>-0.3506548858183223</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9125208612763487</v>
+        <v>-0.9116052180689351</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7524623694136707</v>
+        <v>-0.7098342520734491</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4131575240428731</v>
+        <v>-0.3268822154166244</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7809968117089241</v>
+        <v>-0.6943739761970278</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.488441582625903</v>
+        <v>-0.4008335256077515</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.7286245512098972</v>
+        <v>-0.6849239096676882</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.8196335423610606</v>
+        <v>-0.8188410466451614</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.174930782783804</v>
+        <v>-1.216507519133991</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5486022479311572</v>
+        <v>-0.634583927375111</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.02423421282704652</v>
+        <v>-0.1549123487394368</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.08276893457558288</v>
+        <v>-0.2145641538696665</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1796246573828029</v>
+        <v>0.04656473782512194</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.2778854352375788</v>
+        <v>0.144935763210178</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.2461428106793164</v>
+        <v>0.1130055443479208</v>
       </c>
     </row>
     <row r="20">
@@ -6976,79 +6976,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1482</v>
+        <v>1487</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.127329072244819</v>
+        <v>-1.149152761272497</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3892355632225204</v>
+        <v>-0.4516877415690104</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5919520601111543</v>
+        <v>-0.6564905988699863</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.06670314555640289</v>
+        <v>-0.001430535515162035</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1399893608085776</v>
+        <v>0.03328210082812433</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.9671263828706529</v>
+        <v>0.8579120666279252</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5670723250004244</v>
+        <v>0.4576333849612766</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.208756828323537</v>
+        <v>-0.3162356009563183</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2342127755189196</v>
+        <v>-0.3034662909224366</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6064030433117367</v>
+        <v>-0.6372237932139342</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.135719605244049</v>
+        <v>-1.127431852659868</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.146982820636012</v>
+        <v>-1.100521605241298</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9322220898693345</v>
+        <v>-0.8459467812430859</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.980499086407761</v>
+        <v>-0.9330671848162737</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5943478842717909</v>
+        <v>-0.5865219358462568</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.6974029763641667</v>
+        <v>-0.7289066147070145</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.7248524595819816</v>
+        <v>-0.7958445152477793</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.9918569970959936</v>
+        <v>-1.101622928379086</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.5343820902651686</v>
+        <v>-0.6453784429761313</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02891924590560535</v>
+        <v>-0.08371896098488918</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.003050178386232005</v>
+        <v>-0.1167201634082247</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.1635096687574986</v>
+        <v>0.04902658413106309</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.3440749547503259</v>
+        <v>0.2293972215681634</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.2411703432315804</v>
+        <v>0.1265838198970499</v>
       </c>
     </row>
     <row r="21">
@@ -7058,243 +7058,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1621</v>
+        <v>1626</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.250656304296882</v>
+        <v>-1.268584339709335</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3619890716664855</v>
+        <v>-0.4150639604731978</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3032347885383047</v>
+        <v>-0.3588317549662392</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.05559698866234442</v>
+        <v>-0.00228253784235477</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2142273884432555</v>
+        <v>-0.3038508674369282</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4358573219863544</v>
+        <v>0.344468910231754</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.1799861272203671</v>
+        <v>-0.2708131740389845</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9139267060536014</v>
+        <v>-1.003040161384263</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9949524364201139</v>
+        <v>-1.049375387028256</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.156273024793947</v>
+        <v>-1.17627594451649</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.494583847525021</v>
+        <v>-1.479400675705271</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.712489498859888</v>
+        <v>-1.662434494602373</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.427999771337092</v>
+        <v>-1.341724462710843</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.430025109522248</v>
+        <v>-1.378979809745672</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.194636733934182</v>
+        <v>-1.179279970071327</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.299864238471692</v>
+        <v>-1.320187165775394</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.459643053338318</v>
+        <v>-1.51537881255679</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.344483375878767</v>
+        <v>-1.436395986966211</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.092354381487745</v>
+        <v>-1.1847767956044</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6231151261826042</v>
+        <v>-0.7167605643885508</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.6376805543959279</v>
+        <v>-0.7322416881217819</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.7387411628693954</v>
+        <v>-0.833200658069309</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7972613407748739</v>
+        <v>-0.8911838994342745</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.8368699860831441</v>
+        <v>-0.9308793438401608</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.02</t>
+          <t>X &lt; 57.01</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1739</v>
+        <v>1744</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.017114935424658</v>
+        <v>-1.033137362865077</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2707265230660525</v>
+        <v>-0.3170873264159226</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1435454196503017</v>
+        <v>-0.1923035737526106</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5406959299102283</v>
+        <v>0.4889623610278448</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1506540773556395</v>
+        <v>0.07170345628811958</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3701917127616241</v>
+        <v>0.2908095462565043</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2564537626168146</v>
+        <v>-0.3351970268187401</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.7880201790592452</v>
+        <v>-0.8657066087808261</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8854911761878697</v>
+        <v>-0.9629097031835627</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.259785303491832</v>
+        <v>-1.304873137333871</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.328012364562902</v>
+        <v>-1.3405329154957</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.321641412052344</v>
+        <v>-1.301859376940371</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.099708454810489</v>
+        <v>-1.079838886562591</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9448218629618097</v>
+        <v>-0.9250725186739075</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8839573948823727</v>
+        <v>-0.8978931434960415</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9416952050361402</v>
+        <v>-0.9888288943114745</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.984988454972374</v>
+        <v>-1.065635808559072</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.285591784661079</v>
+        <v>-1.365597667638482</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.9211823716024981</v>
+        <v>-1.001997391835452</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6430630497449954</v>
+        <v>-0.7244819216627647</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.463838698876252</v>
+        <v>-0.5466037990174968</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6205379786738021</v>
+        <v>-0.703033002128457</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.9437386569872928</v>
+        <v>-1.024993202685465</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.7558814936858838</v>
+        <v>-0.8378526108205406</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.24</t>
+          <t>X &lt; 60.23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1898</v>
+        <v>1903</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5845414462455096</v>
+        <v>-0.5987254285645704</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2430417696205964</v>
+        <v>-0.2815552333218392</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2981016652910569</v>
+        <v>-0.338161440771124</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5832802510293149</v>
+        <v>0.5400696864111509</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1430626904539096</v>
+        <v>0.07747705996428067</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.09854020870935187</v>
+        <v>0.03323358209542704</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.278919732490337</v>
+        <v>-0.344187895301026</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8941110874984801</v>
+        <v>-0.9581492450356777</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.294203026708587</v>
+        <v>-1.357201263042484</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.439996461812726</v>
+        <v>-1.473937789157141</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.42734229121664</v>
+        <v>-1.431669536383453</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9735381591617056</v>
+        <v>-0.9487289394596203</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.7588269162338221</v>
+        <v>-0.7337889808257856</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.6351210815629145</v>
+        <v>-0.6101290757347968</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.7914402444106017</v>
+        <v>-0.7970681848336767</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.5847949635188172</v>
+        <v>-0.6215294304299519</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.5304962974199086</v>
+        <v>-0.5983785045802037</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.8145280009814186</v>
+        <v>-0.8818440195055715</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.5148044651583135</v>
+        <v>-0.582710180095404</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.2966571467277817</v>
+        <v>-0.3649729945377302</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.177688017411235</v>
+        <v>-0.2470046060372937</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2222188033662036</v>
+        <v>-0.291563817219874</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3371580610293563</v>
+        <v>-0.4059375575047497</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.2237696674906928</v>
+        <v>-0.292992250308167</v>
       </c>
     </row>
     <row r="24">
@@ -7304,79 +7304,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2052</v>
+        <v>2057</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5718593167750541</v>
+        <v>-0.5835529391421304</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5242684468864738</v>
+        <v>-0.5555853761363068</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5375800471857133</v>
+        <v>-0.5702694668368693</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4666007335469473</v>
+        <v>0.4307800689248111</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1769674015413045</v>
+        <v>0.1222724603665313</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3916231330441775</v>
+        <v>0.3365478452637021</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.06358842707530954</v>
+        <v>-0.1183501533963351</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.8472814038649261</v>
+        <v>-0.9004606224019795</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.21440068083416</v>
+        <v>-1.266694503429299</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.503970243216202</v>
+        <v>-1.528963467807174</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.520233642326666</v>
+        <v>-1.517831718039226</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9757703926127306</v>
+        <v>-0.9465011996434356</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8125815245424945</v>
+        <v>-0.7829246716079652</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8601676972725585</v>
+        <v>-0.8303591987105605</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.102686611443168</v>
+        <v>-1.100905597066308</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.4787934761361043</v>
+        <v>-0.5065186751233171</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.4871044411688104</v>
+        <v>-0.5435365872945894</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.7577195633206344</v>
+        <v>-0.813641431920729</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.5614518921031006</v>
+        <v>-0.6176846710843975</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.4915676852966442</v>
+        <v>-0.5478330975266061</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5196517168855834</v>
+        <v>-0.5764191273751251</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.4693361097773234</v>
+        <v>-0.5263438431988945</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.5551567667341786</v>
+        <v>-0.6117341618607739</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.6510173910614157</v>
+        <v>-0.7074799294862757</v>
       </c>
     </row>
     <row r="25">
@@ -7386,79 +7386,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3122461159853884</v>
+        <v>-0.3436474747689147</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3808098464854481</v>
+        <v>-0.4284029447686706</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.528522076171221</v>
+        <v>-0.57639160457407</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4588482574082633</v>
+        <v>0.4089073164428143</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4817893132959554</v>
+        <v>0.4154406014958525</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3774055447026115</v>
+        <v>0.3112695436160067</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.03839986140132368</v>
+        <v>-0.0274424143638754</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6682167561635168</v>
+        <v>-0.7329216762731647</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.145884743948038</v>
+        <v>-1.164420596027057</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.147924998935096</v>
+        <v>-1.140910116227985</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.554689633708705</v>
+        <v>-1.566979285421226</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.308512028725985</v>
+        <v>-1.275499015259641</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9075006626027005</v>
+        <v>-0.8742350146155431</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9659604282070475</v>
+        <v>-0.9779533155496409</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.143502685691772</v>
+        <v>-1.136323782598609</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.8400318815521359</v>
+        <v>-0.8599741164484414</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.6286705010542946</v>
+        <v>-0.6490686521289817</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9801306885256835</v>
+        <v>-0.9999509451022632</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9650363352899589</v>
+        <v>-0.9848291256586492</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7512150244603504</v>
+        <v>-0.7713525763624816</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.7203816438928854</v>
+        <v>-0.7407956637077362</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6324136194799692</v>
+        <v>-0.6530391339442332</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7870704157654345</v>
+        <v>-0.8073378623851326</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.790426112855755</v>
+        <v>-0.8107386075490766</v>
       </c>
     </row>
     <row r="26">
@@ -7468,79 +7468,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2337</v>
+        <v>2342</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6072272910743308</v>
+        <v>-0.6150324710282433</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9490487380642918</v>
+        <v>-0.9696967314261542</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7112962451139069</v>
+        <v>-0.7334227151541555</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.000777888698948459</v>
+        <v>-0.02490206500127101</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0400343405676864</v>
+        <v>0.002216192809754602</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.003697172627418865</v>
+        <v>-0.04132457459345318</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2426290655959704</v>
+        <v>-0.2802931580628822</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.7948180247248402</v>
+        <v>-0.8315236703912774</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.027075924113063</v>
+        <v>-1.063287419378931</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.8649713977601579</v>
+        <v>-0.8777405606685775</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.271388186281797</v>
+        <v>-1.259363336981458</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.015619115968541</v>
+        <v>-1.003876521504985</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6680705867160626</v>
+        <v>-0.6565758817982683</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4810593818507982</v>
+        <v>-0.4697703812934435</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7740278395362026</v>
+        <v>-0.7874881469591131</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5372736135903082</v>
+        <v>-0.5760799484203716</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.1342872911224902</v>
+        <v>-0.1740696196586882</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.4699695630095633</v>
+        <v>-0.509136241500741</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5273470234722311</v>
+        <v>-0.5662745501507587</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4431788727734869</v>
+        <v>-0.4821882078385613</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.4057955811316418</v>
+        <v>-0.4452787129424323</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.2853136932201679</v>
+        <v>-0.3251336397633864</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.6264913781459711</v>
+        <v>-0.6654267565134191</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.7627465785287271</v>
+        <v>-0.801470705603478</v>
       </c>
     </row>
     <row r="27">
@@ -7550,79 +7550,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2478</v>
+        <v>2483</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2793098645617462</v>
+        <v>-0.2862145255725395</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5822385313074676</v>
+        <v>-0.5996750504154207</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4390850415847822</v>
+        <v>-0.4576077889502699</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1910704699487837</v>
+        <v>0.1708840273414509</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1288440755857252</v>
+        <v>0.09761254719721535</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1383010817466115</v>
+        <v>0.1071317545030723</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2511222342232244</v>
+        <v>-0.2819576207318661</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6674517115614123</v>
+        <v>-0.6976278510957243</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8841614319412443</v>
+        <v>-0.9139019057418167</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9757702737135929</v>
+        <v>-0.982861592877434</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.423937363319141</v>
+        <v>-1.407649525576538</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.278843148753573</v>
+        <v>-1.262662346304225</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8942788502647687</v>
+        <v>-0.8782806582227636</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7305055517577941</v>
+        <v>-0.7146519549586401</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.963915511183238</v>
+        <v>-0.9713500498093666</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8275816413174297</v>
+        <v>-0.8586973711421635</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.2942230146788347</v>
+        <v>-0.3265056729395042</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6168764766035579</v>
+        <v>-0.6485914115402238</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.537957174205161</v>
+        <v>-0.5697338475777229</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3673660404576964</v>
+        <v>-0.3994047929044342</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.4838761731179133</v>
+        <v>-0.5160031278750097</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3342731327380193</v>
+        <v>-0.3667656845920817</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.559754569966664</v>
+        <v>-0.5916640220035987</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.7732627407822292</v>
+        <v>-0.8048067983785074</v>
       </c>
     </row>
     <row r="28">
@@ -7632,79 +7632,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2603</v>
+        <v>2608</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1926746007001015</v>
+        <v>-0.1984735873764336</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7272420674951547</v>
+        <v>-0.7412251294378009</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5833466375747278</v>
+        <v>-0.5982642017720394</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1699650273658193</v>
+        <v>-0.1860029208495675</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2467926941369356</v>
+        <v>-0.2719112623265971</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4580901656090077</v>
+        <v>-0.4827383398761356</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6368776741302895</v>
+        <v>-0.6615521846788681</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.9703545121779555</v>
+        <v>-0.9945363915349503</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.098388306180865</v>
+        <v>-1.12232389676111</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.031475399321742</v>
+        <v>-1.034109126111844</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.330435619426439</v>
+        <v>-1.311014393929547</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.205586450833785</v>
+        <v>-1.186222187043938</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7784055801793812</v>
+        <v>-0.759183460066005</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5947448302601615</v>
+        <v>-0.5756653647016066</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9633305397760239</v>
+        <v>-0.9662245644228307</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.8433266498262171</v>
+        <v>-0.8687795385043131</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.495198985445974</v>
+        <v>-0.5213961334430905</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.9224889699608099</v>
+        <v>-0.9479345350556798</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7604208474284775</v>
+        <v>-0.7860957678797575</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.5507655348456737</v>
+        <v>-0.5767742811652923</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.6110746544076378</v>
+        <v>-0.6372335309626322</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.4723450787475514</v>
+        <v>-0.4988223926565567</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.5586547012693046</v>
+        <v>-0.5848592603368985</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6118887503192596</v>
+        <v>-0.6380439768361867</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2736</v>
+        <v>2741</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.668279380550949</v>
+        <v>-0.6719839707817101</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.158519585178126</v>
+        <v>-1.16866990960866</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8734647364200328</v>
+        <v>-0.8846574535663976</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5509446409388801</v>
+        <v>-0.5629869766310165</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7144989854000343</v>
+        <v>-0.7335984752828466</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9067069374995711</v>
+        <v>-0.9254031310507074</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.150740401733472</v>
+        <v>-1.169285770624782</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.299933836178376</v>
+        <v>-1.318321867218167</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.347130412011957</v>
+        <v>-1.365430451633117</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.357281947824781</v>
+        <v>-1.35523001297225</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.410239451345312</v>
+        <v>-1.387601410099393</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.52331448387573</v>
+        <v>-1.500449196376465</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9893751041422263</v>
+        <v>-0.966679899431</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8982444201029764</v>
+        <v>-0.8755659123569686</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.098868633539716</v>
+        <v>-1.097186838165975</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.101652883421913</v>
+        <v>-1.121206609566016</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.9228287724482129</v>
+        <v>-0.942769856310548</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.00641547807291</v>
+        <v>-1.02625604820949</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.9512013829457189</v>
+        <v>-0.9710776320476242</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7062145085520584</v>
+        <v>-0.7264826469256747</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.7535268324773483</v>
+        <v>-0.7739197642456901</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8444171040851316</v>
+        <v>-0.8646857606444627</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8037036324827369</v>
+        <v>-0.8239603464890592</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.7119335703986494</v>
+        <v>-0.7323990664434419</v>
       </c>
     </row>
     <row r="30">
@@ -7796,325 +7796,325 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2840</v>
+        <v>2845</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5858895194845033</v>
+        <v>-0.5888764123506931</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.9316687220871387</v>
+        <v>-0.9400342397650334</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9546267685802547</v>
+        <v>-0.9633811807080619</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6352253704472659</v>
+        <v>-0.6447534048365142</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8412136045050431</v>
+        <v>-0.8563797685554917</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.054523194591496</v>
+        <v>-1.069271720933223</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.10797520405135</v>
+        <v>-1.122868028191</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.296940682222001</v>
+        <v>-1.311595381362821</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.375910706203157</v>
+        <v>-1.390425098358925</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.309051375096921</v>
+        <v>-1.30403578170295</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.154900129663538</v>
+        <v>-1.150118605726618</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.273942761791986</v>
+        <v>-1.268982563921959</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9056512317809791</v>
+        <v>-0.9011489330243734</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8609844822028734</v>
+        <v>-0.8565362492801469</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.043232840199003</v>
+        <v>-1.059178495704437</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.024160008262207</v>
+        <v>-1.039973871204154</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9269904658912083</v>
+        <v>-0.9430250463658894</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.9762247949484788</v>
+        <v>-0.9922148946766143</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.7393689535666752</v>
+        <v>-0.7557213243081478</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6019098897874997</v>
+        <v>-0.6184589323445806</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.5266351901879176</v>
+        <v>-0.5434885066704211</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.511340622692849</v>
+        <v>-0.5282544627121624</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5675355230737864</v>
+        <v>-0.5842801524485637</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.552247383099413</v>
+        <v>-0.5690525269779769</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 85.99</t>
+          <t>X &lt; 85.98</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2937</v>
+        <v>2941</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6021967077072432</v>
+        <v>-0.586510292642231</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9485897596870529</v>
+        <v>-0.9371364033415333</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8489512469426188</v>
+        <v>-0.8374862569964918</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5634249500574668</v>
+        <v>-0.5522726559311906</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9099848513035909</v>
+        <v>-0.9030768749048548</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.04246098010637</v>
+        <v>-1.03539422140453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9840922611010541</v>
+        <v>-0.9770283882014397</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.14208707589259</v>
+        <v>-1.1347830191648</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.183157165956793</v>
+        <v>-1.175803181285225</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.110052401675162</v>
+        <v>-1.117267167737374</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.053573545098963</v>
+        <v>-1.060972597461088</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.177849142208579</v>
+        <v>-1.185005883819024</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8247326843123304</v>
+        <v>-0.8317610737632677</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7548640742947441</v>
+        <v>-0.7618727974492359</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.9188338359629356</v>
+        <v>-0.9454398238433512</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8128301023084887</v>
+        <v>-0.8396528869570616</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.7571773712530643</v>
+        <v>-0.7840754363895002</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.9101294423734743</v>
+        <v>-0.9368226421888721</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.8438852074690146</v>
+        <v>-0.8707032802162473</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.7388266842607081</v>
+        <v>-0.7658194871754205</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.7180230362162447</v>
+        <v>-0.7450029180040829</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6717809530411714</v>
+        <v>-0.6988294227806406</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6490272652359295</v>
+        <v>-0.6761476129749369</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7389258467995674</v>
+        <v>-0.7659297174652835</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 89.21</t>
+          <t>X &lt; 89.2</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3031</v>
+        <v>3036</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4998369879561366</v>
+        <v>-0.5015403770029323</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5846257621930917</v>
+        <v>-0.5899516841075965</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7945164757266028</v>
+        <v>-0.7997686152630337</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.53977757544844</v>
+        <v>-0.5455822503046193</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7557194101920004</v>
+        <v>-0.7649414803076979</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9110941071266225</v>
+        <v>-0.9200331238950596</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.075247968096249</v>
+        <v>-1.084067198302186</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.236995854921283</v>
+        <v>-1.245607616260017</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.275547433039449</v>
+        <v>-1.284094213434123</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.162913612063342</v>
+        <v>-1.153106970480785</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.132573077382538</v>
+        <v>-1.122845260432065</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.19593511174191</v>
+        <v>-1.186084291386827</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.82274780861907</v>
+        <v>-0.8132267865556884</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8276505719586709</v>
+        <v>-0.8180916613828799</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.8424814223423169</v>
+        <v>-0.8522612315414406</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.8529424840174684</v>
+        <v>-0.8626010432843572</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7044261690891744</v>
+        <v>-0.7143600810418462</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.8229500395367211</v>
+        <v>-0.8327151655252081</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.7849728491743875</v>
+        <v>-0.7947666521954346</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8420987784446794</v>
+        <v>-0.8517702511822165</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.9047279093322587</v>
+        <v>-0.914403965259325</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.8623354153709997</v>
+        <v>-0.8721018490442347</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.7988473823080113</v>
+        <v>-0.8086735613564073</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7234013275513576</v>
+        <v>-0.7333724280595391</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 92.43</t>
+          <t>X &lt; 92.42</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3135</v>
+        <v>3140</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4772604416883865</v>
+        <v>-0.4782917687134329</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4445111123634291</v>
+        <v>-0.4482591537937992</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5681273725721425</v>
+        <v>-0.571870808914035</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2818485340022505</v>
+        <v>-0.2861411397996747</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.6295010320097347</v>
+        <v>-0.6359150018844772</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6466284343712587</v>
+        <v>-0.6529949125717351</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8307967350756869</v>
+        <v>-0.8369770481876486</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.028072364316905</v>
+        <v>-1.033980761434414</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.9686446760978171</v>
+        <v>-0.9746458938399627</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9170514231650486</v>
+        <v>-0.9050910819856881</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8150362978825427</v>
+        <v>-0.8032548158366168</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.7901007626218188</v>
+        <v>-0.7782975561835386</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4663054941348008</v>
+        <v>-0.4547029874540769</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5100515058828989</v>
+        <v>-0.4983508830400325</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5460939842815264</v>
+        <v>-0.5531280326371046</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.536418835618889</v>
+        <v>-0.54339455546571</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3653307559706462</v>
+        <v>-0.3726004428676433</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3559515426999198</v>
+        <v>-0.3632545562044598</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3119233287695664</v>
+        <v>-0.3192724915744733</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2652353506539029</v>
+        <v>-0.2726387391961538</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3754806655394773</v>
+        <v>-0.3827849456984822</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.336843906129495</v>
+        <v>-0.3442243256811395</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3299543501611097</v>
+        <v>-0.3373141195909</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2274838096330996</v>
+        <v>-0.2350214298470163</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3244</v>
+        <v>3249</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1701541385848842</v>
+        <v>-0.1709602286872425</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1505670072582035</v>
+        <v>-0.1529939423628264</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3180574555403552</v>
+        <v>-0.3203422572336976</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2796428306948044</v>
+        <v>-0.2820437366814659</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3826387306152839</v>
+        <v>-0.3864768314376192</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4848565634525244</v>
+        <v>-0.4885259819534156</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5352921430969104</v>
+        <v>-0.5389472859709414</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.643145641249653</v>
+        <v>-0.6466598267213826</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6148924934742368</v>
+        <v>-0.61844910157388</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.6216162523243725</v>
+        <v>-0.6075923542161803</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5137401744709038</v>
+        <v>-0.4999082356558375</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4988928808514999</v>
+        <v>-0.4850125341922791</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3156838772375252</v>
+        <v>-0.301768744308113</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2731411800322618</v>
+        <v>-0.2592248175093701</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2685071961219876</v>
+        <v>-0.272800895937074</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2391202056169917</v>
+        <v>-0.2434151152296664</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.108934104967112</v>
+        <v>-0.1134421165024477</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.07254351487928545</v>
+        <v>-0.0771184049656668</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.02265254873534417</v>
+        <v>-0.02728992004455932</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.03273998408332801</v>
+        <v>-0.03734995898230409</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1882509179448419</v>
+        <v>-0.1926672316037426</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1842125122224516</v>
+        <v>-0.188643738520085</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1066417970967422</v>
+        <v>-0.1111734980348089</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.04092420357839899</v>
+        <v>-0.04556578156326907</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3343</v>
+        <v>3348</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03618231050982246</v>
+        <v>-0.03657538397483506</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.146835230955439</v>
+        <v>-0.1477307367076008</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2035229378093604</v>
+        <v>-0.2043820525313862</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1577123819005308</v>
+        <v>-0.1586634885690543</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1792438432620855</v>
+        <v>-0.1808311712465098</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2430366220480593</v>
+        <v>-0.2445240593376141</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2256222628748787</v>
+        <v>-0.2271619268216156</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3682387970704184</v>
+        <v>-0.3695766391062634</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2799493416741825</v>
+        <v>-0.2814180314537609</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2922969607311501</v>
+        <v>-0.2937737205235678</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2688015202913832</v>
+        <v>-0.2703052011914693</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2625574395980266</v>
+        <v>-0.2640806031376499</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2669629057858671</v>
+        <v>-0.2685175675681606</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1725514999560289</v>
+        <v>-0.1742550669599368</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1278256002094267</v>
+        <v>-0.1296185952443736</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.08167973237609516</v>
+        <v>-0.08352295301043711</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1383624783263997</v>
+        <v>-0.1401267743346466</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1360205573948434</v>
+        <v>-0.13779291425233</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.008374367735235921</v>
+        <v>0.006392729092588922</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.06388356380383442</v>
+        <v>0.0618241465065168</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.01341483310235247</v>
+        <v>-0.01537808180982836</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.01169248757673103</v>
+        <v>-0.01366198778437422</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.01794258373205793</v>
+        <v>-0.01989481553486883</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.01369237751030994</v>
+        <v>0.01168922163044073</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_7.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_7.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 7.123</t>
+          <t>X ≈ 7.109</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.177409896605582</v>
+        <v>3.992983534367376</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.806864913669529</v>
+        <v>7.561516664363275</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.364205093049044</v>
+        <v>0.5365419799265538</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3621525103428809</v>
+        <v>-0.0771686181491944</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.690404480820135</v>
+        <v>-5.034205317489715</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.559022720679522</v>
+        <v>9.577073854820704</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.935866228777101</v>
+        <v>3.048777285116955</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.660296267030773</v>
+        <v>2.746645201351427</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.702335047878293</v>
+        <v>0.9604567390230443</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.05763351182547183</v>
+        <v>-1.746691791349448</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.776894320021718</v>
+        <v>-3.391695341683821</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.033754031421445</v>
+        <v>-9.417086703044809</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.1684195102793</v>
+        <v>-6.697184149448233</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.378213489265917</v>
+        <v>-10.78119952377039</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-12.03176638494576</v>
+        <v>-13.38243293299445</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.447272324795414</v>
+        <v>-10.90794187336889</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-7.587995807165193</v>
+        <v>-9.095789950310682</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.691182961335272</v>
+        <v>-11.15061109373181</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.484464979725423</v>
+        <v>-7.099290388377121</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.299576841395535</v>
+        <v>-6.887164181684447</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-9.839571595056675</v>
+        <v>-11.29883693809671</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-7.919442177743271</v>
+        <v>-9.455363792991697</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-7.647376599920719</v>
+        <v>-9.214634450309553</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.72546728971917</v>
+        <v>-3.610299529406959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 10.34</t>
+          <t>X ≈ 10.32</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.285443041731959</v>
+        <v>-8.310537337406195</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-12.83353575893236</v>
+        <v>-12.44689668412335</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-15.89353468842279</v>
+        <v>-15.27758749575366</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.597255457159939</v>
+        <v>-7.973468725264532</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-15.36038189180448</v>
+        <v>-14.56120824493051</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-15.16804393983075</v>
+        <v>-14.40707208108304</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-15.94905747863713</v>
+        <v>-15.20214374557407</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-10.50092494429479</v>
+        <v>-10.77111900141823</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10.46291552122366</v>
+        <v>-10.64685919012737</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.023193464349362</v>
+        <v>-8.281265627155875</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.752678172328622</v>
+        <v>-8.012627645013183</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.42584616563515</v>
+        <v>-6.709178045533015</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.331984018024876</v>
+        <v>-4.658137677434624</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.553453799843595</v>
+        <v>-4.906779392463861</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.994048741094396</v>
+        <v>-2.422437063585157</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.2070558479803708</v>
+        <v>-0.2798913145988564</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-3.145452296716122</v>
+        <v>-3.551483292104095</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.640995225168396</v>
+        <v>-2.100640042071362</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-3.036354402367181</v>
+        <v>-3.472003001583843</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.239866359695185</v>
+        <v>-1.673496374473878</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1708150165389526</v>
+        <v>-0.6550455758470264</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.858510441632866</v>
+        <v>-2.316689038071551</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.640154081532522</v>
+        <v>1.099757311735416</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>3.177758516731622</v>
+        <v>2.525231606124976</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 13.56</t>
+          <t>X ≈ 13.54</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.762667937049414</v>
+        <v>-6.754809132610923</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.743670909236229</v>
+        <v>7.019864398697941</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.236188915645947</v>
+        <v>-1.19002958173855</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.607786743213786</v>
+        <v>5.869500402342716</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.016904085196792</v>
+        <v>4.322027810216056</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.460829128188315</v>
+        <v>4.476040634681468</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.08525238334040353</v>
+        <v>-0.138826043579968</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.3622233492532345</v>
+        <v>-0.4422988354493853</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.581009069324367</v>
+        <v>-1.591000401194265</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.169832259913008</v>
+        <v>0.1690317412952353</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4427744517305072</v>
+        <v>0.4401573888916559</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1650711453117921</v>
+        <v>0.164599677190914</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.83029984881437</v>
+        <v>2.886646734760248</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.349248328619979</v>
+        <v>1.362319824849386</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.830935279825823</v>
+        <v>-1.874240374107828</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.286365368998723</v>
+        <v>1.242559096039521</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.205278773427821</v>
+        <v>6.256321549092142</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>8.629530957836081</v>
+        <v>8.685046451458987</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>7.584025197636755</v>
+        <v>7.621906358408424</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.24442340557512</v>
+        <v>5.277558692100186</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.439475434960066</v>
+        <v>3.431482517436478</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.8348092252787467</v>
+        <v>0.7949726608360663</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.374891397969364</v>
+        <v>2.320360874415726</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.497619188453513</v>
+        <v>-1.687222606329598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 16.78</t>
+          <t>X ≈ 16.75</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6941615231786287</v>
+        <v>-0.1319111007059277</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1405180772613974</v>
+        <v>1.881936269074011</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.457583656118523</v>
+        <v>-1.624186899398637</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.508828266435906</v>
+        <v>-6.733744752528075</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.34947117646341</v>
+        <v>2.032247667235133</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1929115778636756</v>
+        <v>-0.07346863273832582</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.914888030462791</v>
+        <v>-1.993417619360685</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.532542887433856</v>
+        <v>-4.558437067823796</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.663790606493201</v>
+        <v>-5.563189513475251</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.606309401372364</v>
+        <v>-8.6198931038792</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.82173235131841</v>
+        <v>-4.956839594403299</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.929194185568974</v>
+        <v>-4.102110775513111</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.877422545598527</v>
+        <v>-2.949780543885979</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.753316833543302</v>
+        <v>-0.9323511791112509</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.236711888205427</v>
+        <v>-0.4794059021427728</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-5.338412400720777</v>
+        <v>-4.453827247802359</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-4.300191769433106</v>
+        <v>-3.425293453945464</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.754553813186426</v>
+        <v>-5.827289468580375</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-6.541057520823877</v>
+        <v>-5.614895575240659</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.706502199841914</v>
+        <v>-7.67224273697753</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.42653958075157</v>
+        <v>-9.376773175262798</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.978451896894541</v>
+        <v>-6.047942588581201</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-4.354159140142016</v>
+        <v>-2.398430799950276</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-2.078408466190218</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 20</t>
+          <t>X ≈ 19.96</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.223378353074501</v>
+        <v>-2.974405269206628</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.628871782467066</v>
+        <v>2.241242121944829</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.920185539087321</v>
+        <v>2.087907665681065</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.05456308716946268</v>
+        <v>1.498381144919968</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.720788100079751</v>
+        <v>-3.144656627460414</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.236855913224815</v>
+        <v>-1.898249511765179</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.027678138609353</v>
+        <v>-2.688158606293122</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.455847079169658</v>
+        <v>-4.085058045946226</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.4696469028109007</v>
+        <v>-1.771851547414435</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.617778077501512</v>
+        <v>3.998383677111335</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.8343029992995028</v>
+        <v>-1.200654814923794</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.732975022913145</v>
+        <v>-3.665866236999435</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5829056350658917</v>
+        <v>-1.493481918002111</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.508557679690171</v>
+        <v>-0.6459165444449795</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.2927510548397123</v>
+        <v>-2.421532492682822</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.992975274396052</v>
+        <v>-4.054609839634828</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.60607687427207</v>
+        <v>1.321821555812079</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.502775978058892</v>
+        <v>1.189811843301293</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.42455869484963</v>
+        <v>-0.7897295680975276</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>3.907382972587968</v>
+        <v>1.61915494180132</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.515068994075598</v>
+        <v>2.150706919099967</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.292139192705058</v>
+        <v>0.9780826132835898</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.418498097425051</v>
+        <v>0.1232528875209127</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.55305349661618</v>
+        <v>-6.632277551384789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 23.22</t>
+          <t>X ≈ 23.18</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.749062480578061</v>
+        <v>-2.996203567200425</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.221990219342509</v>
+        <v>-4.289485475377589</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.354694627727739</v>
+        <v>-1.350193334525279</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.014049215215003</v>
+        <v>-0.8933852983305286</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.525227335230603</v>
+        <v>3.018517781986567</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.863642327672991</v>
+        <v>7.356795399968597</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8607742582610243</v>
+        <v>1.337834087000566</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.71787424629786</v>
+        <v>4.176239986997182</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.522211797995155</v>
+        <v>-0.9311691625876719</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1653998778789472</v>
+        <v>-1.724167901951652</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.184559915645629</v>
+        <v>-0.4057076157683142</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1705003139096704</v>
+        <v>-0.6812979748460606</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2405147691681506</v>
+        <v>-0.7441009165769188</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6059145371288253</v>
+        <v>0.05741275825913306</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-3.285662263716013</v>
+        <v>-3.770251364764675</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-3.753574709103432</v>
+        <v>-4.261546496796086</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-8.17890895017981</v>
+        <v>-8.567802847046956</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-10.43715430528511</v>
+        <v>-10.80407826155434</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-8.074174538415221</v>
+        <v>-8.491822845206144</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-6.809722633178509</v>
+        <v>-7.229405579429816</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-8.442627117065705</v>
+        <v>-8.850203131768012</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-7.877582338242291</v>
+        <v>-8.928373037325677</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-8.034001721389259</v>
+        <v>-9.74032899959397</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.886757612300272</v>
+        <v>-6.747951351268625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 26.44</t>
+          <t>X ≈ 26.39</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.583122440450062</v>
+        <v>-3.100136089273128</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.212009113951481</v>
+        <v>-7.521858257950228</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.967200110917673</v>
+        <v>-7.09744768725502</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.633441241049603</v>
+        <v>-5.181946587945092</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.833354161933833</v>
+        <v>-6.290253696305413</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-6.355445722330636</v>
+        <v>-7.807596566225087</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.707874975414605</v>
+        <v>-5.256754203489344</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.567222262633685</v>
+        <v>-8.068300239358798</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.808253707316794</v>
+        <v>-6.271296979721676</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.373041421537245</v>
+        <v>-3.72142517684064</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.956406220031241</v>
+        <v>-4.288346756480337</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.379057106508967</v>
+        <v>-3.72851504731981</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.790097375824473</v>
+        <v>-3.166876919874582</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-5.593239221747744</v>
+        <v>-5.92731338770254</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.678876773090686</v>
+        <v>-4.095546639952097</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.360771774412314</v>
+        <v>-1.861475235916998</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.355741282607539</v>
+        <v>-2.804501705217</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.046576240914625</v>
+        <v>-5.453422347931365</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.385295484296364</v>
+        <v>-1.885991111936733</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.919853367617797</v>
+        <v>-3.350961647844883</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.46931102406181</v>
+        <v>-3.918924698588434</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.9601420266523419</v>
+        <v>-1.476356662765369</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.26829839752213</v>
+        <v>-3.75371699775534</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.828915565581688</v>
+        <v>-3.917345424687703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 29.66</t>
+          <t>X ≈ 29.61</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.245929615193297</v>
+        <v>-1.546044283253998</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.893257707069473</v>
+        <v>3.817401312433752</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.196696978331609</v>
+        <v>-3.049026792377525</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.7593551605073188</v>
+        <v>0.3645963847807892</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.419344578285298</v>
+        <v>-3.918296995625212</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.568333159323188</v>
+        <v>-2.157619559184802</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.345765349371128</v>
+        <v>-2.955828142376618</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.795580367247751</v>
+        <v>-1.199663739309244</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.584435372459168</v>
+        <v>-2.676275565643024</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.360181245221689</v>
+        <v>-2.667992182215535</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.254187430275394</v>
+        <v>-2.39815920755079</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.881274946357884</v>
+        <v>-3.477377496174981</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.679662552930878</v>
+        <v>-1.377243873493647</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.069340776856372</v>
+        <v>-0.01776408289197207</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.599863242299932</v>
+        <v>2.517993886521133</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.96544541897034</v>
+        <v>-0.9419971669937794</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.4360729516286099</v>
+        <v>0.5622366944643957</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.124043876919181</v>
+        <v>2.844287282707491</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.339958681978082</v>
+        <v>3.059020599620098</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.6940899290694844</v>
+        <v>2.46891531816258</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.9850695457640271</v>
+        <v>2.708632130372138</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.742556917688269</v>
+        <v>3.440118105167933</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.850364963503651</v>
+        <v>4.490815502449401</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>1.910792282007876</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 32.87</t>
+          <t>X ≈ 32.82</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.10159173552227</v>
+        <v>-6.619219420993893</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.832278228288196</v>
+        <v>2.445682795611091</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.005915160319155</v>
+        <v>-5.00569491410355</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.855590263371425</v>
+        <v>-0.1642855062703035</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.96169278306818</v>
+        <v>-1.987958162932465</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.232371333940101</v>
+        <v>-0.2839042854471572</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.317519995312765</v>
+        <v>-2.624157517349381</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.821823888628273</v>
+        <v>-2.150386809149666</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.78033670671357</v>
+        <v>-2.023129497531428</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.64089257897173</v>
+        <v>-5.924657847989486</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.368031438239058</v>
+        <v>-5.656340563956931</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.873139623900457</v>
+        <v>-5.156239316814435</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.905372375511625</v>
+        <v>-3.158203084530562</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.673649548941128</v>
+        <v>-5.741043375980183</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.692538616300141</v>
+        <v>-2.5302807671846</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.647744352127198</v>
+        <v>-3.529182126274023</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-6.879276179077053</v>
+        <v>-5.97219843336093</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-6.986564664495539</v>
+        <v>-6.886205136685184</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-5.999273840160413</v>
+        <v>-5.115851614181075</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3841161110896678</v>
+        <v>0.5563135682712073</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.9335351053989314</v>
+        <v>-0.7904776360233683</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2341872683582551</v>
+        <v>-0.0855330817033817</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.285293951225029</v>
+        <v>-2.18512460103144</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.361126204448126</v>
+        <v>-2.348280298637107</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 36.09</t>
+          <t>X ≈ 36.03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.411086601022227</v>
+        <v>3.60263325769786</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.550288747772825</v>
+        <v>-1.910549519714145</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.037585492929516</v>
+        <v>0.5956168793138445</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.931957808637343</v>
+        <v>0.003250391547233278</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.812438491253246</v>
+        <v>3.489874060911774</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.389429912424774</v>
+        <v>2.142463466542196</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.229368748298292</v>
+        <v>2.099362104253274</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.149186188326567</v>
+        <v>1.041097939531355</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.994115835334995</v>
+        <v>2.354651164869345</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.831027789236636</v>
+        <v>3.070308536053346</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.496878286323202</v>
+        <v>2.588427894167346</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.826190892963034</v>
+        <v>3.821706260062584</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.511066709726634</v>
+        <v>3.465524953805222</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.90113442381822</v>
+        <v>5.483760499321257</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>8.464408343321615</v>
+        <v>8.579810089345777</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>9.061087766094317</v>
+        <v>9.898141719910143</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.710344608466087</v>
+        <v>6.021260480781969</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>6.413477385661778</v>
+        <v>7.402928092235598</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>9.048734550941667</v>
+        <v>9.13125190582403</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>7.626654200637731</v>
+        <v>8.592150690181796</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>6.280768470495396</v>
+        <v>7.272549801311328</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>7.817825734892558</v>
+        <v>8.714014608512365</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.672945608664932</v>
+        <v>6.689133322182833</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.597113355441486</v>
+        <v>7.287136368029216</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 39.31</t>
+          <t>X ≈ 39.25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.926195870069705</v>
+        <v>2.459787046427088</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.171528793163731</v>
+        <v>-3.393637807932684</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.556781541598546</v>
+        <v>8.167477704472972</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.843630915955707</v>
+        <v>7.575136398059954</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.681725430397591</v>
+        <v>6.497608267197769</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.22530886946992</v>
+        <v>4.252224552211814</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.388423581652596</v>
+        <v>8.718754260468302</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>9.931608601112359</v>
+        <v>9.217716423751739</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.50261499199145</v>
+        <v>7.743288554180005</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.726160404356236</v>
+        <v>6.955010912839356</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.707359760270158</v>
+        <v>4.020980505047</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.545226381681914</v>
+        <v>7.758215148876957</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.083656347550296</v>
+        <v>5.847365154974774</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>8.338009029914787</v>
+        <v>8.011928398453115</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.68453084695556</v>
+        <v>7.335021545048797</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>7.456475408330761</v>
+        <v>7.094191176837924</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>7.326154786052257</v>
+        <v>6.994029344933757</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.399403831955468</v>
+        <v>6.86488247822939</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>5.791697097484878</v>
+        <v>6.276305330259177</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.15472935851291</v>
+        <v>5.687599354184925</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.267438691769549</v>
+        <v>6.73469627886989</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>6.191592730360448</v>
+        <v>6.662267904059455</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>6.466067442842501</v>
+        <v>6.908690061645522</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>6.390235189619226</v>
+        <v>6.749501959427228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 42.53</t>
+          <t>X ≈ 42.46</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.038314483843152</v>
+        <v>0.538269467904982</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.704479795860301</v>
+        <v>0.2932057722769912</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.292869042112997</v>
+        <v>0.05713375324535974</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.617942679147681</v>
+        <v>-0.5350998175479731</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.431122464619996</v>
+        <v>4.3087584270138</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.508402196331403</v>
+        <v>1.395492403145461</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7.958338715525379</v>
+        <v>6.741990046751475</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.561961823082463</v>
+        <v>3.362485645083112</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.64116262468584</v>
+        <v>4.514432734111494</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.862594286446857</v>
+        <v>5.331969885719516</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9842292659098604</v>
+        <v>1.506580507321694</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.371517560859715</v>
+        <v>-0.8199706888539779</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6143787530923959</v>
+        <v>2.171758657692223</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.724668179124322</v>
+        <v>-2.17923248927633</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-5.466333316203674</v>
+        <v>-2.860261413466901</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-4.870024011763348</v>
+        <v>-2.301805825827032</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-5.008274174957883</v>
+        <v>-3.433515728514237</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-5.118508421665688</v>
+        <v>-4.595151695518538</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-4.899605512878956</v>
+        <v>-4.384016228156895</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.66803328612415</v>
+        <v>-3.143262087460869</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4732637875693015</v>
+        <v>-0.6221926454515483</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.632443082311497</v>
+        <v>-2.757680413379994</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.357968369829685</v>
+        <v>-2.515291179631717</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.43380062305296</v>
+        <v>-2.678499370802236</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 45.75</t>
+          <t>X ≈ 45.67</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.724145328114915</v>
+        <v>-1.289958557828982</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.298619169269273</v>
+        <v>-0.7962094308209373</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.730910621055827</v>
+        <v>-2.040700694998741</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.48693406838661</v>
+        <v>-5.598219459563069</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.778107113790782</v>
+        <v>-3.647389465916881</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.832540769678559</v>
+        <v>-2.753582489310702</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.079858741114514</v>
+        <v>-2.059768092206596</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.638359857751929</v>
+        <v>-4.584583954452107</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.7928810910514841</v>
+        <v>-0.7503366317977225</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.8022430114564898</v>
+        <v>-0.7999302724956152</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.288795926340974</v>
+        <v>-1.269231926278472</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.567080930012644</v>
+        <v>-1.545952848231231</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.209300912004643</v>
+        <v>-4.885019613958939</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.192330959545465</v>
+        <v>-5.133413832211332</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.567077803353619</v>
+        <v>-4.329745519019802</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-5.26101760369508</v>
+        <v>-6.002419356755617</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.634863974187077</v>
+        <v>-4.620712360148822</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.741670865570796</v>
+        <v>-4.01067653147674</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.528529981886109</v>
+        <v>-3.055179543116424</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.870603115786302</v>
+        <v>-4.332859797944423</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-4.123072947874817</v>
+        <v>-2.665579657821674</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.435560130657784</v>
+        <v>-1.250966464168222</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.8710090822978742</v>
+        <v>0.4838266147515284</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1834825568951999</v>
+        <v>1.814499552108984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 48.97</t>
+          <t>X ≈ 48.89</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.485393935999554</v>
+        <v>1.145174810902553</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.153211643372948</v>
+        <v>0.1174790366861203</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.276723132165415</v>
+        <v>4.335787301263643</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.359107423536926</v>
+        <v>4.525333973261823</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.019425192405116</v>
+        <v>5.031564771674873</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.014053591501586</v>
+        <v>5.971406842244896</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.836631182244844</v>
+        <v>3.611094319280525</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.75010889806201</v>
+        <v>2.523265411299967</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5996078639126594</v>
+        <v>0.3050811547408472</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.777348638885059</v>
+        <v>-2.05604091891594</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.504586249584463</v>
+        <v>-1.331982350502713</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.381147165399767</v>
+        <v>-3.956294734704713</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.51598450800951</v>
+        <v>-4.285654912970756</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.553560222285711</v>
+        <v>-1.400464840928741</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.622911409608491</v>
+        <v>-0.5138881832349469</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.224680644861451</v>
+        <v>0.8297265683693951</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5632673324687687</v>
+        <v>1.511460778039357</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.125478101512293</v>
+        <v>2.165230126229645</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.7707735463027916</v>
+        <v>0.02282082943317931</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.694282380396551</v>
+        <v>1.021977579700611</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.9517362124308875</v>
+        <v>1.242345956383581</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.07589025102141989</v>
+        <v>0.381048876652109</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.150364963503648</v>
+        <v>1.411734991767588</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>0.4629893864020929</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 52.19</t>
+          <t>X ≈ 52.1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.552269588856213</v>
+        <v>-1.745396780174389</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0179354502342477</v>
+        <v>-0.5515844543355755</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.852891374778764</v>
+        <v>3.951378646834463</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.01189584739279326</v>
+        <v>1.199543508692877</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.933931117027271</v>
+        <v>-3.394907019706125</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.184110133708884</v>
+        <v>-3.957342566272892</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.105302286034657</v>
+        <v>-6.192567894172541</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.381067870621884</v>
+        <v>-6.497912491705726</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9.057146171204899</v>
+        <v>-7.089750379078133</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.957497931211954</v>
+        <v>-5.726899127619674</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.248307324054736</v>
+        <v>-4.734923825591743</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.678602181976714</v>
+        <v>-6.032322899862869</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-6.646909689428568</v>
+        <v>-6.425495510665364</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.153506773025462</v>
+        <v>-5.955334529814962</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-7.532963677450354</v>
+        <v>-7.360089892267148</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-7.662114550114318</v>
+        <v>-7.526336261950163</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-9.238481793275248</v>
+        <v>-9.077464948577017</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-5.032195817690031</v>
+        <v>-4.881241867990362</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-6.974577818060347</v>
+        <v>-6.116425281823609</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.507156468524137</v>
+        <v>-7.35279427942524</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.33027817605835</v>
+        <v>-6.476291979648927</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-10.28382197919423</v>
+        <v>-9.45050884233769</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-12.88704510843863</v>
+        <v>-12.10927185448578</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-12.24345290123025</v>
+        <v>-11.55344334211554</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 55.41</t>
+          <t>X ≈ 55.31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.20913692671899</v>
+        <v>1.823712804085567</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.035158333442226</v>
+        <v>1.575010469135471</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.114744669191502</v>
+        <v>1.148026728768485</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.318321359642667</v>
+        <v>6.301274859376171</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.281383498722377</v>
+        <v>6.030109646663888</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4414421218090681</v>
+        <v>-1.203644516888623</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.233607515495038</v>
+        <v>-2.810063252203733</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.011682964888919</v>
+        <v>-1.467550113266626</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2072294486118835</v>
+        <v>-2.160143138474027</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.116986128530073</v>
+        <v>-3.770726213057436</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5408363063989938</v>
+        <v>0.6045178330393171</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.639110792453344</v>
+        <v>2.792297182488568</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.503313281974705</v>
+        <v>1.684074354588795</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.327983311489604</v>
+        <v>3.902325082648758</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.975988125125568</v>
+        <v>1.580529357022584</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.57528875085999</v>
+        <v>2.962838540119783</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>5.135149513180352</v>
+        <v>4.507466163039624</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3864209121905446</v>
+        <v>-1.387573498508289</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.524385722970877</v>
+        <v>-0.3518228167336375</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.8311413484168284</v>
+        <v>-1.788121180593471</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.016142992091432</v>
+        <v>0.1191018883174095</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.092839403563971</v>
+        <v>-0.781615850189489</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.869974019547392</v>
+        <v>-5.494653324672058</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.4440242357039139</v>
+        <v>-2.354736910207535</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 58.62</t>
+          <t>X ≈ 58.53</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.214444605165937</v>
+        <v>3.760185161841193</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1127195336035882</v>
+        <v>-0.2804548827188285</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.950508683509788</v>
+        <v>-3.422828482577323</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.102541614487521</v>
+        <v>0.4071538875309741</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1405980180852993</v>
+        <v>-1.127014765139187</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.811697017044715</v>
+        <v>-2.868629118015555</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4423785736910801</v>
+        <v>-0.4928489472237345</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.97431219981263</v>
+        <v>-1.423058041799614</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-5.698829335338047</v>
+        <v>-5.086082006742807</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.331067856488566</v>
+        <v>-3.978860125301459</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.429793140227524</v>
+        <v>-3.708515277811578</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.941112902077904</v>
+        <v>2.967739531575809</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.07509485626607</v>
+        <v>3.757818605515496</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.854133974290889</v>
+        <v>3.512105873974853</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.3138794305949375</v>
+        <v>1.569239787066437</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.42169597699597</v>
+        <v>3.395614984254777</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.547329289551968</v>
+        <v>5.196464002943536</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>4.442488585730786</v>
+        <v>5.068258084759208</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.029449149045128</v>
+        <v>4.648791267757218</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.587364141403015</v>
+        <v>4.22943349310016</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.044817973437063</v>
+        <v>3.665379361871736</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>4.226833647247936</v>
+        <v>5.500820763792525</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>6.388100812560253</v>
+        <v>7.657269427552912</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>5.683337741726909</v>
+        <v>6.862507917923217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.84</t>
+          <t>X ≈ 61.75</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.391736612563335</v>
+        <v>-0.376138456728988</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.966265556414797</v>
+        <v>-1.885736670601013</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.457328375433903</v>
+        <v>0.02084681735239968</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9316909756220966</v>
+        <v>0.6909650570411898</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6783140555954219</v>
+        <v>1.048716280615018</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.104597114851913</v>
+        <v>4.364234315214517</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.687483744854262</v>
+        <v>3.571377088356996</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1800918911813412</v>
+        <v>0.7410644860528848</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1375890738003349</v>
+        <v>0.2380259114062611</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.204316300792826</v>
+        <v>-1.82007764644186</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.578903523479596</v>
+        <v>-1.548311007705692</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9146141479994796</v>
+        <v>-0.5621383357458214</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.387968623760024</v>
+        <v>-1.044974256675225</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.552666642258274</v>
+        <v>-2.81467786191331</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-4.860924658922393</v>
+        <v>-4.759157993857109</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.9196756507812296</v>
+        <v>1.492803512350179</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.1366456335852959</v>
+        <v>0.1225740063930303</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.03180492976419202</v>
+        <v>-0.008294348486813874</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.051004988012927</v>
+        <v>-1.065402701638639</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.812211126096777</v>
+        <v>-1.488290564284</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-4.653458592764039</v>
+        <v>-3.326845509767566</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.430603255471759</v>
+        <v>-3.404632827193943</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.156128542989855</v>
+        <v>-3.163734926881581</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-5.829363393615729</v>
+        <v>-5.87634558526149</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 65.06</t>
+          <t>X ≈ 64.95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.30770821565082</v>
+        <v>3.470515704890843</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.503066578799626</v>
+        <v>-0.445148625831493</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6770062116784032</v>
+        <v>-2.424007137988788</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.08325581782563773</v>
+        <v>-0.08734849653401255</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.881519747392545</v>
+        <v>5.517698896397995</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.06724407384687225</v>
+        <v>0.5307558854423107</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.354713066068058</v>
+        <v>1.216405892940983</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.802218211841335</v>
+        <v>2.392217469263763</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3725838513375095</v>
+        <v>1.791352940224797</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.731628070886863</v>
+        <v>6.143807090416502</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.333582848123342</v>
+        <v>-0.9274406236933856</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.279454124323401</v>
+        <v>-4.880392970978818</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.268980690371222</v>
+        <v>-0.8503668996859943</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.225829788679597</v>
+        <v>-1.830876521559389</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.690383750790566</v>
+        <v>-1.036715760222386</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-6.234618956125608</v>
+        <v>-4.901957544426331</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.25067293020377</v>
+        <v>-0.5901051923770311</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-3.826101869319317</v>
+        <v>-2.195264865676549</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-6.551386958983059</v>
+        <v>-4.935757620970179</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-4.158658796073858</v>
+        <v>-3.250491900721052</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-3.230616728745943</v>
+        <v>-2.341260630536937</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.571168572507815</v>
+        <v>-1.679346167617332</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.7672820953198</v>
+        <v>-2.917946482451057</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.372526113249116</v>
+        <v>-1.601752520859513</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 68.28</t>
+          <t>X ≈ 68.17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.637964129320636</v>
+        <v>-4.483942894834222</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-8.991199857643096</v>
+        <v>-7.346674405514612</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.05734866203256</v>
+        <v>-2.688805218057865</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.452001743858652</v>
+        <v>-4.604695682209297</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.117291716298958</v>
+        <v>-4.876903616118575</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.260430906183792</v>
+        <v>-4.720807561667883</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.020120744641552</v>
+        <v>-2.879801213331859</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.285770405917532</v>
+        <v>-1.859558288302459</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4366584932689079</v>
+        <v>0.897758569570648</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.014579158522025</v>
+        <v>2.730257470992605</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.289547614817941</v>
+        <v>3.007517794881885</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.01034380430292</v>
+        <v>2.727585634220752</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.557833706576211</v>
+        <v>2.273223840993005</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.026774543365349</v>
+        <v>6.621321043914243</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.363074581838895</v>
+        <v>4.63958897138918</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.617551352450761</v>
+        <v>3.881050738233405</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>6.839338913459628</v>
+        <v>7.725586923098341</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>6.734498209638602</v>
+        <v>7.603837284129497</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.608107711368369</v>
+        <v>6.505456557598848</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.781530702544458</v>
+        <v>5.403101202134678</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.910125474175665</v>
+        <v>4.841859070190338</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.505420452363815</v>
+        <v>5.431198229664851</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.424190466859358</v>
+        <v>2.37102889997832</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6650646051557842</v>
+        <v>0.2231187079852361</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 71.5</t>
+          <t>X ≈ 71.38</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.215874198098859</v>
+        <v>5.183708374166464</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.59118261318276</v>
+        <v>6.334636183507321</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.15494915089559</v>
+        <v>5.082412082048954</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.440011146181909</v>
+        <v>3.092116666581809</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.689407006998579</v>
+        <v>2.121316918802997</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.583879225677464</v>
+        <v>3.671203740593398</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.3084051721596737</v>
+        <v>-0.6025563104702627</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.539671052846778</v>
+        <v>1.884428250186708</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.582150227396987</v>
+        <v>2.710774482393255</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.728494010074563</v>
+        <v>-0.8704777300013049</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.868652838967591</v>
+        <v>-1.989431645165567</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-5.563406300214204</v>
+        <v>-3.660731101453052</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.562661479635963</v>
+        <v>-2.967086228873526</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.784137153136712</v>
+        <v>-2.520673352347679</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-4.029837241939923</v>
+        <v>-2.495310072077991</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-5.56898774983889</v>
+        <v>-3.343288833470105</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.866025454192091</v>
+        <v>-1.36125950363072</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.970866158013195</v>
+        <v>-1.489299043066396</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.6273152026211051</v>
+        <v>1.525202058053154</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.9779703236591359</v>
+        <v>2.439800856752505</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.692235418774892</v>
+        <v>-0.2284921721923183</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.058861522028053</v>
+        <v>0.397945368065578</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.6340529067659801</v>
+        <v>2.049266992376296</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.860219062769275</v>
+        <v>1.183849983052774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 74.72</t>
+          <t>X ≈ 74.6</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.556868063568039</v>
+        <v>0.7863738352455272</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.563173312648019</v>
+        <v>-4.891991270937439</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.402766866089657</v>
+        <v>-3.804524441101542</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.310464106416077</v>
+        <v>-7.522039656428895</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.644937222528867</v>
+        <v>-7.790902473880664</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-12.24666074102746</v>
+        <v>-11.52596519483912</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.225967651018351</v>
+        <v>-7.631369085498847</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-6.904699715034234</v>
+        <v>-7.143963992409219</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.265840922677761</v>
+        <v>-6.233082997933458</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.0462497221137</v>
+        <v>-3.130442843548565</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6239990713545822</v>
+        <v>-0.5147078326873427</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.3449861966197219</v>
+        <v>-0.7939679162176319</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.616168982061588</v>
+        <v>1.20286233755548</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.192590290044826</v>
+        <v>0.9506110825337473</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.8601913716690106</v>
+        <v>-1.272046442716544</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.069696969696928</v>
+        <v>-2.283468467526873</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-4.403614106674496</v>
+        <v>-5.525351920512364</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-6.908454810495712</v>
+        <v>-7.21994940972813</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-5.092563429571207</v>
+        <v>-5.45262950084507</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-4.105717619603368</v>
+        <v>-4.465449000206178</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-3.048263787569354</v>
+        <v>-3.464838303400917</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.124109748978405</v>
+        <v>-2.76039297008748</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4496350364963533</v>
+        <v>-0.1607549721858845</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.674532710280374</v>
+        <v>2.037792536008475</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 77.94</t>
+          <t>X ≈ 77.81</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-10.0007871520864</v>
+        <v>-8.523311435071641</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-9.579718770777134</v>
+        <v>-7.965831585855803</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.517221117710498</v>
+        <v>-4.558635136026687</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.982019283818339</v>
+        <v>-6.715440008984302</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.815314635068873</v>
+        <v>-9.309047995820926</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.626893527882721</v>
+        <v>-7.596922736475669</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-11.1445029438112</v>
+        <v>-9.921405543809477</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.670404530410096</v>
+        <v>-7.104889455561015</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.128502627614701</v>
+        <v>-4.644173065856151</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.649625147594527</v>
+        <v>-5.434697948594255</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.875776263879452</v>
+        <v>-1.274483800621908</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.652859987791913</v>
+        <v>-6.209271898493128</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.028440690032106</v>
+        <v>-4.226676138372476</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.74993428735938</v>
+        <v>-6.031944057313176</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-3.663581294811941</v>
+        <v>-3.590621820550489</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-6.086238323080472</v>
+        <v>-6.160812225327703</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-9.227674257050332</v>
+        <v>-9.404077723243446</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-2.565597667638485</v>
+        <v>-2.515416266543546</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-4.605345384458516</v>
+        <v>-3.875529160895759</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.666619875242418</v>
+        <v>-2.891608375992767</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-3.457286343960234</v>
+        <v>-3.458948406652787</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-8.044410500858099</v>
+        <v>-9.037810416776615</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-5.514296690631689</v>
+        <v>-6.449945320284975</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>-3.474018487613662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 81.16</t>
+          <t>X ≈ 81.03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.589735598270181</v>
+        <v>-1.224550692085892</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.075867230938577</v>
+        <v>4.010916115977025</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.08233282474886</v>
+        <v>-4.535607713641674</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.829634865010597</v>
+        <v>-2.399324384619007</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.133393954833743</v>
+        <v>-2.66688166201665</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.910921428870168</v>
+        <v>-5.243634123037978</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.06239236233574275</v>
+        <v>0.3538861975025611</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.182629380645906</v>
+        <v>0.05496640112016848</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.10216090172279</v>
+        <v>-1.639562067208622</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.001287021163825841</v>
+        <v>0.3010728281046227</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.07323285976635</v>
+        <v>5.129451287741247</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.788691861081318</v>
+        <v>3.945641075614404</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.7940568757245074</v>
+        <v>1.00129082528661</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3857240656187528</v>
+        <v>-0.1591720329906749</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.103568041168522</v>
+        <v>0.9890452778680654</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.107226107226104</v>
+        <v>1.544998521806171</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.9497679528282887</v>
+        <v>-0.3948498791621162</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.09307019511101089</v>
+        <v>0.3848875757428303</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.930513493505636</v>
+        <v>4.273695186244396</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.232743918858326</v>
+        <v>0.8126150131194265</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>5.536351597046085</v>
+        <v>5.771843686560686</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>8.345121020252371</v>
+        <v>7.54757775462695</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>5.734980348119038</v>
+        <v>5.950024987506232</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>3.736071171818836</v>
+        <v>3.583432664325677</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 84.38</t>
+          <t>X ≈ 84.24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5090442150084797</v>
+        <v>2.145546325712843</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8394305713505901</v>
+        <v>-1.106902601858842</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.922891736484466</v>
+        <v>2.714600039478533</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.207742496037994</v>
+        <v>2.095179941311962</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.283052531592965</v>
+        <v>-2.198106954397225</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.01529123644793629</v>
+        <v>-0.008668308655671808</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.372886817087618</v>
+        <v>3.264636996018311</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.136719342611251</v>
+        <v>3.991166640870553</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.218421143966161</v>
+        <v>5.137036689136231</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.446237208264307</v>
+        <v>3.329798530174848</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.599652992105781</v>
+        <v>1.562774030196181</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.322732939494351</v>
+        <v>2.314264926565833</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.237590271074474</v>
+        <v>2.193673285758145</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.055994273733454</v>
+        <v>2.956625888067151</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.435916108360097</v>
+        <v>3.317791117270311</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.113636363636303</v>
+        <v>5.900797604343381</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.938052559992286</v>
+        <v>4.779035097020426</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.7082118561709834</v>
+        <v>1.593582129173036</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-4.284230096238026</v>
+        <v>-3.316778029301467</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-5.139050952936543</v>
+        <v>-4.142969505695234</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-6.723263787569245</v>
+        <v>-5.746148848359134</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-5.757443082311738</v>
+        <v>-4.807691431185091</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.399635036496349</v>
+        <v>-2.516360376512772</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-6.600467289719568</v>
+        <v>-5.771282875956871</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 87.59</t>
+          <t>X ≈ 87.45</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.151855856413178</v>
+        <v>1.216842111484972</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.22267271225718</v>
+        <v>11.40784488797372</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3872920877969293</v>
+        <v>2.867531350440025</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3289547631516001</v>
+        <v>1.215403785704538</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.541344422903848</v>
+        <v>5.132270573928757</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.680081025856346</v>
+        <v>3.209258503150011</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.390026040918691</v>
+        <v>-3.825660539413192</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.664944654165893</v>
+        <v>-4.118961848975459</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.622908667000274</v>
+        <v>-5.029843864295088</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.245098735841495</v>
+        <v>-2.700167277426019</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.022561508330291</v>
+        <v>-3.476038494902582</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.19881488772792</v>
+        <v>-1.661055638750661</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2249689830433184</v>
+        <v>-0.7076212132709259</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.546348662536502</v>
+        <v>-3.040448605019513</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.041179266254751</v>
+        <v>1.497679168953283</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.574960127591645</v>
+        <v>-2.13980950545222</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.449017472272871</v>
+        <v>0.8903364293423337</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>2.396808347399173</v>
+        <v>0.7532192764747592</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.560068149376157</v>
+        <v>-0.09346512218661474</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-3.516243935392772</v>
+        <v>-5.174141884233052</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-6.164053261253542</v>
+        <v>-6.831526680277776</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-6.239899222662643</v>
+        <v>-5.871175923180594</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.912792931233163</v>
+        <v>-4.962072155411654</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.2745327102802833</v>
+        <v>-0.8688920007649443</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 90.81</t>
+          <t>X ≈ 90.66</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2178379884261261</v>
+        <v>1.430583068628614</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.7191465706643</v>
+        <v>4.047478789844924</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.123804487591798</v>
+        <v>5.710288099574413</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.321359918019645</v>
+        <v>6.966510478802554</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.160783925519439</v>
+        <v>3.898479452112674</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.183835492204814</v>
+        <v>6.933844430659782</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.419420048737827</v>
+        <v>6.209092088756762</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.188778844208151</v>
+        <v>4.991580968051586</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.105446751458061</v>
+        <v>9.893452275207459</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.373509730274534</v>
+        <v>7.178446531622129</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.561845442518781</v>
+        <v>9.338378163334809</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.16016007451177</v>
+        <v>11.93241317359816</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.03040642228526</v>
+        <v>10.75500579363207</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.85218951079753</v>
+        <v>8.611260707276237</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.20514687759087</v>
+        <v>7.971835462843451</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.799533799533805</v>
+        <v>8.539464064054584</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>9.627155124094784</v>
+        <v>9.391929188043157</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>13.36846826642744</v>
+        <v>13.16464954409102</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>13.58435964735173</v>
+        <v>13.40881984461114</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>16.65582084193517</v>
+        <v>16.58132366470979</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>15.15173621243067</v>
+        <v>15.08798519619977</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>15.07589025102163</v>
+        <v>16.02917028880521</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.4272880404267</v>
+        <v>14.31202046035809</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>14.31299424874194</v>
+        <v>16.11066577979408</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 94.03</t>
+          <t>X ≈ 93.88</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.722271457451527</v>
+        <v>6.559669604911065</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.387494659101712</v>
+        <v>5.354101832390299</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.964374933215751</v>
+        <v>4.185596051981179</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1496251241591651</v>
+        <v>-3.038244383062576</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.836146945887478</v>
+        <v>4.277296649890452</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.287105314819648</v>
+        <v>1.658673431216918</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.092197457418017</v>
+        <v>5.644658438771955</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.56489315297516</v>
+        <v>8.218720805813859</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.690120779698134</v>
+        <v>7.369751114384663</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.005202497939891</v>
+        <v>6.573699619165325</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.270748241161847</v>
+        <v>6.776983976583736</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.991998837713851</v>
+        <v>6.483164357815909</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.117929630547444</v>
+        <v>2.454814101321645</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.637115520736103</v>
+        <v>5.959035465673445</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.825824365240742</v>
+        <v>7.217067941549864</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>8.420211287183776</v>
+        <v>7.787921375314269</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.368862957545744</v>
+        <v>6.713523129038585</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>8.18145344638512</v>
+        <v>7.570799964679694</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>8.39734482730946</v>
+        <v>7.817978177092556</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.749328251956371</v>
+        <v>6.153941440567039</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>5.289350891329782</v>
+        <v>4.674631945584096</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.296073737260137</v>
+        <v>3.64577032687864</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.405410835063293</v>
+        <v>6.802026171380298</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.412147389179459</v>
+        <v>5.669013390683112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 97.25</t>
+          <t>X ≈ 97.09</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.377203212310654</v>
+        <v>6.555710479112697</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.002022373556805235</v>
+        <v>2.195732483029808</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.572669871653908</v>
+        <v>4.976439775738633</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.87579379136605</v>
+        <v>4.423372459819738</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.546398632906367</v>
+        <v>7.189115946754178</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.725535041943232</v>
+        <v>8.320481878874197</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.965958601194352</v>
+        <v>10.54703405223061</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.653738430124847</v>
+        <v>8.116241983576145</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.72140456129542</v>
+        <v>9.316940426605505</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.942511956205081</v>
+        <v>7.487454280930237</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.210176284279392</v>
+        <v>4.738055109945435</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.931426880831395</v>
+        <v>3.447705946462889</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.7816674796856091</v>
+        <v>-3.769456866500128</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.586767552494898</v>
+        <v>-1.931154185576702</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>4.58238075482469</v>
+        <v>0.03375554585822016</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.176767676767682</v>
+        <v>0.63314536701332</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-1.017755520815868</v>
+        <v>-6.757595181976484</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-2.132697234738046</v>
+        <v>-7.350517938366785</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.113497176489311</v>
+        <v>-3.327009079821131</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.320545006659358</v>
+        <v>-0.4115687403430925</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.808301868996359</v>
+        <v>3.81084734452071</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.732455907587259</v>
+        <v>4.368761444416336</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.97662758976626</v>
+        <v>1.420906567992596</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1.890694326441988</v>
+        <v>1.258767573703146</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 5.514</t>
+          <t>X &gt; 5.502</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3348</v>
+        <v>3373</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09590495976836877</v>
+        <v>-0.11110979143902</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02903637468979525</v>
+        <v>-0.01717233812207297</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2340644508691696</v>
+        <v>-0.2244831917891545</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2180459113719095</v>
+        <v>-0.1684916387553557</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1808311712465098</v>
+        <v>-0.1328861178211582</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2742329125758829</v>
+        <v>-0.2544018477455694</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3163149728840224</v>
+        <v>-0.3251476202877726</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2506705748969935</v>
+        <v>-0.2593911121500483</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2814180314537609</v>
+        <v>-0.2623373896731067</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2045411208804921</v>
+        <v>-0.2150278011738465</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.24055215150387</v>
+        <v>-0.2507350926419747</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3533663174233652</v>
+        <v>-0.3627677385955366</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2387468024594881</v>
+        <v>-0.2491835089301588</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.2338143284250975</v>
+        <v>-0.2436805218890825</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1891955985211027</v>
+        <v>-0.1988549593516993</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2027124643334375</v>
+        <v>-0.1819540307476331</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2295455522780259</v>
+        <v>-0.1796720907297882</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1974232064407602</v>
+        <v>-0.1175473437923671</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1427274617812557</v>
+        <v>-0.03359727766058995</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.2365052091020772</v>
+        <v>-0.09766069699791302</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2839546261249595</v>
+        <v>-0.1145362534529042</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.2226172116649749</v>
+        <v>-0.05361838221878656</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1990527731341558</v>
+        <v>-0.059122187572477</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.2571279826706316</v>
+        <v>-0.1444280158030082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 8.732</t>
+          <t>X &gt; 8.716</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3298</v>
+        <v>3321</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1910128259959976</v>
+        <v>-0.175371415329991</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1781555573514026</v>
+        <v>-0.1358389530360284</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2734560449249273</v>
+        <v>-0.2363992739719976</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2158611539587696</v>
+        <v>-0.1699215686172977</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1124628675840853</v>
+        <v>-0.05614158352945253</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4081512817883635</v>
+        <v>-0.4083424489299858</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3656203276696672</v>
+        <v>-0.3779763149824547</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2948028799595761</v>
+        <v>-0.3064594314219846</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.326653827077358</v>
+        <v>-0.2814838198725056</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.206768343576897</v>
+        <v>-0.1910451069585051</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2172601234790363</v>
+        <v>-0.2015541432441452</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2369262368594178</v>
+        <v>-0.2209958066017492</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.164009496397945</v>
+        <v>-0.1482211381662495</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.09517880445844185</v>
+        <v>-0.07868474107070256</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.009653894663848916</v>
+        <v>0.00757263915159001</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.06255843370180258</v>
+        <v>-0.01400721719259224</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1179862700632412</v>
+        <v>-0.04006410256410931</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05349113010821327</v>
+        <v>0.05520764416211676</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.06174296332849138</v>
+        <v>0.0770368812545712</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1597454815051478</v>
+        <v>0.008648902882747223</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1390847509137458</v>
+        <v>0.06058679249755983</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1059279307965895</v>
+        <v>0.09359353026546557</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08613094434721802</v>
+        <v>0.08423422244327128</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2348669258627396</v>
+        <v>-0.09015962715278647</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 11.95</t>
+          <t>X &gt; 11.93</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3236</v>
+        <v>3258</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.01676848935334618</v>
+        <v>-0.01806157705780009</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.06431464428580824</v>
+        <v>0.1022201743606885</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.02581616641526097</v>
+        <v>0.05445243197405603</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05527819759335273</v>
+        <v>-0.01902424790865354</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1796789678614203</v>
+        <v>0.2243431309175321</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1253597660903978</v>
+        <v>-0.1376487820099044</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.06705014739772963</v>
+        <v>-0.09132114367266553</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.09925913212620685</v>
+        <v>-0.1041041358695693</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1324485659410541</v>
+        <v>-0.0810483845360892</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05700988947062768</v>
+        <v>-0.03460437866739596</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07288561203630195</v>
+        <v>-0.05051128547513173</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1183498970621102</v>
+        <v>-0.09553371910859454</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.08415337144712254</v>
+        <v>-0.06101280729642156</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.009760680319416792</v>
+        <v>0.01467620522695512</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.02836603131844129</v>
+        <v>0.05456177704981968</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.06772409670066537</v>
+        <v>-0.008865811994120065</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.05998166757483858</v>
+        <v>0.02783626850433762</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.02307541506070976</v>
+        <v>0.09689530660309487</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.004751025992156599</v>
+        <v>0.1456647242928852</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1390509529366071</v>
+        <v>0.04117657399185504</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1384768162818659</v>
+        <v>0.07442498746554804</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.07234940308588023</v>
+        <v>0.140201204238835</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1192056265488688</v>
+        <v>0.06459703563375996</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3002509732795673</v>
+        <v>-0.1407334907797022</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 15.17</t>
+          <t>X &gt; 15.14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3157</v>
+        <v>3180</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1520392573580835</v>
+        <v>0.1471794007199207</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1028279420084814</v>
+        <v>-0.0674578915192825</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.08242003131321241</v>
+        <v>0.08497746249908289</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1719656002933192</v>
+        <v>-0.1634597581978312</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1086809367339328</v>
+        <v>0.1238338840668192</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2401234413035738</v>
+        <v>-0.2508147488344079</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.06659465907353734</v>
+        <v>-0.09015592914663983</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.09267877952784431</v>
+        <v>-0.0958087941817638</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.09620014029415103</v>
+        <v>-0.04401182563691464</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.062686332233163</v>
+        <v>-0.03959922689290352</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.08578936402793857</v>
+        <v>-0.06254655484639216</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1254421562789432</v>
+        <v>-0.1019143495838648</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.157083939835033</v>
+        <v>-0.1333138904034641</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.04376819115444874</v>
+        <v>-0.01837920431096052</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.07489273501828819</v>
+        <v>0.1018720184933031</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1016085020824349</v>
+        <v>-0.0395611399270237</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.2167620207073071</v>
+        <v>-0.1249378987553627</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2395961320258166</v>
+        <v>-0.1137574573273312</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1946507160988062</v>
+        <v>-0.03771478748730317</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2737657056519822</v>
+        <v>-0.08726298739570382</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2280106230123451</v>
+        <v>-0.007917933080904049</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.09504991991857281</v>
+        <v>0.1241407722845551</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1816173037541091</v>
+        <v>0.00926697921080688</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2702883223455359</v>
+        <v>-0.1028007388888525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 18.39</t>
+          <t>X &gt; 18.36</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3072</v>
+        <v>3092</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1754530159341314</v>
+        <v>0.1551224680308749</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1095611489218697</v>
+        <v>-0.1229387085090039</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1527000812584234</v>
+        <v>0.1336212088920234</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.02429850178351245</v>
+        <v>0.02353412262398535</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.04667990471016736</v>
+        <v>0.06951939088479264</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2521052045292436</v>
+        <v>-0.2558621156573224</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.01221554163222294</v>
+        <v>-0.03598806732941995</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05783829377033811</v>
+        <v>0.03120003120002934</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.08552029903752612</v>
+        <v>0.1130669701359679</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1737094883647643</v>
+        <v>0.2046005988428092</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.04525072513862938</v>
+        <v>0.07674768431304813</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.02019511119767259</v>
+        <v>0.0119334141553793</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.05414488336045764</v>
+        <v>-0.0531557191530041</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.003533773234565274</v>
+        <v>0.007632934687237025</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.1111838785645176</v>
+        <v>0.1184155039447887</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.0432900432900496</v>
+        <v>0.0860712719400567</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.1037764970609274</v>
+        <v>-0.03100798644723568</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.0593320034780831</v>
+        <v>0.04885276808995798</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.01905026740035254</v>
+        <v>0.1210148080244267</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.04043803572810845</v>
+        <v>0.1286096574824285</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.05417523682093872</v>
+        <v>0.2587247775633372</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.09540879363707688</v>
+        <v>0.2998016182600338</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.06616611361967983</v>
+        <v>0.07779136619857496</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2202589563862887</v>
+        <v>-0.09751218738243494</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 21.61</t>
+          <t>X &gt; 21.57</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2985</v>
+        <v>3001</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2745144327193216</v>
+        <v>0.2500198436018906</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1602290434045699</v>
+        <v>-0.1946282971698849</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1011854297237136</v>
+        <v>0.07436093979246294</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.02659698025550483</v>
+        <v>-0.02118799634600776</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1564855048497691</v>
+        <v>0.166983575379767</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.223403927592372</v>
+        <v>-0.206059632136558</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.07166972929754678</v>
+        <v>0.04443429823061962</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1602472141876845</v>
+        <v>0.1560182534660441</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1017010516542243</v>
+        <v>0.170223779565184</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.01503814255072911</v>
+        <v>0.08956085871536601</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.02225322167061705</v>
+        <v>0.1154826484685145</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.02972510733473399</v>
+        <v>0.1234561626575754</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.07271218490253517</v>
+        <v>-0.009480382899994311</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.040331245144543</v>
+        <v>0.02745066297815413</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.1229568565230323</v>
+        <v>0.1954349200371297</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.10263847968492</v>
+        <v>0.2116300793886765</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.211902876727919</v>
+        <v>-0.0720301418439675</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1631522361057876</v>
+        <v>0.0142552086616945</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.06112530248100256</v>
+        <v>0.1486315151977422</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1555001555684754</v>
+        <v>0.08341151657172219</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.07584076213422719</v>
+        <v>0.2013537762704942</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.002237756880319353</v>
+        <v>0.2792339506335395</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1385834624842985</v>
+        <v>0.07641282623178824</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.09397650244994082</v>
+        <v>0.1006429769375288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 24.83</t>
+          <t>X &gt; 24.78</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2892</v>
+        <v>2906</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.4039033168606281</v>
+        <v>0.3561420817389163</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.03470311059343345</v>
+        <v>-0.06076338597589626</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1801608257620941</v>
+        <v>0.1209310210244539</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.03731486547451368</v>
+        <v>0.007324991846878959</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08031227171512256</v>
+        <v>0.07376411576942843</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3869915146392913</v>
+        <v>-0.4532968062762635</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04629396124996532</v>
+        <v>0.002151786209580564</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.07799987186879775</v>
+        <v>0.02459324841255039</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1539223154914851</v>
+        <v>0.2062293988028046</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.02084061001267656</v>
+        <v>0.1488534369202412</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.01512386081197548</v>
+        <v>0.1325208711466033</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.03616389162787215</v>
+        <v>0.1497643674279985</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.06731604370726529</v>
+        <v>0.01453508533789716</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.06111300785250506</v>
+        <v>0.02647117259560616</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2325701269871558</v>
+        <v>0.3250771075994621</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.226645335340983</v>
+        <v>0.3578626240334017</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.04429752604906412</v>
+        <v>0.2057050291795406</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1672357972391865</v>
+        <v>0.3679171768896765</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1965557414131496</v>
+        <v>0.4310964719211938</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.05848417721774268</v>
+        <v>0.3224747045002019</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1932156455451093</v>
+        <v>0.4972580798712016</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.2556344611840515</v>
+        <v>0.5802396849267666</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1153148425219754</v>
+        <v>0.3973317778675138</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.06014820129005471</v>
+        <v>0.3245302657123403</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 28.05</t>
+          <t>X &gt; 28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2776</v>
+        <v>2787</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.4869346525407465</v>
+        <v>0.5037190829410889</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.295732872137819</v>
+        <v>0.2578122472372186</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.4370390205224766</v>
+        <v>0.4291431007823618</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1907038094070828</v>
+        <v>0.2288977647192354</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2856383907004485</v>
+        <v>0.3454964873650113</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1375892494763988</v>
+        <v>-0.1392811365834348</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2031684557215385</v>
+        <v>0.2266978259563217</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3556820648090948</v>
+        <v>0.3701455717153124</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.361275492237084</v>
+        <v>0.4828083866192472</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1626598879881058</v>
+        <v>0.3141075291475701</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1495694942562693</v>
+        <v>0.3212841462408207</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1788748555269635</v>
+        <v>0.3153600797907501</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.04646012146765344</v>
+        <v>0.150375784519909</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.1700565313448408</v>
+        <v>0.2806873055972119</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.3960167553765714</v>
+        <v>0.5138299694432575</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2929783269589095</v>
+        <v>0.4526244486957935</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1445873321744813</v>
+        <v>0.3342355643044641</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.385104023617366</v>
+        <v>0.6164781397363583</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2626561528621068</v>
+        <v>0.5300320379345038</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1829392043074165</v>
+        <v>0.4793239782458301</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.3462607081079341</v>
+        <v>0.6858213201427077</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.3064378014538747</v>
+        <v>0.6680527331418205</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.2567050211405402</v>
+        <v>0.5745742623666672</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1808727679172648</v>
+        <v>0.5056508997839586</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 31.26</t>
+          <t>X &gt; 31.21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2656</v>
+        <v>2663</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6555881586130639</v>
+        <v>0.5991643166655223</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1331940994752472</v>
+        <v>0.09206345111090286</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6463945626393794</v>
+        <v>0.5911006925029056</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2336281604574353</v>
+        <v>0.2225790907096012</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4982129224317404</v>
+        <v>0.5440358759834112</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.02776648246525326</v>
+        <v>-0.04529917473492873</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3635118505299459</v>
+        <v>0.3748890464119299</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4980583795104607</v>
+        <v>0.4432422125591131</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5395455614251645</v>
+        <v>0.6299080524399443</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3670051199102389</v>
+        <v>0.4529660962557287</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3033536926537792</v>
+        <v>0.4479123760080626</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3623153586241656</v>
+        <v>0.4919652091259934</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1244475916965015</v>
+        <v>0.2215079052835947</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2260533976792374</v>
+        <v>0.2945844036718057</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.341626100846895</v>
+        <v>0.4205080296318968</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.395015544395477</v>
+        <v>0.5175636452205765</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1708219835511287</v>
+        <v>0.3236189138576719</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.3517181868718069</v>
+        <v>0.5127423779156999</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.2139828458237361</v>
+        <v>0.4122721499701711</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.159845045056116</v>
+        <v>0.3866805962895015</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.3173988630331124</v>
+        <v>0.5916311059224881</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.2415529016240114</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1395215900096716</v>
+        <v>0.3922183052617925</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.1766411440153135</v>
+        <v>0.4402218605816444</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 34.48</t>
+          <t>X &gt; 34.43</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2527</v>
+        <v>2535</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.051581908650057</v>
+        <v>0.9636428643658874</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.04645810714566068</v>
+        <v>-0.02677807792105114</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9349374808276139</v>
+        <v>0.8737002339804718</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3402799913533272</v>
+        <v>0.2421130821941944</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6748365219606214</v>
+        <v>0.6718840956998733</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.03372699827882286</v>
+        <v>-0.03325126381928101</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6024723206976148</v>
+        <v>0.5263201944046045</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.718582642506064</v>
+        <v>0.5742025734185674</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7600698244207678</v>
+        <v>0.7638681338586224</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7757976815072993</v>
+        <v>0.7749920784503601</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6949677337638605</v>
+        <v>0.7561350096631045</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7316757435650771</v>
+        <v>0.7771605461360025</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3812132330775313</v>
+        <v>0.3921599789310193</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5782740862878768</v>
+        <v>0.5993419404747513</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.4965161873178019</v>
+        <v>0.5695024935342659</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6013930776963932</v>
+        <v>0.7218963705662631</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.530720148560647</v>
+        <v>0.6415142276422685</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.7263277982000247</v>
+        <v>0.8863381498561012</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.5311613628367624</v>
+        <v>0.6914042374697331</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1483963044473597</v>
+        <v>0.3781153022407366</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.381257383780131</v>
+        <v>0.661418056206152</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.2658388066211259</v>
+        <v>0.5705075174293768</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.2633052088538719</v>
+        <v>0.5223563297215748</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.3061908028802875</v>
+        <v>0.5810219696072849</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 37.7</t>
+          <t>X &gt; 37.64</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2403</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8782241966841156</v>
+        <v>0.8186795968170628</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1288537001585155</v>
+        <v>0.07670000377544284</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.929640621276782</v>
+        <v>0.8889757241244567</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.258145971651615</v>
+        <v>0.2552341288714288</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4613273067328691</v>
+        <v>0.5170881425546483</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1394345337037421</v>
+        <v>-0.1527661803435123</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4153166165684183</v>
+        <v>0.4399109009797186</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.5931582398087087</v>
+        <v>0.5485553872650542</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.593186051905839</v>
+        <v>0.6764842969491625</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5665390325857658</v>
+        <v>0.648907279281147</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.6554847138850874</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5203899014821118</v>
+        <v>0.6099195830738751</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1681038568376252</v>
+        <v>0.2233359353673876</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3036029744053295</v>
+        <v>0.3310343042834276</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.08535570985443286</v>
+        <v>0.1294855968854378</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1648545253196403</v>
+        <v>0.2178329556210343</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2634403179204909</v>
+        <v>0.3459975795297368</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4328585727130232</v>
+        <v>0.5283731592634666</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.0916361546282829</v>
+        <v>0.2277921308435324</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.2374979856598429</v>
+        <v>-0.07309263417551648</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.07682984538950421</v>
+        <v>0.2982597580979984</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1238600610882656</v>
+        <v>0.1231737945733826</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.01584394203109696</v>
+        <v>0.1836070317586689</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.03316774981428949</v>
+        <v>0.2126461474717516</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 40.92</t>
+          <t>X &gt; 40.85</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7696332359130125</v>
+        <v>0.7293872213227104</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3038520707509704</v>
+        <v>0.265520490239588</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5252216680081858</v>
+        <v>0.4929536769269021</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1440642291638028</v>
+        <v>-0.1430405009571629</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1314990100793025</v>
+        <v>0.1916890660054023</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4238928824259247</v>
+        <v>-0.3924409722859679</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.06047038727697895</v>
+        <v>-0.01053954947073521</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.09799939067735863</v>
+        <v>0.07686781880329363</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2268228171335593</v>
+        <v>0.291980686639107</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2399333419704277</v>
+        <v>0.3057932597281834</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3829886173201231</v>
+        <v>0.4723686638174769</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1479073361428718</v>
+        <v>0.2209820446098192</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1455604075691426</v>
+        <v>-0.08266653204432828</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.122410668327646</v>
+        <v>-0.08688182896670327</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.31758039513646</v>
+        <v>-0.2625663809874297</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2217739264088152</v>
+        <v>-0.1563085184601007</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.1110506771031439</v>
+        <v>-0.01572069116360808</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1164904849091926</v>
+        <v>0.1836047715707139</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.2106019584679686</v>
+        <v>-0.1013064372685974</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5234136336199171</v>
+        <v>-0.3865308994483101</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2514189146508059</v>
+        <v>-0.0519456515447061</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4587285044560474</v>
+        <v>-0.2326171969037034</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3595386298355265</v>
+        <v>-0.1823035850495813</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3039072546626613</v>
+        <v>-0.1430230586197325</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 44.14</t>
+          <t>X &gt; 44.07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2186</v>
+        <v>2182</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.713918048446736</v>
+        <v>0.7378832901043353</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2423423444881649</v>
+        <v>0.2642897513039273</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4915097979651577</v>
+        <v>0.5123278898495087</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2214442214775829</v>
+        <v>-0.1256116495780191</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1012383419956677</v>
+        <v>0.008666275896409559</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5526670487391527</v>
+        <v>-0.4719228867758147</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.412623028571133</v>
+        <v>-0.3107207460030708</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.09803921568627061</v>
+        <v>-0.06919310197999806</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.01095239856864794</v>
+        <v>0.104273148323422</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.03692535904739458</v>
+        <v>0.08235644363232097</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3565846364122365</v>
+        <v>0.4263931602336584</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.2146341385729897</v>
+        <v>0.2672572119544441</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1789337650364331</v>
+        <v>-0.1828861669684656</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.008130375081307761</v>
+        <v>0.006132842916912296</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.09146864745922301</v>
+        <v>-0.147086812632466</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.01764217517641953</v>
+        <v>-0.06093123211060458</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.1040149476882775</v>
+        <v>0.1362161184711468</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.346389796451362</v>
+        <v>0.3960426163496678</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.004680484898230475</v>
+        <v>0.08907983666180996</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3853150578466398</v>
+        <v>-0.2639814378363781</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.2416764133698521</v>
+        <v>-0.02659553311713836</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3632680289418104</v>
+        <v>-0.1203664489668554</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.2717759331111722</v>
+        <v>-0.07859148758190315</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2103712238458826</v>
+        <v>-0.0303094003788047</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 47.36</t>
+          <t>X &gt; 47.28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8693371736679367</v>
+        <v>0.8705643485140371</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3405739543675921</v>
+        <v>0.3336778813843608</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6969292991290317</v>
+        <v>0.6793717523346956</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1779617006368213</v>
+        <v>0.2324593692393648</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1331508595153537</v>
+        <v>0.2478808605658358</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4073320329517713</v>
+        <v>-0.3226346120005843</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3063418225647254</v>
+        <v>-0.1962811247182685</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1913924164843408</v>
+        <v>0.2262475104376165</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.03889317744850729</v>
+        <v>0.1601899991711875</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.09041979045178294</v>
+        <v>0.1400841877539776</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.4614726430889746</v>
+        <v>0.5373373797613041</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3282130553538778</v>
+        <v>0.3858949795642488</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.07798988277516372</v>
+        <v>0.1247729550514265</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3223466451448687</v>
+        <v>0.3424117757622156</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.1300908656415913</v>
+        <v>0.1265832394456083</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.3166070613860796</v>
+        <v>0.3278184791698848</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4061040663090409</v>
+        <v>0.447460462287097</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.6707381890182305</v>
+        <v>0.6843728730922081</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.283701161868386</v>
+        <v>0.2948077452996429</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.03564462690254544</v>
+        <v>0.002244001741004809</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.005750810970852172</v>
+        <v>0.1460723734797469</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1674187514114962</v>
+        <v>-0.04639164328473555</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2335766423357626</v>
+        <v>-0.115390328261924</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2120852945858047</v>
+        <v>-0.1510146736372846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 50.58</t>
+          <t>X &gt; 50.49</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1930</v>
+        <v>1921</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.829437124294131</v>
+        <v>0.8524094663051187</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2879419796910838</v>
+        <v>0.3479710897532726</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.40031052755932</v>
+        <v>0.4376410002711992</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.157604732193505</v>
+        <v>-0.05134858219783212</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.183317685360926</v>
+        <v>-0.0683751814491842</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8232248842764633</v>
+        <v>-0.7387425061646482</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5099022503373689</v>
+        <v>-0.4479920468358358</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.09043927648578887</v>
+        <v>0.0743884404690931</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.08024687183718981</v>
+        <v>0.1506110419836091</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.340922927066849</v>
+        <v>0.2852730938170112</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7183417423553848</v>
+        <v>0.6609207247605369</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6979902717239241</v>
+        <v>0.6729632219964046</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5050607630073358</v>
+        <v>0.4163525173829257</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5733768826727612</v>
+        <v>0.4576357894632821</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.308394121810629</v>
+        <v>0.168925702059056</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.4164313946922675</v>
+        <v>0.2946366325648171</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.4688871879915411</v>
+        <v>0.3771179114799423</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.7060529615250957</v>
+        <v>0.586471326424622</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.3519961559209293</v>
+        <v>0.3127891811742032</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.08291969214213424</v>
+        <v>-0.06517201304342279</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.05551767357966497</v>
+        <v>0.07359619178854615</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1831771064913568</v>
+        <v>-0.07465033460799475</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.3232101660300302</v>
+        <v>-0.2163507216214953</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.243602004745533</v>
+        <v>-0.1916073418439481</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 53.8</t>
+          <t>X &gt; 53.71</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1791</v>
+        <v>1783</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.09189230750345</v>
+        <v>1.053473550440934</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3116812107126492</v>
+        <v>0.4175945698902694</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2099650570046023</v>
+        <v>0.1656859833190225</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1689132386074021</v>
+        <v>-0.148164683455775</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1077684492016715</v>
+        <v>0.189090546918429</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4847753869726716</v>
+        <v>-0.4896304431837635</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.07957882445991515</v>
+        <v>-0.003375408062723295</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7479152638939297</v>
+        <v>0.583069051035622</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7894024458086335</v>
+        <v>0.7109979607197303</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.9073553666540946</v>
+        <v>0.7506010616006691</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.181415008816018</v>
+        <v>1.078546382611691</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.348099903809008</v>
+        <v>1.191936572987188</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.060127146529723</v>
+        <v>0.9458954382301954</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.095452163600761</v>
+        <v>0.9539845859077047</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.916964045929717</v>
+        <v>0.7516537738577185</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.043409555679489</v>
+        <v>0.8999615116691686</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.222278750468419</v>
+        <v>1.108880353817497</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.151400019208452</v>
+        <v>1.009659448033851</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9206135665202666</v>
+        <v>0.8103952360781363</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.4932773552711041</v>
+        <v>0.4988727837937574</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5090784793206993</v>
+        <v>0.5805421074690642</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.6007367055162902</v>
+        <v>0.651019028300972</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.6518725011920878</v>
+        <v>0.7041333593293047</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.6877097063719404</v>
+        <v>0.6877720008579473</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.01</t>
+          <t>X &gt; 56.92</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1673</v>
+        <v>1662</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.013090834062069</v>
+        <v>0.9973971667520019</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2606529378602289</v>
+        <v>0.3333302354686865</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.07561718238532222</v>
+        <v>0.0941677942700565</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6970027081791343</v>
+        <v>-0.6177087175608662</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2571368561440792</v>
+        <v>-0.2361581360353568</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4878317678987329</v>
+        <v>-0.4376474691053645</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1722004551321703</v>
+        <v>0.2009622749343123</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7293112060831533</v>
+        <v>0.7323620226845904</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.830464259119573</v>
+        <v>0.9200280888800521</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.191200134395721</v>
+        <v>1.079771097842325</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.226596292070781</v>
+        <v>1.11305748640126</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.186510373109648</v>
+        <v>1.075424157975363</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.9583363730793195</v>
+        <v>0.8921531705530583</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7969233677544452</v>
+        <v>0.739334044327876</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7717370038824285</v>
+        <v>0.6913084395839846</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.8648311067665873</v>
+        <v>0.7497761203078426</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.9462962340308749</v>
+        <v>0.8614502196924292</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.2598655720507</v>
+        <v>1.184187237764057</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.8780283217735914</v>
+        <v>0.8950091857714142</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5866912267804665</v>
+        <v>0.6653747511167794</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4027822375353054</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.5660277286067696</v>
+        <v>0.7553203642199549</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.900275304208968</v>
+        <v>1.15542890010196</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.70489732474541</v>
+        <v>0.9092783656226473</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.23</t>
+          <t>X &gt; 60.14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6768852530808829</v>
+        <v>0.709186060287557</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2761888766163736</v>
+        <v>0.3973596464689848</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2884005461087753</v>
+        <v>0.4610571068714009</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.8859905201368576</v>
+        <v>-0.7246212949691184</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2989068990783323</v>
+        <v>-0.1432249195773494</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2437798692103499</v>
+        <v>-0.1840500479233711</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.236743431078601</v>
+        <v>0.2733399240232188</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.013245236160721</v>
+        <v>0.9572131523351004</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.516169464878331</v>
+        <v>1.546579108822108</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.666127882447633</v>
+        <v>1.607482129093867</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.61058963403606</v>
+        <v>1.616038831239408</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.002242340014568</v>
+        <v>0.8780198299652042</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.7360347886495404</v>
+        <v>0.5932099989323874</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5808754903176592</v>
+        <v>0.4500814348564077</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8198211215526499</v>
+        <v>0.5997235747635585</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.5963096309631055</v>
+        <v>0.4737650228728398</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.5681164085171062</v>
+        <v>0.4092261904761898</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.92562709175008</v>
+        <v>0.7790050962502661</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5470666893190526</v>
+        <v>0.5034186297104384</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.2715611122329236</v>
+        <v>0.2935759321856324</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.1253161331704575</v>
+        <v>0.2958343450611878</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.1815705680625541</v>
+        <v>0.2602748075868035</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.3239448842434101</v>
+        <v>0.4771638085339873</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.182062432869543</v>
+        <v>0.2882437877414503</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.45</t>
+          <t>X &gt; 63.35</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1360</v>
+        <v>1348</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.7978909643376539</v>
+        <v>0.835592550770933</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7565844521213734</v>
+        <v>0.663269232359184</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.7125492622246483</v>
+        <v>0.5123278898495087</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8808156156186868</v>
+        <v>-0.8894929991721057</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4095628012987476</v>
+        <v>-0.282048931765928</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7361696159350473</v>
+        <v>-0.713783464104857</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.04076686915775696</v>
+        <v>-0.1107786477871713</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.148373116756815</v>
+        <v>0.9823877373546139</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.703433299405191</v>
+        <v>1.698984785375735</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.104398767902815</v>
+        <v>2.006686049538303</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.084988123931218</v>
+        <v>1.984586994974123</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.219298148216161</v>
+        <v>1.045753384873692</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9765469397606239</v>
+        <v>0.7840074233614587</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.048938349447575</v>
+        <v>0.8303241719430758</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.463082040812317</v>
+        <v>1.22386630938778</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5596931846013433</v>
+        <v>0.3550787893061269</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.6169741286196739</v>
+        <v>0.4426122386223881</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.026839307151427</v>
+        <v>0.8707009514607478</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.7280248057228178</v>
+        <v>0.6861374346227507</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6207529686320186</v>
+        <v>0.5011078609287551</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.6664420947836334</v>
+        <v>0.7177636753342682</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.5905961333745324</v>
+        <v>0.6871223585219539</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.71801202232718</v>
+        <v>0.901215070744847</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.8627680043980206</v>
+        <v>1.006226377920584</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 66.67</t>
+          <t>X &gt; 66.56</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1224</v>
+        <v>1213</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5190223808584165</v>
+        <v>0.5423405921508362</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.6736419936015778</v>
+        <v>0.7866298348783403</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8669443148805414</v>
+        <v>0.8391252754704226</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9879346637791642</v>
+        <v>-0.97876711941624</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9974608622644539</v>
+        <v>-0.9275278738946469</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8104946761670746</v>
+        <v>-0.852293614301793</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1958201952939689</v>
+        <v>-0.2584867376456259</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.075723661747418</v>
+        <v>0.8254817078346406</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.851305460301589</v>
+        <v>1.688704735165814</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.81248440090458</v>
+        <v>1.546248011188304</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.575940454159493</v>
+        <v>2.308679104224005</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.052492845164998</v>
+        <v>1.705299764131794</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.337161120886378</v>
+        <v>0.9659039885810969</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.523912587017271</v>
+        <v>1.126500671219944</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.813467128768202</v>
+        <v>1.475456234694761</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.314616755793224</v>
+        <v>0.9401570292516226</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.9356015796000605</v>
+        <v>0.557547814207652</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.566054993425951</v>
+        <v>1.211925506541981</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.536848335134586</v>
+        <v>1.311822374857734</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.151798720266008</v>
+        <v>0.9186395738905944</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.099448630731359</v>
+        <v>1.058215679697504</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.941903322917014</v>
+        <v>0.9504968441186534</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.216378035399067</v>
+        <v>1.326266026788915</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.222245128581037</v>
+        <v>1.296479594190416</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 69.89</t>
+          <t>X &gt; 69.78</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.233804697152998</v>
+        <v>1.257000485309725</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.013234026936878</v>
+        <v>1.943060098813675</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.410869574006163</v>
+        <v>1.34074251136758</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2305895522146599</v>
+        <v>-0.4632160714108267</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2878284927285009</v>
+        <v>-0.365987631827025</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1937128173089349</v>
+        <v>-0.3022506707497286</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.334245648290036</v>
+        <v>0.1142237009877363</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.541642374381901</v>
+        <v>1.207252931390855</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.04738210968565</v>
+        <v>1.80116506567888</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.645868476360391</v>
+        <v>1.377900150142679</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.477031182589172</v>
+        <v>2.209315034271704</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.919730247107744</v>
+        <v>1.55994650011727</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.167970222962857</v>
+        <v>0.7800232939349527</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7611903251606549</v>
+        <v>0.3452220683227338</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.46007967713328</v>
+        <v>1.025565421850253</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.9954193093727923</v>
+        <v>0.5220073587655065</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.1173161258837041</v>
+        <v>-0.4616366541939527</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.8496847243881049</v>
+        <v>0.3030943592578765</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.972552849498463</v>
+        <v>0.5733677970857016</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.7873056362106752</v>
+        <v>0.2810183819274599</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.7098757473144275</v>
+        <v>0.5202400187140697</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.4479832742774121</v>
+        <v>0.3134103005993722</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.187574265829227</v>
+        <v>1.177716880035995</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.483835035861766</v>
+        <v>1.449094936767615</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 73.11</t>
+          <t>X &gt; 72.99</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.6326571600723057</v>
+        <v>0.650921658986185</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.473094036936168</v>
+        <v>1.265229877045748</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.9966134494436361</v>
+        <v>0.7632239471971829</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7847166383751656</v>
+        <v>-1.011973950535776</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5863190767344122</v>
+        <v>-0.7498976820329588</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6130281043122423</v>
+        <v>-0.91554472119617</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4312625280367186</v>
+        <v>0.2248571375388551</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.541939972172536</v>
+        <v>1.102732393054971</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.117615188275273</v>
+        <v>1.660768829620793</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.306237973777236</v>
+        <v>1.724932388164902</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.434998470640025</v>
+        <v>2.857382456532676</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.04941146035442</v>
+        <v>2.365746738620516</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.033087000335911</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.598332910214111</v>
+        <v>0.7875667962957777</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.288857284830627</v>
+        <v>1.569004900260921</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.986405814028942</v>
+        <v>1.118607423219267</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.5676921031756663</v>
+        <v>-0.3227818230852293</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.426448829761327</v>
+        <v>0.579746384399229</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.2140746860604</v>
+        <v>0.4264542481102964</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.7585222090905148</v>
+        <v>-0.05218500005641147</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.072507090375026</v>
+        <v>0.6358052047017893</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.6754619854969732</v>
+        <v>0.3003624967078622</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.271135841447979</v>
+        <v>1.043195014870427</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.837701875162601</v>
+        <v>1.490034918754027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 76.33</t>
+          <t>X &gt; 76.21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4898557225729618</v>
+        <v>0.629228813607952</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.251256482792812</v>
+        <v>2.251316996584038</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.67636936964346</v>
+        <v>1.494754899673779</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2235879765878934</v>
+        <v>0.03062169214824451</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5043203153846321</v>
+        <v>0.3777285582755638</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.184504750557231</v>
+        <v>0.7837281667643055</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.768906251623726</v>
+        <v>1.483042169475546</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.847044991827488</v>
+        <v>2.423451738520228</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.258445860548612</v>
+        <v>2.924979651940326</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.978748433587334</v>
+        <v>2.502527160456971</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.869330887093277</v>
+        <v>3.397427181287959</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.467276921376474</v>
+        <v>2.871779224325998</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.09750572998275</v>
+        <v>1.383288103139236</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.506513166729754</v>
+        <v>0.7614550379701441</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.775422281199546</v>
+        <v>2.024003034634362</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>2.458609581600925</v>
+        <v>1.663454381762463</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.33581729011172</v>
+        <v>0.5104166666666572</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.71428931805815</v>
+        <v>1.828877993294796</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.188524333098663</v>
+        <v>1.367997294916506</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.510104382868917</v>
+        <v>0.654605073107561</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.7092145807867</v>
+        <v>1.29252869212808</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.262540436435692</v>
+        <v>0.7905465374178249</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.537015148917746</v>
+        <v>1.236009199430519</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.708401684322403</v>
+        <v>1.402310811072681</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 79.55</t>
+          <t>X &gt; 79.42</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.55384315205476</v>
+        <v>2.374533035203008</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.578948359604645</v>
+        <v>4.199632116658904</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.288421935942388</v>
+        <v>2.649080026601638</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.83800478965599</v>
+        <v>1.317032857379218</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.534662694689835</v>
+        <v>2.224906669942612</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.311599382262138</v>
+        <v>2.381840275940696</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.30956220279657</v>
+        <v>3.657764180867737</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.916306510255886</v>
+        <v>4.240417701956154</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.105286317539317</v>
+        <v>4.368346611640263</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.069833768346491</v>
+        <v>4.01608209866945</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.196400785139687</v>
+        <v>4.288317113273784</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.655114508535341</v>
+        <v>4.603451135133845</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.499504064098105</v>
+        <v>2.45305605910319</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.130932562282787</v>
+        <v>2.056893003587241</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.042267659320153</v>
+        <v>3.094659726238682</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.139770485924338</v>
+        <v>3.155469185216596</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.4141373726155</v>
+        <v>2.401018449727587</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.753083651042836</v>
+        <v>2.657294466266968</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.525188049718643</v>
+        <v>2.367888976430265</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.528601907023955</v>
+        <v>1.330834965053107</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.725700709472122</v>
+        <v>2.198591141895598</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.093641730311539</v>
+        <v>2.664722713367816</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.924329460545074</v>
+        <v>2.7016491754123</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.55263921915612</v>
+        <v>2.33218141307443</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 82.77</t>
+          <t>X &gt; 82.63</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.729135434561044</v>
+        <v>3.071129885646016</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.48859947390757</v>
+        <v>4.236157794210229</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.446740983340803</v>
+        <v>4.039664750519705</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.686666545049903</v>
+        <v>2.036327807443399</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.747036630966846</v>
+        <v>3.171704411612147</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.806603166104374</v>
+        <v>3.857738546710756</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.081774901062175</v>
+        <v>4.297224435712607</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.025203944965298</v>
+        <v>5.050505050505045</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.415731266496067</v>
+        <v>5.531167646256172</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.991855730075628</v>
+        <v>4.735116151036834</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.218794953389384</v>
+        <v>4.125516950473617</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.812645898981529</v>
+        <v>4.730769211169871</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.991403552893296</v>
+        <v>2.734042878551548</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.770324676446705</v>
+        <v>2.485808817118439</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.796055968499907</v>
+        <v>3.502198006568484</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.691142191142191</v>
+        <v>3.467173184586358</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.207574704514371</v>
+        <v>2.942154255319139</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.452384350343536</v>
+        <v>3.097115154755507</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.269674332666462</v>
+        <v>1.999023258401721</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.582394268508615</v>
+        <v>1.431135600911247</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>2.214673275367758</v>
+        <v>1.506993875186225</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.138827313958657</v>
+        <v>1.719653995704753</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.413302026440711</v>
+        <v>2.072931276297339</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.337469773217435</v>
+        <v>2.090003751541921</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 85.98</t>
+          <t>X &gt; 85.85</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.382213683213728</v>
+        <v>3.26588391018727</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.563160155304175</v>
+        <v>5.360402606398296</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.754071923883252</v>
+        <v>4.318474461953528</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.783256269220381</v>
+        <v>2.023944603570833</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.963189067113362</v>
+        <v>4.301577952833206</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.779086070820803</v>
+        <v>4.671277516278096</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.426424598670486</v>
+        <v>4.514493376385808</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.406074789137541</v>
+        <v>5.273402720211223</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.657205576922266</v>
+        <v>5.614097587342137</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.303577112625817</v>
+        <v>5.030812049569612</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.948705937177678</v>
+        <v>4.664749191833515</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.718174563079785</v>
+        <v>5.239231067149454</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.546794466873564</v>
+        <v>2.847743205017842</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.116071984556946</v>
+        <v>2.386743186137913</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.272050562141551</v>
+        <v>3.540999456160499</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>4.605933282403882</v>
+        <v>2.955109044203638</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.261932111812946</v>
+        <v>2.555652212705205</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.207511576059005</v>
+        <v>3.41347676751365</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.793150856142994</v>
+        <v>3.117532423059437</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>4.139660531657228</v>
+        <v>2.603995026813266</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>4.017282430918087</v>
+        <v>3.033143211810732</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.731352435895545</v>
+        <v>3.093086764486351</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.585659081150709</v>
+        <v>3.03857398849383</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.140078928767764</v>
+        <v>3.744113952989615</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 89.2</t>
+          <t>X &gt; 89.06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.688995818505205</v>
+        <v>3.790706605222738</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.401339439003557</v>
+        <v>3.811466436185526</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.842901541805034</v>
+        <v>4.690105667627293</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.55926689409003</v>
+        <v>2.231036802152396</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.317717259239096</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.551803864184642</v>
+        <v>5.045745601384475</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.874096017990631</v>
+        <v>6.650663589151762</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.166565201509798</v>
+        <v>7.679076479076471</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.469832488136547</v>
+        <v>8.340338722093911</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.435136707388011</v>
+        <v>7.010953893541242</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.185636140125858</v>
+        <v>6.749855574812244</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.692227050813983</v>
+        <v>7.006606953674279</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.736604250973578</v>
+        <v>3.758381502890174</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.777305479239033</v>
+        <v>3.776814108123737</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>6.077648391824617</v>
+        <v>4.064356695935643</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.1471009305655</v>
+        <v>4.26007455828443</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.963315027183825</v>
+        <v>2.982190860215049</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.908343089766845</v>
+        <v>4.094850620804259</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>5.599300087489063</v>
+        <v>3.939967761623812</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>6.048613089058136</v>
+        <v>4.596215380051284</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.555935687496309</v>
+        <v>5.559788906242133</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.217622534486175</v>
+        <v>5.389110450155819</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>5.704695672165059</v>
+        <v>5.087785807368796</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>5.103929035739704</v>
+        <v>4.925646813079332</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 92.42</t>
+          <t>X &gt; 92.27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.992246411747892</v>
+        <v>4.69913151364765</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.657469613398078</v>
+        <v>3.720623945343036</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.737436175877875</v>
+        <v>4.297431674953295</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.146784314708519</v>
+        <v>0.4083261794417723</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.127540604751168</v>
+        <v>4.162072068646467</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.314506790848547</v>
+        <v>4.319005674644551</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.420255948684819</v>
+        <v>6.820626959115124</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.66003011544254</v>
+        <v>8.713508713508702</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.982092836925588</v>
+        <v>7.742536524291715</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.209177160889098</v>
+        <v>6.946485029072377</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.044387882187714</v>
+        <v>5.753518578475244</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.765638478739717</v>
+        <v>5.110636257703582</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.124490800372797</v>
+        <v>1.065341209849883</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.622836384357868</v>
+        <v>1.916008247317869</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.278876397168695</v>
+        <v>2.560346000748481</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.151241658461871</v>
+        <v>2.612913314554035</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>3.212270369859858</v>
+        <v>0.5150462962962976</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>3.107429666038676</v>
+        <v>0.603833676746703</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.601299386313187</v>
+        <v>0.2953529976060594</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.066123535631384</v>
+        <v>-0.01692063894935814</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.3286315192899</v>
+        <v>1.892332221050893</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.891774727555898</v>
+        <v>1.293691191505872</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.805238609713037</v>
+        <v>1.537325676784249</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>1.646373865515031</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 95.64</t>
+          <t>X &gt; 95.49</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.572170638047318</v>
+        <v>3.516196801301163</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.237393839697503</v>
+        <v>2.682054671479648</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.941386624986045</v>
+        <v>4.368537040176307</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.636716629211946</v>
+        <v>2.599664253132794</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.667790061990111</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.629904177081578</v>
+        <v>6.01045148373742</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.633103422185307</v>
+        <v>7.568310647975295</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.72175588275768</v>
+        <v>9.028096086919604</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.17152708834102</v>
+        <v>7.979554408368422</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.99032738863589</v>
+        <v>7.183502913149084</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.897523125472368</v>
+        <v>5.102796751282831</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.618773722024372</v>
+        <v>4.237979502693889</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.128747749842809</v>
+        <v>0.1819109146548854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.315952897064854</v>
+        <v>-0.6545584408958689</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.62639229883623</v>
+        <v>-0.4004093072918948</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.030303030303031</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.5154335123731713</v>
+        <v>-3.425960578842322</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1846452866860986</v>
+        <v>-3.825780691506985</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-1.159230096237962</v>
+        <v>-4.487550665894624</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.9723842862699357</v>
+        <v>-3.94036998580237</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.056498117192604</v>
+        <v>0.1233391863168194</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>1.980652155783503</v>
+        <v>-0.201766530366946</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.4694125825512643</v>
+        <v>-1.809983896940416</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.7968958611481938</v>
+        <v>-2.589406841847165</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 98.86</t>
+          <t>X &gt; 98.7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.44466594329068</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.905197618897368</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.293692874816948</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.407177764588525</v>
+        <v>-0.1969022903278912</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.49269467532357</v>
+        <v>2.817174172813054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.720745991433219</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.68891135827435</v>
+        <v>10.28860028860028</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>6.130814912570102</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.05893213951489</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>5.606998431955098</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>5.330416477483801</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>8.931080311372703</v>
+        <v>5.644095788604467</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>4.362175347969576</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>2.254756688070181</v>
+        <v>-1.000578368999413</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.04940711462450764</v>
+        <v>-2.488963791173546</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.715226473035699</v>
+        <v>1.179534313725483</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>2.610385769214517</v>
+        <v>1.046650208563882</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-4.420099661455353</v>
+        <v>-6.091828740760924</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-7.131804576125013</v>
+        <v>-8.818418766290179</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-3.32652465713452</v>
+        <v>-4.974098561788566</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-3.402370618543621</v>
+        <v>-6.519849319037959</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-3.127895906061568</v>
+        <v>-6.276214833759582</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-4.653003521603679</v>
+        <v>-7.908942063343169</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 5.514</t>
+          <t>X &lt; 5.502</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3524355059846727</v>
+        <v>0.4971807218998165</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.354472981216205</v>
+        <v>9.242486620008243</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.192243599454628</v>
+        <v>6.68321071519587</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.407177764588525</v>
+        <v>4.958377212777705</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.94197003764242</v>
+        <v>9.463136905732306</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.06857207838976</v>
+        <v>11.56660561813727</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.891809908998994</v>
+        <v>8.363134450090968</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.711106052558357</v>
+        <v>6.245736502236888</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.43444105703913</v>
+        <v>7.967246879160072</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.95279310286649</v>
+        <v>13.48776637396413</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.153307412707868</v>
+        <v>5.645384363919838</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.747694334650859</v>
+        <v>6.2066883827395</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>5.508936493852204</v>
+        <v>5.969923865852891</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.826277150138843</v>
+        <v>3.285835368360978</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>9.716953603735043</v>
+        <v>10.17935412363343</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.567756267851479</v>
+        <v>6.000000000000007</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.39047473926589</v>
+        <v>8.73641173034823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 8.732</t>
+          <t>X &lt; 8.716</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.210392555989515</v>
+        <v>3.715437788018441</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.8756157576397</v>
+        <v>3.469530952314571</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.74338183257565</v>
+        <v>5.440643302035888</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.377535251149446</v>
+        <v>3.71396363142069</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5624059356269626</v>
+        <v>0.646189044566718</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.724578733294592</v>
+        <v>9.535001799731596</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.658512402345416</v>
+        <v>7.913473506507131</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.699628688684776</v>
+        <v>5.955660501115041</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.581452005053258</v>
+        <v>6.083589410799149</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.287527925655432</v>
+        <v>2.808199072604602</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.561587567817355</v>
+        <v>3.080434087208936</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.123174298823137</v>
+        <v>3.630298413729371</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.159676097513241</v>
+        <v>1.688960015286867</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2579249521590867</v>
+        <v>-0.2121666081297064</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.080890614329029</v>
+        <v>-2.54721355199824</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-1.159463252186846</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.9005875739978251</v>
+        <v>0.3895488980716237</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.884925398730914</v>
+        <v>-1.396227769073455</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.6690340178065881</v>
+        <v>-1.181765541927682</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.038820195522781</v>
+        <v>1.512159746106512</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.496274027556751</v>
+        <v>0.9447152447257778</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.5800919316938646</v>
+        <v>0.043106441778761</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.01423050972213957</v>
+        <v>-0.5397053539345933</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>4.140078928767764</v>
+        <v>3.430387056734617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 11.95</t>
+          <t>X &lt; 11.93</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3799775482145691</v>
+        <v>-0.3511373664084729</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-1.916875809803777</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.609295134725819</v>
+        <v>-1.567291836829042</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6918143715598575</v>
+        <v>-0.2592857784927673</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.831952670194099</v>
+        <v>-4.559836653262259</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.5551798261907663</v>
+        <v>1.310962992688822</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.453963357189167</v>
+        <v>-0.02759728041345966</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1329821405627669</v>
+        <v>0.2109605370474839</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.7269555103227745</v>
+        <v>0.3388894467315922</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.5984463535590194</v>
+        <v>-1.000640309357308</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3243867113970964</v>
+        <v>-0.7284052947529744</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5018362608455078</v>
+        <v>0.0819692725148613</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.06883961816529194</v>
+        <v>-0.4894445840663408</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.394890870302497</v>
+        <v>-1.82463516723859</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.053034167883055</v>
+        <v>-2.506789549123646</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.3536748702494492</v>
+        <v>-0.8585290085648438</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.4875920072269224</v>
+        <v>-0.9624094202898519</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1.144918898893422</v>
+        <v>-1.638771786321023</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-1.481513705814393</v>
+        <v>-1.967787820044819</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.9152768555348487</v>
+        <v>0.420711668492423</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.9252168754141223</v>
+        <v>0.3967454279812586</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2556014616855791</v>
+        <v>-0.7653736157131519</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.5713594386417711</v>
+        <v>0.02173913043478137</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.810444312490326</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 15.17</t>
+          <t>X &lt; 15.14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.310048634344518</v>
+        <v>-2.23176530488962</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7772277992448338</v>
+        <v>0.722744631674253</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.801475660432544</v>
+        <v>-1.458322005328689</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9076235520638747</v>
+        <v>1.561339832455431</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.469992015540434</v>
+        <v>-1.918792567351254</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.73984590886711</v>
+        <v>2.261012776956996</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3423891076838785</v>
+        <v>-0.06078679252762242</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.01788908765652764</v>
+        <v>0.01597215337672964</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02359809425817616</v>
+        <v>-0.2377783262521334</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3647021971629343</v>
+        <v>-0.6521504321584999</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.09064255500101126</v>
+        <v>-0.3799154175541659</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3998388107817732</v>
+        <v>0.106861406600494</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>0.5186868464016285</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.5597867479055552</v>
+        <v>-0.874585382970416</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.98716081471688</v>
+        <v>-2.320098543481429</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1456876456876444</v>
+        <v>-0.2320769674098528</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.550232047171718</v>
+        <v>1.190760178117046</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.830006727965916</v>
+        <v>1.439555462268416</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.276667339659468</v>
+        <v>0.8906589107882468</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>1.868604134473173</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>1.301159633092439</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>-0.3007204461147452</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.119595732734417</v>
+        <v>0.7062728177895892</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.197609633357303</v>
+        <v>1.689171991439053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 18.39</t>
+          <t>X &lt; 18.36</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.916709182397483</v>
+        <v>-1.711640812617645</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.6220772376435093</v>
+        <v>1.013726323191179</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.965367098743812</v>
+        <v>-1.502151178453921</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.6668268653129843</v>
+        <v>-0.5219935008779046</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.289973659699342</v>
+        <v>-0.9254330188586195</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.361466341363759</v>
+        <v>1.674317029955908</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9780057887460458</v>
+        <v>-0.5493364108482339</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.383552409841592</v>
+        <v>-1.139971139971145</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.631920300390654</v>
+        <v>-1.583470801715613</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.404835976427144</v>
+        <v>-2.665236582649229</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.261211116873916</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6703953029306078</v>
+        <v>-0.9552978082304833</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3442820074678892</v>
+        <v>-0.35590421139554</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.8552159563782382</v>
+        <v>-0.8898525585429411</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.80321432642257</v>
+        <v>-1.857721226142274</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.208827404479578</v>
+        <v>-1.296417207322612</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1065308208617921</v>
+        <v>0.0282738095238031</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>-0.3903245813520826</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.6519837194263758</v>
+        <v>-0.7472909256348785</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.465137909458349</v>
+        <v>-0.5327044805758945</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.297539149888138</v>
+        <v>-1.385863267670921</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.663240183761012</v>
+        <v>-1.746740075340483</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2293451814238878</v>
+        <v>-0.07453416149068204</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.144097927671687</v>
+        <v>1.191898272791292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 21.61</t>
+          <t>X &lt; 21.57</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.160209300220117</v>
+        <v>-1.973120001653193</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8188966361634229</v>
+        <v>1.267646211466435</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.180233349828789</v>
+        <v>-0.7639483864267689</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5201896576010512</v>
+        <v>-0.105155823882221</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.771311937928644</v>
+        <v>-1.386301126785554</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.8346704764138551</v>
+        <v>0.9350880050125951</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.18530098507852</v>
+        <v>-0.9937808552926839</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.795627478298144</v>
+        <v>-1.752216037930339</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.394948716898334</v>
+        <v>-1.62428712824623</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7821830996322774</v>
+        <v>-1.286551775392994</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8385058028642547</v>
+        <v>-1.467831500017695</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8857737248307629</v>
+        <v>-1.517656084874474</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.157083939835033</v>
+        <v>-0.591731875794629</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3781628162816233</v>
+        <v>-0.8399659372277384</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.499269076825144</v>
+        <v>-1.975635058341815</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.367845117845121</v>
+        <v>-1.867845778751189</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.8130525599922223</v>
+        <v>0.295847505668938</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4767303746895593</v>
+        <v>-0.06379396910718071</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.2333041703120458</v>
+        <v>-0.7563612204194499</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.4165046026189501</v>
+        <v>-0.08826003613144451</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1260415653470801</v>
+        <v>-0.6557045375121788</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.6648504897191501</v>
+        <v>-1.184381798696485</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.3040686672073605</v>
+        <v>-0.03371783496006486</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.003245067497402943</v>
+        <v>-0.4226141988640464</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 24.83</t>
+          <t>X &lt; 24.78</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.425893842403923</v>
+        <v>-2.156305101493224</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4175714773248558</v>
+        <v>0.285540510259608</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.379871853870931</v>
+        <v>-0.8688306341661587</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.7795050477977341</v>
+        <v>-0.2452952920235631</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.011259633253914</v>
+        <v>-0.6039254347812033</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.540021294499866</v>
+        <v>2.081566496906859</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.8209548562561366</v>
+        <v>-0.5791871571169054</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.9928781817382415</v>
+        <v>-0.697540436346415</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.412882092222006</v>
+        <v>-1.502447347557826</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6706462531069874</v>
+        <v>-1.365663021881645</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4774474010088952</v>
+        <v>-1.27999517145642</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7561968044568914</v>
+        <v>-1.370009961748607</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1715789851649987</v>
+        <v>-0.6192304374083335</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.202904540928472</v>
+        <v>-0.6808973346623333</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.809814441924594</v>
+        <v>-2.295887537442916</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.784687482030932</v>
+        <v>-2.294285011160568</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.780084694909732</v>
+        <v>-1.278762437810954</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.454185360780258</v>
+        <v>-1.971348035509862</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.617800621222152</v>
+        <v>-2.130020136722294</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.8616948492047882</v>
+        <v>-1.355732199126003</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.593994337853935</v>
+        <v>-2.109743864685839</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.939318874453683</v>
+        <v>-2.558040714999329</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.173444560305867</v>
+        <v>-1.754704737183644</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.8683244325767703</v>
+        <v>-1.543709403114903</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 28.05</t>
+          <t>X &lt; 28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.264700324441137</v>
+        <v>-2.330505515989387</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.448824524339216</v>
+        <v>-1.13299486882206</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.192784065107247</v>
+        <v>-2.003713987894507</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.287887302836161</v>
+        <v>-1.145523319613211</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.693156683572013</v>
+        <v>-1.642895321686773</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1190317379170835</v>
+        <v>0.2762799525295137</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.337493407385878</v>
+        <v>-1.434832594054349</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.99327845871823</v>
+        <v>-2.045096548913349</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.020936318697281</v>
+        <v>-2.375182906404817</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.157785083269069</v>
+        <v>-1.797188600097428</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.10593161376832</v>
+        <v>-1.830297096943482</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.229401514110727</v>
+        <v>-1.801535539964391</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6444890468053615</v>
+        <v>-1.084366588712882</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.176126929463123</v>
+        <v>-1.637944161596373</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.144829233254875</v>
+        <v>-2.625442054931803</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.705721814417466</v>
+        <v>-2.216809791837335</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.063241435866992</v>
+        <v>-1.557331424936393</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.09975915832171</v>
+        <v>-2.606246064449131</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.573308771186213</v>
+        <v>-2.086440325852976</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.231183458112582</v>
+        <v>-1.719182125068805</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.929009129184216</v>
+        <v>-2.439298382174726</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.759257493923968</v>
+        <v>-2.361789148404824</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.549946562976096</v>
+        <v>-2.118154663126447</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.223127196115882</v>
+        <v>-1.974950145965529</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 31.26</t>
+          <t>X &lt; 31.21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.41504066181907</v>
+        <v>-2.205047110276205</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.6164507851667906</v>
+        <v>-0.3446560127940543</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.502905574008111</v>
+        <v>-2.169664447315242</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.204317187509403</v>
+        <v>-0.9041720640027648</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.117380967718482</v>
+        <v>-2.005938324716034</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3013952926794303</v>
+        <v>-0.11322875758988</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.650750964900048</v>
+        <v>-1.677541539053365</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.117248062015499</v>
+        <v>-1.912023221394215</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.264537498962156</v>
+        <v>-2.425942835458507</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.660143048739549</v>
+        <v>-1.938297283181051</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.443080966262947</v>
+        <v>-1.92280167807607</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.648087085311666</v>
+        <v>-2.071013927797694</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8078983668274731</v>
+        <v>-1.131990769253598</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.159867295630079</v>
+        <v>-1.380224830686707</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.556230488498599</v>
+        <v>-1.80563980307241</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.747183880691736</v>
+        <v>-2.014554012750814</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9648706511770655</v>
+        <v>-1.219846491228068</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.593271564422324</v>
+        <v>-1.73783971063871</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.11560007878596</v>
+        <v>-1.266638073993583</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.9287542688179329</v>
+        <v>-1.052051628934599</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.471300436783963</v>
+        <v>-1.619496130315333</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.20851341870317</v>
+        <v>-1.437919242771258</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.856984117861181</v>
+        <v>-1.0659150527432</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.986965318628954</v>
+        <v>-1.356423751782344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 34.48</t>
+          <t>X &lt; 34.43</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.087749768299219</v>
+        <v>-2.830688064364708</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2657678763443485</v>
+        <v>0.04918573443114127</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.863753825557779</v>
+        <v>-2.573414273828988</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.298628056837089</v>
+        <v>-0.8004650293494322</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.240165230580558</v>
+        <v>-2.005797465559695</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4355992422337778</v>
+        <v>-0.1375143105097933</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.03623409313473</v>
+        <v>-1.813653591464984</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.364600347411262</v>
+        <v>-1.947972400012105</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.484987070576992</v>
+        <v>-2.37131140653527</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.526283632487377</v>
+        <v>-2.505841402305869</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.301965907263948</v>
+        <v>-2.454113554184445</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.406604465986248</v>
+        <v>-2.510188342172832</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.40210695837429</v>
+        <v>-1.420008794794498</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.959132083421096</v>
+        <v>-1.999003605951977</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.721418718067731</v>
+        <v>-1.909382905146835</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.022888459058663</v>
+        <v>-2.230107552258822</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.82085934743592</v>
+        <v>-1.892973631018009</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.373628382724064</v>
+        <v>-2.466872069145431</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.821790753199515</v>
+        <v>-1.811395509033837</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.7390882802975653</v>
+        <v>-0.825033981284669</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.393616531130327</v>
+        <v>-1.502732065906855</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.067607506825937</v>
+        <v>-1.247133838137771</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.063776450637761</v>
+        <v>-1.224006519342311</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.18614144702299</v>
+        <v>-1.496399096873226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 37.7</t>
+          <t>X &lt; 37.64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.18170314456038</v>
+        <v>-2.012990016829526</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4215830159687357</v>
+        <v>-0.2000168174029824</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.392200465686066</v>
+        <v>-2.169664447315242</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9070847851335557</v>
+        <v>-0.6979500946197419</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.384262452802787</v>
+        <v>-1.30466209290536</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.02956407053800092</v>
+        <v>0.1535265812115725</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.274375821437246</v>
+        <v>-1.313985786448626</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.693847800833659</v>
+        <v>-1.56579531579532</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.695858919316478</v>
+        <v>-1.769638820414912</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.629139428234112</v>
+        <v>-1.795719189551477</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.594345139253683</v>
+        <v>-1.812223347228183</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.522859926076258</v>
+        <v>-1.703819738658098</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.6794536546826251</v>
+        <v>-0.7975376501415852</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.9988609480417026</v>
+        <v>-1.045771711574695</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.4770632426724148</v>
+        <v>-0.572969404335602</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.6693036560293137</v>
+        <v>-0.6853901208383562</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.9015492099192812</v>
+        <v>-0.8855169233237135</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.301375164477925</v>
+        <v>-1.210893810006006</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.4955132820786758</v>
+        <v>-0.4189532382981582</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.281303029364274</v>
+        <v>0.3731115513229142</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4578999724267234</v>
+        <v>-0.3868257315785257</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.01683513291136762</v>
+        <v>0.01924370026793554</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2407680414224558</v>
+        <v>-0.2183537682554331</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3566309978064055</v>
+        <v>-0.3804927625448968</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 40.92</t>
+          <t>X &lt; 40.85</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1135</v>
+        <v>1163</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.640847113431967</v>
+        <v>-1.535794960390703</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7119163399802133</v>
+        <v>-0.5406703159512176</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.232458291823228</v>
+        <v>-1.06546889752812</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01987206943934439</v>
+        <v>0.1862879437049045</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5287050793298391</v>
+        <v>-0.4698855196093206</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.580473929801137</v>
+        <v>0.592229306358746</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1417755450013516</v>
+        <v>-0.2403235353117594</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4576898817880277</v>
+        <v>-0.4109578851846933</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7166686442572399</v>
+        <v>-0.7504036109528016</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7388679087519492</v>
+        <v>-0.8585789238849557</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.028564282396417</v>
+        <v>-1.188235568781906</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5551149273150813</v>
+        <v>-0.6909568181801191</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.04185181490036172</v>
+        <v>-0.08615847991292469</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.003480137117392701</v>
+        <v>-0.0764389729883348</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.3928581118749719</v>
+        <v>0.2732209185573922</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1963838738882657</v>
+        <v>0.1466487550898634</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.02540672530361121</v>
+        <v>-0.04321617942104439</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.4817412779824508</v>
+        <v>-0.3480693301544449</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.1735174140139364</v>
+        <v>0.2963155109208344</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.7997305350540245</v>
+        <v>0.9408245699093101</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2571843670879943</v>
+        <v>0.3733800685285757</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.6739553345748064</v>
+        <v>0.7281401605027753</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.4736044001233637</v>
+        <v>0.5418520318516684</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.3626384371526186</v>
+        <v>0.3797130375622046</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 44.14</t>
+          <t>X &lt; 44.07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1231</v>
+        <v>1260</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.355361949037416</v>
+        <v>-1.375566050411628</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5245805730979924</v>
+        <v>-0.47623072469775</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.036132920652136</v>
+        <v>-0.9785078551298838</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1434994827669982</v>
+        <v>0.1305628685030982</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.06657087999506217</v>
+        <v>-0.1009113247717082</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7294096511689858</v>
+        <v>0.653973449485747</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4868766247467065</v>
+        <v>0.299436352413835</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.0675168792197951</v>
+        <v>-0.1189161252552751</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2219473207787672</v>
+        <v>-0.3425055813689468</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3025672400360548</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.871066657979668</v>
+        <v>-0.9803031553464834</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6183339549638163</v>
+        <v>-0.7013295542622302</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.08639334311593672</v>
+        <v>0.08854023304891001</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2156571932496831</v>
+        <v>-0.239058907749282</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.03116766274661131</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1984419089682206</v>
+        <v>-0.04244895335435928</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.4133307058647233</v>
+        <v>-0.3050595238095255</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8420580493620236</v>
+        <v>-0.6760388670663602</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2213083688425499</v>
+        <v>-0.06475124309519487</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.4513674006396471</v>
+        <v>0.6260256781542637</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.2003585787191966</v>
+        <v>0.2966764148687702</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.4165228544279245</v>
+        <v>0.4596091310087189</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.2529623661010518</v>
+        <v>0.3064182194617047</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.1445570807109178</v>
+        <v>0.1442792251722409</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 47.36</t>
+          <t>X &lt; 47.28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1362</v>
+        <v>1394</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.391209958134432</v>
+        <v>-1.36871368463234</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5987175936989999</v>
+        <v>-0.5075064596775221</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.198526681743012</v>
+        <v>-1.081771562922327</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4902333438918731</v>
+        <v>-0.4213441502285562</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4216305386834236</v>
+        <v>-0.4429964392097503</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3888176262297733</v>
+        <v>0.3258600505976332</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2412597870135755</v>
+        <v>0.07199501363279381</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5057418621613792</v>
+        <v>-0.5505319258900983</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2767949433611321</v>
+        <v>-0.3822419230673759</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3506548858183223</v>
+        <v>-0.4205143034936683</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9116052180689351</v>
+        <v>-1.009111426622482</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7098342520734491</v>
+        <v>-0.7835413007494481</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.3268822154166244</v>
+        <v>-0.3919771771672131</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6943739761970278</v>
+        <v>-0.711947250078083</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.4008335256077515</v>
+        <v>-0.3897974712744769</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6849239096676882</v>
+        <v>-0.6175895787101879</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.8188410466451614</v>
+        <v>-0.721469990435196</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.216507519133991</v>
+        <v>-0.9978261185523252</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.634583927375111</v>
+        <v>-0.3529478225399814</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1549123487394368</v>
+        <v>0.148582668430052</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.2145641538696665</v>
+        <v>0.011554235915888</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.04656473782512194</v>
+        <v>0.2950717713494058</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.144935763210178</v>
+        <v>0.3234982221945089</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.1130055443479208</v>
+        <v>0.3048312508605591</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 50.58</t>
+          <t>X &lt; 50.49</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1487</v>
+        <v>1521</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.149152761272497</v>
+        <v>-1.158564023995645</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4516877415690104</v>
+        <v>-0.4552002304811325</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6564905988699863</v>
+        <v>-0.6285775676027114</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.001430535515162035</v>
+        <v>-0.007357613205371649</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03328210082812433</v>
+        <v>0.01546556447611636</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8579120666279252</v>
+        <v>0.798825548959833</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4576333849612766</v>
+        <v>0.3686963760370006</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3162356009563183</v>
+        <v>-0.2925770642306205</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3034662909224366</v>
+        <v>-0.3244894678820032</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6372237932139342</v>
+        <v>-0.5578590718551695</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.127431852659868</v>
+        <v>-1.037126673708471</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.100521605241298</v>
+        <v>-1.050723749810267</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8459467812430859</v>
+        <v>-0.7191990362288223</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9330671848162737</v>
+        <v>-0.7701944388848077</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5865219358462568</v>
+        <v>-0.4004093072918948</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7289066147070145</v>
+        <v>-0.4965674843959746</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.7958445152477793</v>
+        <v>-0.5347016765286057</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.101622928379086</v>
+        <v>-0.7333320012825837</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.6453784429761313</v>
+        <v>-0.3216311153596862</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.08371896098488918</v>
+        <v>0.2216864276611759</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1167201634082247</v>
+        <v>0.1144654634270523</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.04902658413106309</v>
+        <v>0.3022878198412613</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.2293972215681634</v>
+        <v>0.4144298659348848</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.1265838198970499</v>
+        <v>0.3180370912377981</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 53.8</t>
+          <t>X &lt; 53.71</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1626</v>
+        <v>1659</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.268584339709335</v>
+        <v>-1.207297386793236</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4150639604731978</v>
+        <v>-0.4631890461392132</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3588317549662392</v>
+        <v>-0.2470645961616782</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.00228253784235477</v>
+        <v>0.09322436463989447</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3038508674369282</v>
+        <v>-0.2689311018525089</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.344468910231754</v>
+        <v>0.4019017575406352</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2708131740389845</v>
+        <v>-0.1791441031559273</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.003040161384263</v>
+        <v>-0.8109616047078561</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.049375387028256</v>
+        <v>-0.8899861876533777</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.17627594451649</v>
+        <v>-0.9901699274501325</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.479400675705271</v>
+        <v>-1.346529967356425</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.662434494602373</v>
+        <v>-1.468860195210581</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.341724462710843</v>
+        <v>-1.19737497691694</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.378979809745672</v>
+        <v>-1.204499936481454</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.179279970071327</v>
+        <v>-0.9824951863592801</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.320187165775394</v>
+        <v>-1.084241197678253</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.51537881255679</v>
+        <v>-1.248398884870404</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.436395986966211</v>
+        <v>-1.07989661269626</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.1847767956044</v>
+        <v>-0.8051571100833428</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.7167605643885508</v>
+        <v>-0.4097388386229071</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.7322416881217819</v>
+        <v>-0.4346878607993006</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.833200658069309</v>
+        <v>-0.5098503827545855</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8911838994342745</v>
+        <v>-0.6278795502791112</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.9308793438401608</v>
+        <v>-0.6694639936342668</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.01</t>
+          <t>X &lt; 56.92</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1744</v>
+        <v>1780</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.033137362865077</v>
+        <v>-1.002146549439466</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3170873264159226</v>
+        <v>-0.324846412976477</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1923035737526106</v>
+        <v>-0.1522271067345571</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4889623610278448</v>
+        <v>0.5164954151277925</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.07170345628811958</v>
+        <v>0.160440422918569</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2908095462565043</v>
+        <v>0.2927780761885046</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3351970268187401</v>
+        <v>-0.3588602203720512</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.8657066087808261</v>
+        <v>-0.8564990067232259</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9629097031835627</v>
+        <v>-0.9775898626882906</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.304873137333871</v>
+        <v>-1.181189765269082</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.3405329154957</v>
+        <v>-1.214209557136101</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.301859376940371</v>
+        <v>-1.178411772917471</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.079838886562591</v>
+        <v>-1.001169058907578</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9250725186739075</v>
+        <v>-0.8561446933743966</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8978931434960415</v>
+        <v>-0.8079619966077658</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9888288943114745</v>
+        <v>-0.808455730597089</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.065635808559072</v>
+        <v>-0.8561563670412013</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.365597667638482</v>
+        <v>-1.101400022764594</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.001997391835452</v>
+        <v>-0.7745782450570289</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7244819216627647</v>
+        <v>-0.503812024717142</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.5466037990174968</v>
+        <v>-0.3970992227270926</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.703033002128457</v>
+        <v>-0.5284415199632733</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.024993202685465</v>
+        <v>-0.9589643380556865</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8378526108205406</v>
+        <v>-0.7840246806597548</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.23</t>
+          <t>X &lt; 60.14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1903</v>
+        <v>1937</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5987254285645704</v>
+        <v>-0.6165486993631646</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2815552333218392</v>
+        <v>-0.3216614528745581</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.338161440771124</v>
+        <v>-0.4183561343596978</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5400696864111509</v>
+        <v>0.5083290043803359</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.07747705996428067</v>
+        <v>0.05589018468680251</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.03323358209542704</v>
+        <v>0.03576104142565129</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.344187895301026</v>
+        <v>-0.3701397064198133</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9581492450356777</v>
+        <v>-0.9037158959879221</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.357201263042484</v>
+        <v>-1.313956810552128</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.473937789157141</v>
+        <v>-1.410981812148975</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.431669536383453</v>
+        <v>-1.419391071214584</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9487289394596203</v>
+        <v>-0.8411300967473352</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.7337889808257856</v>
+        <v>-0.6137403350034774</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.6101290757347968</v>
+        <v>-0.5005908135764869</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.7970681848336767</v>
+        <v>-0.6148567081099685</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6215294304299519</v>
+        <v>-0.4665624982732695</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.5983785045802037</v>
+        <v>-0.3639380055068031</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.8818440195055715</v>
+        <v>-0.6000745629141448</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.582710180095404</v>
+        <v>-0.333986109645501</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3649729945377302</v>
+        <v>-0.119399664586517</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2470046060372937</v>
+        <v>-0.06732945249280675</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.291563817219874</v>
+        <v>-0.03923952220235094</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4059375575047497</v>
+        <v>-0.2602410720297996</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.292992250308167</v>
+        <v>-0.1642489357049115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.45</t>
+          <t>X &lt; 63.35</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2057</v>
+        <v>2094</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5835529391421304</v>
+        <v>-0.5986571174743247</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5555853761363068</v>
+        <v>-0.4393649177337124</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5702694668368693</v>
+        <v>-0.3854329888999644</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4307800689248111</v>
+        <v>0.5222398454239112</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1222724603665313</v>
+        <v>0.1306768859667855</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3365478452637021</v>
+        <v>0.3618807751112811</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1183501533963351</v>
+        <v>-0.07314593465775943</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.9004606224019795</v>
+        <v>-0.7799357489686329</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.266694503429299</v>
+        <v>-1.197252634753873</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.528963467807174</v>
+        <v>-1.442264990578934</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.517831718039226</v>
+        <v>-1.429533738164857</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9465011996434356</v>
+        <v>-0.820282465577904</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7829246716079652</v>
+        <v>-0.6463917667995602</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8303591987105605</v>
+        <v>-0.6759079549135123</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.100905597066308</v>
+        <v>-0.9282629098644719</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.5065186751233171</v>
+        <v>-0.3192033991632499</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.5435365872945894</v>
+        <v>-0.3275728271251239</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.813641431920729</v>
+        <v>-0.555967916049859</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.6176846710843975</v>
+        <v>-0.3892611807856454</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5478330975266061</v>
+        <v>-0.2224302276082284</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5764191273751251</v>
+        <v>-0.3123198101732996</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5263438431988945</v>
+        <v>-0.2919713483654505</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.6117341618607739</v>
+        <v>-0.478136290021169</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7074799294862757</v>
+        <v>-0.5925197924290728</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 66.67</t>
+          <t>X &lt; 66.56</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2193</v>
+        <v>2229</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3436474747689147</v>
+        <v>-0.3520867905827032</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4284029447686706</v>
+        <v>-0.4403192781001763</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.57639160457407</v>
+        <v>-0.5099538827672419</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4089073164428143</v>
+        <v>0.4859072221702618</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4154406014958525</v>
+        <v>0.4589505738396795</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3112695436160067</v>
+        <v>0.3727581237458395</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.0274424143638754</v>
+        <v>0.005473432552200563</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7329216762731647</v>
+        <v>-0.5874708202371579</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.164420596027057</v>
+        <v>-1.01652051062738</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.140910116227985</v>
+        <v>-0.9811608017992626</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.566979285421226</v>
+        <v>-1.400749535003975</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.275499015259641</v>
+        <v>-1.069327276520035</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.8742350146155431</v>
+        <v>-0.6595557168407638</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9779533155496409</v>
+        <v>-0.7471876864029596</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.136323782598609</v>
+        <v>-0.9358472275522658</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.8599741164484414</v>
+        <v>-0.5988590454306646</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.6490686521289817</v>
+        <v>-0.3438341184387639</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9999509451022632</v>
+        <v>-0.6561708929588193</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9848291256586492</v>
+        <v>-0.6660245025111209</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7713525763624816</v>
+        <v>-0.4065748901125161</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.7407956637077362</v>
+        <v>-0.4356613834178873</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6530391339442332</v>
+        <v>-0.3762344033543243</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.8073378623851326</v>
+        <v>-0.6260947588117034</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.8107386075490766</v>
+        <v>-0.6536442510823335</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 69.89</t>
+          <t>X &lt; 69.78</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2342</v>
+        <v>2380</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6150324710282433</v>
+        <v>-0.6162053234283178</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9696967314261542</v>
+        <v>-0.8817999795401121</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7334227151541555</v>
+        <v>-0.6499222263755087</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.02490206500127101</v>
+        <v>0.1617749073568007</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.002216192809754602</v>
+        <v>0.1189627491552443</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.04132457459345318</v>
+        <v>0.04800785525963391</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2802931580628822</v>
+        <v>-0.1788418592975347</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8315236703912774</v>
+        <v>-0.6697704810912413</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.063287419378931</v>
+        <v>-0.8957910318210693</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.8777405606685775</v>
+        <v>-0.7452078073959498</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.259363336981458</v>
+        <v>-1.120841318554682</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.003876521504985</v>
+        <v>-0.8278603569794996</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6565758817982683</v>
+        <v>-0.4727818738422869</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4697703812934435</v>
+        <v>-0.2764071803916721</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7874881469591131</v>
+        <v>-0.580410301772524</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5760799484203716</v>
+        <v>-0.3132239300116879</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.1740696196586882</v>
+        <v>0.171130952380949</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.509136241500741</v>
+        <v>-0.1298203796714077</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5662745501507587</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4821882078385613</v>
+        <v>-0.0369061612481616</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.4452787129424323</v>
+        <v>-0.1001489819566288</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.3251336397633864</v>
+        <v>-0.007244277021158041</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.6654267565134191</v>
+        <v>-0.4358786993058033</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.801470705603478</v>
+        <v>-0.598017693595267</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 73.11</t>
+          <t>X &lt; 72.99</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2483</v>
+        <v>2522</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2862145255725395</v>
+        <v>-0.2881888582881089</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5996750504154207</v>
+        <v>-0.4736164367426454</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4576077889502699</v>
+        <v>-0.3255016491249236</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1708840273414509</v>
+        <v>0.3280352223735647</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.09761254719721535</v>
+        <v>0.2326286686380712</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1071317545030723</v>
+        <v>0.2536507397243994</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.2819576207318661</v>
+        <v>-0.2029544416904727</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6976278510957243</v>
+        <v>-0.5251429302062292</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9139019057418167</v>
+        <v>-0.6915040427128432</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.982861592877434</v>
+        <v>-0.7527832402671493</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.407649525576538</v>
+        <v>-1.170936504395669</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.262662346304225</v>
+        <v>-0.9894839073928026</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8782806582227636</v>
+        <v>-0.6154591629837896</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7146519549586401</v>
+        <v>-0.4045234546571237</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.9713500498093666</v>
+        <v>-0.6901671307531245</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8586973711421635</v>
+        <v>-0.4857227471436119</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3265056729395042</v>
+        <v>0.08446504097277341</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6485914115402238</v>
+        <v>-0.2070233465044495</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.5697338475777229</v>
+        <v>-0.1115143310953925</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3994047929044342</v>
+        <v>0.1030721139635915</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.5160031278750097</v>
+        <v>-0.1075127522069934</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.3667656845920817</v>
+        <v>0.01558007873224909</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.5916640220035987</v>
+        <v>-0.2959004240940502</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8048067983785074</v>
+        <v>-0.4976904889624194</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 76.33</t>
+          <t>X &lt; 76.21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2608</v>
+        <v>2649</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1984735873764336</v>
+        <v>-0.2368416041436561</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7412251294378009</v>
+        <v>-0.6881953450997003</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5982642017720394</v>
+        <v>-0.4943554852549212</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1860029208495675</v>
+        <v>-0.05082354634954811</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2719112623265971</v>
+        <v>-0.1549803296700389</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4827383398761356</v>
+        <v>-0.3157899650438267</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6615521846788681</v>
+        <v>-0.56289062771571</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.9945363915349503</v>
+        <v>-0.8467238975713585</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.12232389676111</v>
+        <v>-0.9614447493956604</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.034109126111844</v>
+        <v>-0.8695336048882041</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.311014393929547</v>
+        <v>-1.141547140119883</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.186222187043938</v>
+        <v>-0.9820262664942021</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.759183460066005</v>
+        <v>-0.5284109499400174</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5756653647016066</v>
+        <v>-0.3394561825519915</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9662245644228307</v>
+        <v>-0.7196098094351626</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.8687795385043131</v>
+        <v>-0.5735568287430937</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.5213961334430905</v>
+        <v>-0.186686013590041</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.9479345350556798</v>
+        <v>-0.5460706850030519</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7860957678797575</v>
+        <v>-0.3693585522325122</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.5767742811652923</v>
+        <v>-0.1170220127982944</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.6372335309626322</v>
+        <v>-0.2692154760514356</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.4988223926565567</v>
+        <v>-0.1178774317553106</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.5848592603368985</v>
+        <v>-0.2894939846045261</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6380439768361867</v>
+        <v>-0.3761327901435152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 79.55</t>
+          <t>X &lt; 79.42</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2741</v>
+        <v>2776</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6719839707817101</v>
+        <v>-0.6204323932235454</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.16866990960866</v>
+        <v>-1.026697121920641</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8846574535663976</v>
+        <v>-0.6837012932625584</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5629869766310165</v>
+        <v>-0.3592479549665342</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7335984752828466</v>
+        <v>-0.57905155937123</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9254031310507074</v>
+        <v>-0.653679685971845</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.169285770624782</v>
+        <v>-0.9977733494037579</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.318321867218167</v>
+        <v>-1.138944129598343</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.365430451633117</v>
+        <v>-1.134814100631722</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.35523001297225</v>
+        <v>-1.083530518928782</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.387601410099393</v>
+        <v>-1.150828124360117</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.500449196376465</v>
+        <v>-1.227230339342277</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.966679899431</v>
+        <v>-0.7013952345963261</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8755659123569686</v>
+        <v>-0.6045499648829988</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.097186838165975</v>
+        <v>-0.8544276897075278</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.121206609566016</v>
+        <v>-0.83346949221351</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.942769856310548</v>
+        <v>-0.6131424111431301</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-1.02625604820949</v>
+        <v>-0.6379573520396065</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.9710776320476242</v>
+        <v>-0.5315642891589576</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7264826469256747</v>
+        <v>-0.2449317345898905</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.7739197642456901</v>
+        <v>-0.4161226336651538</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8646857606444627</v>
+        <v>-0.5273082103754732</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8239603464890592</v>
+        <v>-0.5718581631374491</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.7323990664434419</v>
+        <v>-0.5178588288966566</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 82.77</t>
+          <t>X &lt; 82.63</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2845</v>
+        <v>2884</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5888764123506931</v>
+        <v>-0.644076003472918</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.9400342397650334</v>
+        <v>-0.8372046028203286</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9633811807080619</v>
+        <v>-0.8305204833856052</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6447534048365142</v>
+        <v>-0.4370115570876791</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.8563797685554917</v>
+        <v>-0.6589419783523738</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.069271720933223</v>
+        <v>-0.8285717162788515</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.122868028191</v>
+        <v>-0.9476766598108952</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.311595381362821</v>
+        <v>-1.095004000573013</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.390425098358925</v>
+        <v>-1.155393688517393</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.30403578170295</v>
+        <v>-1.032244444984194</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.150118605726618</v>
+        <v>-0.9135793282348459</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.268982563921959</v>
+        <v>-1.03209527470581</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.9011489330243734</v>
+        <v>-0.6374604929518242</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8565362492801469</v>
+        <v>-0.5882927665152025</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-1.059178495704437</v>
+        <v>-0.7851785175510457</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.039973871204154</v>
+        <v>-0.7438051746412526</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9430250463658894</v>
+        <v>-0.605051270941658</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.9922148946766143</v>
+        <v>-0.5992871958606187</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.7557213243081478</v>
+        <v>-0.3501629236541959</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6184589323445806</v>
+        <v>-0.2049005687165248</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.5434885066704211</v>
+        <v>-0.1830903040660559</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.5282544627121624</v>
+        <v>-0.2235907809606914</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5842801524485637</v>
+        <v>-0.3265767462889002</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.5690525269779769</v>
+        <v>-0.3642737105651648</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 85.98</t>
+          <t>X &lt; 85.85</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2941</v>
+        <v>2981</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.586510292642231</v>
+        <v>-0.5543128716832157</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9371364033415333</v>
+        <v>-0.8493218069674384</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8374862569964918</v>
+        <v>-0.7164652199994066</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5522726559311906</v>
+        <v>-0.3548812014126597</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9030768749048548</v>
+        <v>-0.7122578809091564</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.03539422140453</v>
+        <v>-0.8044216226957985</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9770283882014397</v>
+        <v>-0.811631492815458</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.1347830191648</v>
+        <v>-0.9305620751404007</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.175803181285225</v>
+        <v>-0.9513028357679332</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.117267167737374</v>
+        <v>-0.8914350325583342</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.060972597461088</v>
+        <v>-0.8347340399281222</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.185005883819024</v>
+        <v>-0.9248497040558377</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8317610737632677</v>
+        <v>-0.5457418628490132</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7618727974492359</v>
+        <v>-0.4726828737676172</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.9454398238433512</v>
+        <v>-0.651819147000765</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8396528869570616</v>
+        <v>-0.5264641556794203</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.7840754363895002</v>
+        <v>-0.4291373239436638</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.9368226421888721</v>
+        <v>-0.5284868885284624</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.8707032802162473</v>
+        <v>-0.4481628236898771</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.7658194871754205</v>
+        <v>-0.3341800003612718</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.7450029180040829</v>
+        <v>-0.3650718525132959</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6988294227806406</v>
+        <v>-0.3731652933150045</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6761476129749369</v>
+        <v>-0.3978071326509749</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7659297174652835</v>
+        <v>-0.5402146327533544</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 89.2</t>
+          <t>X &lt; 89.06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3036</v>
+        <v>3075</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5015403770029323</v>
+        <v>-0.5005555306996001</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5899516841075965</v>
+        <v>-0.4703076007196145</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7997686152630337</v>
+        <v>-0.6066991682967142</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5455822503046193</v>
+        <v>-0.3068316785732321</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7649414803076979</v>
+        <v>-0.532056442721192</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9200331238950596</v>
+        <v>-0.6813208491827893</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.084067198302186</v>
+        <v>-0.9073130645447378</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.245607616260017</v>
+        <v>-1.032005800088847</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.284094213434123</v>
+        <v>-1.080643324196373</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.153106970480785</v>
+        <v>-0.9498380571241256</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.122845260432065</v>
+        <v>-0.9189755940189244</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.186084291386827</v>
+        <v>-0.9499157268497029</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8132267865556884</v>
+        <v>-0.5519498811254238</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.8180916613828799</v>
+        <v>-0.5538109595829042</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.8522612315414406</v>
+        <v>-0.5859815910617243</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.8626010432843572</v>
+        <v>-0.577163760087366</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7143600810418462</v>
+        <v>-0.3885514841295574</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.8327151655252081</v>
+        <v>-0.4889364017708573</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.7947666521954346</v>
+        <v>-0.4369701122266392</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8517702511822165</v>
+        <v>-0.4823771673301493</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.914403965259325</v>
+        <v>-0.5623338559062034</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.8721018490442347</v>
+        <v>-0.5399988153005566</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.8086735613564073</v>
+        <v>-0.5372872731384533</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7333724280595391</v>
+        <v>-0.5502620059543588</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 92.42</t>
+          <t>X &lt; 92.27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3140</v>
+        <v>3177</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4782917687134329</v>
+        <v>-0.4411229687121008</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4482591537937992</v>
+        <v>-0.3256692579542317</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.571870808914035</v>
+        <v>-0.4037292331041655</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2861411397996747</v>
+        <v>-0.06962171148824581</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.6359150018844772</v>
+        <v>-0.3904853697328008</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6529949125717351</v>
+        <v>-0.4357730682107572</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8369770481876486</v>
+        <v>-0.679907660063563</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.033980761434414</v>
+        <v>-0.8416979845551396</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.9746458938399627</v>
+        <v>-0.7275842259797827</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9050910819856881</v>
+        <v>-0.6892031909702183</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.8032548158366168</v>
+        <v>-0.587667995269463</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.7782975561835386</v>
+        <v>-0.5320706110328288</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4547029874540769</v>
+        <v>-0.1824990002544737</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4983508830400325</v>
+        <v>-0.2550617438213152</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5531280326371046</v>
+        <v>-0.3080874688960691</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.54339455546571</v>
+        <v>-0.2815428083651668</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3726004428676433</v>
+        <v>-0.07085889168502035</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3632545562044598</v>
+        <v>-0.0464608326440441</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3192724915744733</v>
+        <v>0.01071923029915212</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2726387391961538</v>
+        <v>0.06802351115555894</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3827849456984822</v>
+        <v>-0.0590309304579506</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.3442243256811395</v>
+        <v>-0.008367721051172339</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3373141195909</v>
+        <v>-0.06068897583932653</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2350214298470163</v>
+        <v>-0.01535025457055639</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 95.64</t>
+          <t>X &lt; 95.49</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3249</v>
+        <v>3280</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1709602286872425</v>
+        <v>-0.2194097326629461</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1529939423628264</v>
+        <v>-0.1455463142698434</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3203422572336976</v>
+        <v>-0.2603549053051992</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2820437366814659</v>
+        <v>-0.1678291354741788</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3864768314376192</v>
+        <v>-0.2442174789375215</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4885259819534156</v>
+        <v>-0.3743151888890779</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5389472859709414</v>
+        <v>-0.4836629538704358</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6466598267213826</v>
+        <v>-0.5586364163006508</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.61844910157388</v>
+        <v>-0.4744265146974911</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.6075923542161803</v>
+        <v>-0.4621238098468652</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4999082356558375</v>
+        <v>-0.3551672562379906</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4850125341922791</v>
+        <v>-0.3099176098661189</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.301768744308113</v>
+        <v>-0.09760387633613732</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2592248175093701</v>
+        <v>-0.05377699486225396</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.272800895937074</v>
+        <v>-0.06560840295084347</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2434151152296664</v>
+        <v>-0.02228122751936468</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.1134421165024477</v>
+        <v>0.1480613954905508</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.0771184049656668</v>
+        <v>0.1979926468188893</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.02728992004455932</v>
+        <v>0.2601087435563798</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.03734995898230409</v>
+        <v>0.2614106060437678</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1926672316037426</v>
+        <v>0.09006604372457616</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.188643738520085</v>
+        <v>0.106311200014261</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1111734980348089</v>
+        <v>0.1547513350913761</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.04556578156326907</v>
+        <v>0.1631526281919875</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 98.86</t>
+          <t>X &lt; 98.7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3348</v>
+        <v>3374</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03657538397483506</v>
+        <v>-0.02274454843460205</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1477307367076008</v>
+        <v>-0.07609985727351898</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2043820525313862</v>
+        <v>-0.1065934187269733</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1586634885690543</v>
+        <v>-0.0342147701746498</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1808311712465098</v>
+        <v>-0.02796771561331468</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2445240593376141</v>
+        <v>-0.1200361095299769</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2271619268216156</v>
+        <v>-0.1610212736396335</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3695766391062634</v>
+        <v>-0.3017184835366749</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2814180314537609</v>
+        <v>-0.1866172861729822</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2937737205235678</v>
+        <v>-0.2276363801346761</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2703052011914693</v>
+        <v>-0.2043541740799242</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2640806031376499</v>
+        <v>-0.1981211787134285</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2685175675681606</v>
+        <v>-0.2023633980852892</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1742550669599368</v>
+        <v>-0.1080666330550599</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1296185952443736</v>
+        <v>-0.06298594072375607</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.08352295301043711</v>
+        <v>-0.004491741484102363</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1401267743346466</v>
+        <v>-0.04921805678793589</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.13779291425233</v>
+        <v>-0.01669820772570318</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.006392729092588922</v>
+        <v>0.1561039925573127</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.0618241465065168</v>
+        <v>0.2401957985410803</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.01537808180982836</v>
+        <v>0.1936451717723813</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.01366198778437422</v>
+        <v>0.2249931677197807</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.01989481553486883</v>
+        <v>0.190016103059591</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.01168922163044073</v>
+        <v>0.1936765774741573</v>
       </c>
     </row>
   </sheetData>
